--- a/test-cases/QA_Playground_TypeScript_Playwright_Test_Suite.xlsx
+++ b/test-cases/QA_Playground_TypeScript_Playwright_Test_Suite.xlsx
@@ -1,14 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Silerio\Music\PLAYWRIGHT AUTOMATION\test-cases\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96FC1E58-8D21-454D-8555-AE066D3A5776}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <bookViews>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
-    <sheet state="visible" name="Dashboard" sheetId="1" r:id="rId5"/>
-    <sheet state="visible" name="Test Scenarios" sheetId="2" r:id="rId6"/>
-    <sheet state="visible" name="Test Cases" sheetId="3" r:id="rId7"/>
+    <sheet name="Dashboard" sheetId="1" r:id="rId1"/>
+    <sheet name="Test Scenarios" sheetId="2" r:id="rId2"/>
+    <sheet name="Test Cases" sheetId="3" r:id="rId3"/>
   </sheets>
-  <definedNames/>
-  <calcPr/>
+  <calcPr calcId="181029"/>
 </workbook>
 </file>
 
@@ -1050,91 +1059,98 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="15">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
+  <fonts count="16">
     <font>
-      <sz val="11.0"/>
+      <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Carlito"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="18.0"/>
+      <sz val="18"/>
       <color rgb="FFFFFFFF"/>
       <name val="Play"/>
     </font>
     <font>
-      <sz val="10.0"/>
+      <sz val="10"/>
       <color rgb="FF146C77"/>
       <name val="Aptos"/>
     </font>
     <font>
       <b/>
-      <sz val="11.0"/>
+      <sz val="11"/>
       <color rgb="FFFFFFFF"/>
       <name val="Carlito"/>
     </font>
     <font>
       <b/>
-      <sz val="10.0"/>
+      <sz val="10"/>
       <color rgb="FFFFFFFF"/>
       <name val="Aptos"/>
     </font>
     <font>
-      <sz val="11.0"/>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="Carlito"/>
     </font>
     <font>
       <b/>
-      <sz val="10.0"/>
+      <sz val="10"/>
       <color rgb="FF173B52"/>
       <name val="Aptos"/>
     </font>
     <font>
-      <sz val="10.0"/>
+      <sz val="10"/>
       <color rgb="FF243447"/>
       <name val="Aptos"/>
     </font>
     <font>
-      <sz val="10.0"/>
+      <sz val="10"/>
       <color rgb="FF243447"/>
       <name val="Arial"/>
     </font>
     <font>
       <b/>
-      <sz val="19.0"/>
+      <sz val="19"/>
       <color rgb="FFFFFFFF"/>
       <name val="Play"/>
     </font>
     <font>
       <b/>
-      <sz val="10.0"/>
+      <sz val="10"/>
       <color rgb="FF37566A"/>
       <name val="Aptos"/>
     </font>
     <font>
       <b/>
-      <sz val="20.0"/>
+      <sz val="20"/>
       <color rgb="FF102A43"/>
       <name val="Aptos"/>
     </font>
     <font>
-      <sz val="10.0"/>
+      <sz val="10"/>
       <color rgb="FF7A5A16"/>
       <name val="Aptos"/>
     </font>
     <font>
       <b/>
-      <sz val="10.0"/>
+      <sz val="10"/>
       <color rgb="FF243447"/>
       <name val="Aptos"/>
     </font>
     <font>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="Carlito"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF243447"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="10">
@@ -1142,7 +1158,7 @@
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="lightGray"/>
+      <patternFill patternType="gray125"/>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -1194,7 +1210,13 @@
     </fill>
   </fills>
   <borders count="2">
-    <border/>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
     <border>
       <left style="thin">
         <color rgb="FFD5E2E9"/>
@@ -1208,127 +1230,126 @@
       <bottom style="thin">
         <color rgb="FFD5E2E9"/>
       </bottom>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+  <cellXfs count="27">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf borderId="0" fillId="3" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf borderId="0" fillId="4" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
-      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="0" fillId="4" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
-      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="0" fillId="5" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="top" wrapText="1"/>
-    </xf>
-    <xf borderId="0" fillId="5" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="top" wrapText="1"/>
-    </xf>
-    <xf borderId="0" fillId="5" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="top" wrapText="1"/>
-    </xf>
-    <xf borderId="0" fillId="6" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="top" wrapText="1"/>
-    </xf>
-    <xf borderId="0" fillId="6" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="top" wrapText="1"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="7" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="0" fillId="2" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf borderId="0" fillId="7" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf borderId="0" fillId="7" fontId="11" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf borderId="0" fillId="7" fontId="11" numFmtId="9" xfId="0" applyAlignment="1" applyFill="1" applyFont="1" applyNumberFormat="1">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="9" fontId="11" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf borderId="0" fillId="8" fontId="12" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
-      <alignment shrinkToFit="0" wrapText="1"/>
+    <xf numFmtId="0" fontId="12" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="4" fontId="4" numFmtId="0" xfId="0" applyFill="1" applyFont="1"/>
-    <xf borderId="1" fillId="9" fontId="6" numFmtId="0" xfId="0" applyBorder="1" applyFill="1" applyFont="1"/>
-    <xf borderId="1" fillId="0" fontId="7" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="1" fillId="0" fontId="7" numFmtId="9" xfId="0" applyBorder="1" applyFont="1" applyNumberFormat="1"/>
-    <xf borderId="1" fillId="9" fontId="13" numFmtId="0" xfId="0" applyBorder="1" applyFill="1" applyFont="1"/>
-    <xf borderId="1" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="7" numFmtId="9" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="14" numFmtId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle xfId="0" name="Normal" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="6">
+  <dxfs count="8">
     <dxf>
-      <font/>
-      <fill>
-        <patternFill patternType="none"/>
-      </fill>
-      <border/>
+      <border>
+        <left style="thin">
+          <color theme="4"/>
+        </left>
+        <right style="thin">
+          <color theme="4"/>
+        </right>
+        <top style="thin">
+          <color theme="4"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4"/>
+        </bottom>
+        <vertical style="thin">
+          <color rgb="FFD4D4D4"/>
+        </vertical>
+        <horizontal style="thin">
+          <color rgb="FFD4D4D4"/>
+        </horizontal>
+      </border>
     </dxf>
     <dxf>
-      <font/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
       <fill>
         <patternFill patternType="solid">
           <fgColor theme="4"/>
           <bgColor theme="4"/>
         </patternFill>
       </fill>
-      <border/>
-    </dxf>
-    <dxf>
-      <font/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-      <border/>
-    </dxf>
-    <dxf>
-      <font/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC1E4F5"/>
-          <bgColor rgb="FFC1E4F5"/>
-        </patternFill>
-      </fill>
-      <border/>
-    </dxf>
-    <dxf>
-      <font/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="0"/>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-      <border/>
     </dxf>
     <dxf>
       <border>
@@ -1352,26 +1373,62 @@
         </horizontal>
       </border>
     </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="0"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC1E4F5"/>
+          <bgColor rgb="FFC1E4F5"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4"/>
+          <bgColor theme="4"/>
+        </patternFill>
+      </fill>
+    </dxf>
   </dxfs>
   <tableStyles count="2">
-    <tableStyle count="4" pivot="0" name="Test Scenarios-style">
-      <tableStyleElement dxfId="1" type="headerRow"/>
-      <tableStyleElement dxfId="3" type="firstRowStripe"/>
-      <tableStyleElement dxfId="4" type="secondRowStripe"/>
-      <tableStyleElement dxfId="5" size="0" type="wholeTable"/>
+    <tableStyle name="Test Scenarios-style" pivot="0" count="4" xr9:uid="{00000000-0011-0000-FFFF-FFFF00000000}">
+      <tableStyleElement type="wholeTable" size="0" dxfId="4"/>
+      <tableStyleElement type="headerRow" dxfId="7"/>
+      <tableStyleElement type="firstRowStripe" dxfId="6"/>
+      <tableStyleElement type="secondRowStripe" dxfId="5"/>
     </tableStyle>
-    <tableStyle count="4" pivot="0" name="Test Cases-style">
-      <tableStyleElement dxfId="1" type="headerRow"/>
-      <tableStyleElement dxfId="2" type="firstRowStripe"/>
-      <tableStyleElement dxfId="2" type="secondRowStripe"/>
-      <tableStyleElement dxfId="5" size="0" type="wholeTable"/>
+    <tableStyle name="Test Cases-style" pivot="0" count="4" xr9:uid="{00000000-0011-0000-FFFF-FFFF01000000}">
+      <tableStyleElement type="wholeTable" size="0" dxfId="0"/>
+      <tableStyleElement type="headerRow" dxfId="3"/>
+      <tableStyleElement type="firstRowStripe" dxfId="2"/>
+      <tableStyleElement type="secondRowStripe" dxfId="1"/>
     </tableStyle>
   </tableStyles>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart">
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="1"/>
+  <c:style val="2"/>
   <c:chart>
     <c:title>
       <c:tx>
@@ -1388,7 +1445,7 @@
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:rPr b="0">
+              <a:rPr lang="en-PH" b="0">
                 <a:solidFill>
                   <a:srgbClr val="757575"/>
                 </a:solidFill>
@@ -1401,6 +1458,7 @@
       </c:tx>
       <c:overlay val="0"/>
     </c:title>
+    <c:autoTitleDeleted val="0"/>
     <c:plotArea>
       <c:layout/>
       <c:pieChart>
@@ -1410,56 +1468,106 @@
           <c:order val="0"/>
           <c:dPt>
             <c:idx val="0"/>
+            <c:bubble3D val="0"/>
             <c:spPr>
               <a:solidFill>
                 <a:srgbClr val="156082"/>
               </a:solidFill>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000001-2F76-4FDC-8FA4-FF2CC5A82A45}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="1"/>
+            <c:bubble3D val="0"/>
             <c:spPr>
               <a:solidFill>
                 <a:srgbClr val="E97132"/>
               </a:solidFill>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000003-2F76-4FDC-8FA4-FF2CC5A82A45}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="2"/>
+            <c:bubble3D val="0"/>
             <c:spPr>
               <a:solidFill>
                 <a:srgbClr val="196B24"/>
               </a:solidFill>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000005-2F76-4FDC-8FA4-FF2CC5A82A45}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="3"/>
+            <c:bubble3D val="0"/>
             <c:spPr>
               <a:solidFill>
                 <a:srgbClr val="0F9ED5"/>
               </a:solidFill>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000007-2F76-4FDC-8FA4-FF2CC5A82A45}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
-          <c:dLbls>
-            <c:showLegendKey val="0"/>
-            <c:showVal val="0"/>
-            <c:showCatName val="0"/>
-            <c:showSerName val="0"/>
-            <c:showPercent val="0"/>
-            <c:showBubbleSize val="0"/>
-            <c:showLeaderLines val="1"/>
-          </c:dLbls>
           <c:cat>
             <c:strRef>
               <c:f>Dashboard!$B$22:$B$25</c:f>
+              <c:strCache>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>Not Automated</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>In Progress</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Automated</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Skipped</c:v>
+                </c:pt>
+              </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
               <c:f>Dashboard!$C$22:$C$25</c:f>
-              <c:numCache/>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>16</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0</c:v>
+                </c:pt>
+              </c:numCache>
             </c:numRef>
           </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000008-2F76-4FDC-8FA4-FF2CC5A82A45}"/>
+            </c:ext>
+          </c:extLst>
         </c:ser>
         <c:dLbls>
           <c:showLegendKey val="0"/>
@@ -1468,6 +1576,7 @@
           <c:showSerName val="0"/>
           <c:showPercent val="0"/>
           <c:showBubbleSize val="0"/>
+          <c:showLeaderLines val="1"/>
         </c:dLbls>
         <c:firstSliceAng val="0"/>
       </c:pieChart>
@@ -1487,16 +1596,28 @@
               <a:latin typeface="+mn-lt"/>
             </a:defRPr>
           </a:pPr>
+          <a:endParaRPr lang="en-US"/>
         </a:p>
       </c:txPr>
     </c:legend>
     <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="zero"/>
+    <c:showDLblsOverMax val="1"/>
   </c:chart>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
 </c:chartSpace>
 </file>
 
 <file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart">
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="1"/>
+  <c:style val="2"/>
   <c:chart>
     <c:title>
       <c:tx>
@@ -1513,7 +1634,7 @@
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:rPr b="0">
+              <a:rPr lang="en-PH" b="0">
                 <a:solidFill>
                   <a:srgbClr val="757575"/>
                 </a:solidFill>
@@ -1526,10 +1647,13 @@
       </c:tx>
       <c:overlay val="0"/>
     </c:title>
+    <c:autoTitleDeleted val="0"/>
     <c:plotArea>
       <c:layout/>
       <c:barChart>
         <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="1"/>
         <c:ser>
           <c:idx val="0"/>
           <c:order val="0"/>
@@ -1548,14 +1672,49 @@
           <c:cat>
             <c:strRef>
               <c:f>Dashboard!$B$14:$B$17</c:f>
+              <c:strCache>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>01 Basics</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>02 Forms</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>03 Browser</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>04 Advanced</c:v>
+                </c:pt>
+              </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
               <c:f>Dashboard!$C$14:$C$17</c:f>
-              <c:numCache/>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>4</c:v>
+                </c:pt>
+              </c:numCache>
             </c:numRef>
           </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-1502-4927-9F97-81C2FF6AA4C7}"/>
+            </c:ext>
+          </c:extLst>
         </c:ser>
         <c:ser>
           <c:idx val="1"/>
@@ -1575,15 +1734,59 @@
           <c:cat>
             <c:strRef>
               <c:f>Dashboard!$B$14:$B$17</c:f>
+              <c:strCache>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>01 Basics</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>02 Forms</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>03 Browser</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>04 Advanced</c:v>
+                </c:pt>
+              </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
               <c:f>Dashboard!$D$14:$D$17</c:f>
-              <c:numCache/>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0</c:v>
+                </c:pt>
+              </c:numCache>
             </c:numRef>
           </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-1502-4927-9F97-81C2FF6AA4C7}"/>
+            </c:ext>
+          </c:extLst>
         </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="150"/>
         <c:axId val="2145920074"/>
         <c:axId val="238486389"/>
       </c:barChart>
@@ -1608,15 +1811,7 @@
                     <a:latin typeface="+mn-lt"/>
                   </a:defRPr>
                 </a:pPr>
-                <a:r>
-                  <a:rPr b="0">
-                    <a:solidFill>
-                      <a:srgbClr val="000000"/>
-                    </a:solidFill>
-                    <a:latin typeface="+mn-lt"/>
-                  </a:rPr>
-                  <a:t/>
-                </a:r>
+                <a:endParaRPr lang="en-PH"/>
               </a:p>
             </c:rich>
           </c:tx>
@@ -1625,6 +1820,7 @@
         <c:numFmt formatCode="General" sourceLinked="0"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
         <c:spPr>
           <a:ln>
             <a:noFill/>
@@ -1642,9 +1838,15 @@
                 <a:latin typeface="+mn-lt"/>
               </a:defRPr>
             </a:pPr>
+            <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="238486389"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="1"/>
       </c:catAx>
       <c:valAx>
         <c:axId val="238486389"/>
@@ -1676,15 +1878,7 @@
                     <a:latin typeface="+mn-lt"/>
                   </a:defRPr>
                 </a:pPr>
-                <a:r>
-                  <a:rPr b="0">
-                    <a:solidFill>
-                      <a:srgbClr val="000000"/>
-                    </a:solidFill>
-                    <a:latin typeface="+mn-lt"/>
-                  </a:rPr>
-                  <a:t/>
-                </a:r>
+                <a:endParaRPr lang="en-PH"/>
               </a:p>
             </c:rich>
           </c:tx>
@@ -1711,9 +1905,12 @@
                 <a:latin typeface="+mn-lt"/>
               </a:defRPr>
             </a:pPr>
+            <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="2145920074"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
       </c:valAx>
     </c:plotArea>
     <c:legend>
@@ -1731,16 +1928,24 @@
               <a:latin typeface="+mn-lt"/>
             </a:defRPr>
           </a:pPr>
+          <a:endParaRPr lang="en-US"/>
         </a:p>
       </c:txPr>
     </c:legend>
     <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="zero"/>
+    <c:showDLblsOverMax val="1"/>
   </c:chart>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
 </c:chartSpace>
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer">
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:oneCellAnchor>
     <xdr:from>
       <xdr:col>7</xdr:col>
@@ -1749,9 +1954,15 @@
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="8001000" cy="3371850"/>
-    <xdr:graphicFrame>
+    <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="1" name="Chart 1"/>
+        <xdr:cNvPr id="2" name="Chart 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
@@ -1760,7 +1971,7 @@
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId1"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -1774,9 +1985,15 @@
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="8001000" cy="6229350"/>
-    <xdr:graphicFrame>
+    <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="2" name="Chart 2"/>
+        <xdr:cNvPr id="3" name="Chart 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000003000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
@@ -1785,7 +2002,7 @@
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId2"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -1794,58 +2011,50 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
 <file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
 <x18tc:personList xmlns:x18tc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments"/>
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A5:G24" displayName="ScenariosTable" name="ScenariosTable" id="2">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="ScenariosTable" displayName="ScenariosTable" ref="A5:G24">
   <tableColumns count="7">
-    <tableColumn name="Scenario ID" id="1"/>
-    <tableColumn name="Practice area" id="2"/>
-    <tableColumn name="Level" id="3"/>
-    <tableColumn name="Scenario / coverage" id="4"/>
-    <tableColumn name="Source URL" id="5"/>
-    <tableColumn name="Phase" id="6"/>
-    <tableColumn name="Status" id="7"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Scenario ID"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Practice area"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Level"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Scenario / coverage"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Source URL"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="Phase"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="Status"/>
   </tableColumns>
-  <tableStyleInfo name="Test Scenarios-style" showColumnStripes="0" showFirstColumn="1" showLastColumn="1" showRowStripes="1"/>
+  <tableStyleInfo name="Test Scenarios-style" showFirstColumn="1" showLastColumn="1" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A5:O24" displayName="CasesByScenario" name="CasesByScenario" id="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="CasesByScenario" displayName="CasesByScenario" ref="A5:O24">
   <tableColumns count="15">
-    <tableColumn name="Scenario ID" id="1"/>
-    <tableColumn name="TC ID" id="2"/>
-    <tableColumn name="Scenario coverage" id="3"/>
-    <tableColumn name="Practice area" id="4"/>
-    <tableColumn name="Test case / objective" id="5"/>
-    <tableColumn name="Test steps" id="6"/>
-    <tableColumn name="Test data by step" id="7"/>
-    <tableColumn name="Expected result by step" id="8"/>
-    <tableColumn name="Type" id="9"/>
-    <tableColumn name="Priority" id="10"/>
-    <tableColumn name="Phase" id="11"/>
-    <tableColumn name="Automation" id="12"/>
-    <tableColumn name="Run status" id="13"/>
-    <tableColumn name="Source URL" id="14"/>
-    <tableColumn name="Step count" id="15"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="Scenario ID"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0100-000002000000}" name="TC ID"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0100-000003000000}" name="Scenario coverage"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0100-000004000000}" name="Practice area"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0100-000005000000}" name="Test case / objective"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0100-000006000000}" name="Test steps"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0100-000007000000}" name="Test data by step"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0100-000008000000}" name="Expected result by step"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0100-000009000000}" name="Type"/>
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0100-00000A000000}" name="Priority"/>
+    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0100-00000B000000}" name="Phase"/>
+    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0100-00000C000000}" name="Automation"/>
+    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0100-00000D000000}" name="Run status"/>
+    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0100-00000E000000}" name="Source URL"/>
+    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0100-00000F000000}" name="Step count"/>
   </tableColumns>
-  <tableStyleInfo name="Test Cases-style" showColumnStripes="0" showFirstColumn="1" showLastColumn="1" showRowStripes="1"/>
+  <tableStyleInfo name="Test Cases-style" showFirstColumn="1" showLastColumn="1" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheets">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Sheets">
   <a:themeElements>
     <a:clrScheme name="Sheets">
       <a:dk1>
@@ -2035,1142 +2244,1232 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
     <tabColor rgb="FFE3A429"/>
-    <pageSetUpPr/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.0"/>
+  <dimension ref="A1:N1000"/>
+  <sheetFormatPr defaultColWidth="12.625" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="3.0"/>
-    <col customWidth="1" min="2" max="2" width="26.0"/>
-    <col customWidth="1" min="3" max="3" width="18.0"/>
-    <col customWidth="1" min="4" max="4" width="17.0"/>
-    <col customWidth="1" min="5" max="6" width="18.0"/>
-    <col customWidth="1" min="7" max="7" width="3.0"/>
-    <col customWidth="1" min="8" max="14" width="15.0"/>
-    <col customWidth="1" min="15" max="26" width="8.63"/>
+    <col min="1" max="1" width="3" customWidth="1"/>
+    <col min="2" max="2" width="26" customWidth="1"/>
+    <col min="3" max="3" width="18" customWidth="1"/>
+    <col min="4" max="4" width="17" customWidth="1"/>
+    <col min="5" max="6" width="18" customWidth="1"/>
+    <col min="7" max="7" width="3" customWidth="1"/>
+    <col min="8" max="14" width="15" customWidth="1"/>
+    <col min="15" max="26" width="8.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="27.75" customHeight="1">
-      <c r="A1" s="12"/>
-      <c r="B1" s="13" t="s">
+    <row r="1" spans="1:14" ht="27.75" customHeight="1">
+      <c r="A1" s="9"/>
+      <c r="B1" s="17" t="s">
         <v>160</v>
       </c>
-    </row>
-    <row r="2" ht="27.75" customHeight="1">
-      <c r="A2" s="12"/>
-    </row>
-    <row r="3" ht="27.75" customHeight="1">
-      <c r="A3" s="12"/>
-      <c r="B3" s="2" t="s">
+      <c r="C1" s="18"/>
+      <c r="D1" s="18"/>
+      <c r="E1" s="18"/>
+      <c r="F1" s="18"/>
+      <c r="G1" s="18"/>
+      <c r="H1" s="18"/>
+      <c r="I1" s="18"/>
+      <c r="J1" s="18"/>
+      <c r="K1" s="18"/>
+      <c r="L1" s="18"/>
+      <c r="M1" s="18"/>
+      <c r="N1" s="18"/>
+    </row>
+    <row r="2" spans="1:14" ht="27.75" customHeight="1">
+      <c r="A2" s="9"/>
+      <c r="B2" s="18"/>
+      <c r="C2" s="18"/>
+      <c r="D2" s="18"/>
+      <c r="E2" s="18"/>
+      <c r="F2" s="18"/>
+      <c r="G2" s="18"/>
+      <c r="H2" s="18"/>
+      <c r="I2" s="18"/>
+      <c r="J2" s="18"/>
+      <c r="K2" s="18"/>
+      <c r="L2" s="18"/>
+      <c r="M2" s="18"/>
+      <c r="N2" s="18"/>
+    </row>
+    <row r="3" spans="1:14" ht="27.75" customHeight="1">
+      <c r="A3" s="9"/>
+      <c r="B3" s="19" t="s">
         <v>161</v>
       </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="12"/>
-      <c r="B4" s="12"/>
-      <c r="C4" s="12"/>
-      <c r="D4" s="12"/>
-      <c r="E4" s="12"/>
-      <c r="F4" s="12"/>
-      <c r="G4" s="12"/>
-      <c r="H4" s="12"/>
-      <c r="I4" s="12"/>
-      <c r="J4" s="12"/>
-      <c r="K4" s="12"/>
-      <c r="L4" s="12"/>
-      <c r="M4" s="12"/>
-      <c r="N4" s="12"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="12"/>
-      <c r="B5" s="14" t="s">
+      <c r="C3" s="18"/>
+      <c r="D3" s="18"/>
+      <c r="E3" s="18"/>
+      <c r="F3" s="18"/>
+      <c r="G3" s="18"/>
+      <c r="H3" s="18"/>
+      <c r="I3" s="18"/>
+      <c r="J3" s="18"/>
+      <c r="K3" s="18"/>
+      <c r="L3" s="18"/>
+      <c r="M3" s="18"/>
+      <c r="N3" s="18"/>
+    </row>
+    <row r="4" spans="1:14">
+      <c r="A4" s="9"/>
+      <c r="B4" s="9"/>
+      <c r="C4" s="9"/>
+      <c r="D4" s="9"/>
+      <c r="E4" s="9"/>
+      <c r="F4" s="9"/>
+      <c r="G4" s="9"/>
+      <c r="H4" s="9"/>
+      <c r="I4" s="9"/>
+      <c r="J4" s="9"/>
+      <c r="K4" s="9"/>
+      <c r="L4" s="9"/>
+      <c r="M4" s="9"/>
+      <c r="N4" s="9"/>
+    </row>
+    <row r="5" spans="1:14">
+      <c r="A5" s="9"/>
+      <c r="B5" s="20" t="s">
         <v>163</v>
       </c>
-      <c r="D5" s="14" t="s">
+      <c r="C5" s="18"/>
+      <c r="D5" s="20" t="s">
         <v>164</v>
       </c>
-      <c r="F5" s="14" t="s">
+      <c r="E5" s="18"/>
+      <c r="F5" s="20" t="s">
         <v>165</v>
       </c>
-      <c r="I5" s="14" t="s">
+      <c r="G5" s="18"/>
+      <c r="H5" s="18"/>
+      <c r="I5" s="20" t="s">
         <v>166</v>
       </c>
-      <c r="K5" s="14" t="s">
+      <c r="J5" s="18"/>
+      <c r="K5" s="20" t="s">
         <v>167</v>
       </c>
-      <c r="M5" s="14" t="s">
+      <c r="L5" s="18"/>
+      <c r="M5" s="20" t="s">
         <v>168</v>
       </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="12"/>
-      <c r="B6" s="15">
+      <c r="N5" s="18"/>
+    </row>
+    <row r="6" spans="1:14">
+      <c r="A6" s="9"/>
+      <c r="B6" s="21">
         <f>COUNTA('Test Scenarios'!$A$6:$A$24)</f>
         <v>19</v>
       </c>
-      <c r="D6" s="15">
+      <c r="C6" s="18"/>
+      <c r="D6" s="21">
         <f>COUNTA('Test Cases'!$B$6:$B$24)</f>
         <v>19</v>
       </c>
-      <c r="F6" s="16">
+      <c r="E6" s="18"/>
+      <c r="F6" s="23">
         <f>IFERROR(COUNTIF('Test Cases'!$L$6:$L$23,"Automated")/D6,0)</f>
-        <v>0.05263157895</v>
-      </c>
-      <c r="I6" s="15">
+        <v>0.10526315789473684</v>
+      </c>
+      <c r="G6" s="18"/>
+      <c r="H6" s="18"/>
+      <c r="I6" s="21">
         <f>COUNTIFS('Test Cases'!$M$6:$M$23,"Pass")</f>
-        <v>1</v>
-      </c>
-      <c r="K6" s="15">
+        <v>2</v>
+      </c>
+      <c r="J6" s="18"/>
+      <c r="K6" s="21">
         <f>COUNTIFS('Test Cases'!$M$6:$M$23,"Fail")</f>
         <v>0</v>
       </c>
-      <c r="M6" s="16">
+      <c r="L6" s="18"/>
+      <c r="M6" s="23">
         <f>IFERROR((COUNTIF('Test Cases'!$M$6:$M$23,"Pass")+COUNTIF('Test Cases'!$M$6:$M$23,"Fail")+COUNTIF('Test Cases'!$M$6:$M$23,"Blocked"))/D6,0)</f>
-        <v>0.05263157895</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="12"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="12"/>
-      <c r="B8" s="12"/>
-      <c r="C8" s="12"/>
-      <c r="D8" s="12"/>
-      <c r="E8" s="12"/>
-      <c r="F8" s="12"/>
-      <c r="G8" s="12"/>
-      <c r="H8" s="12"/>
-      <c r="I8" s="12"/>
-      <c r="J8" s="12"/>
-      <c r="K8" s="12"/>
-      <c r="L8" s="12"/>
-      <c r="M8" s="12"/>
-      <c r="N8" s="12"/>
-    </row>
-    <row r="9" ht="36.75" customHeight="1">
-      <c r="A9" s="12"/>
-      <c r="B9" s="17" t="s">
+        <v>0.10526315789473684</v>
+      </c>
+      <c r="N6" s="18"/>
+    </row>
+    <row r="7" spans="1:14">
+      <c r="A7" s="9"/>
+      <c r="B7" s="18"/>
+      <c r="C7" s="18"/>
+      <c r="D7" s="18"/>
+      <c r="E7" s="18"/>
+      <c r="F7" s="18"/>
+      <c r="G7" s="18"/>
+      <c r="H7" s="18"/>
+      <c r="I7" s="18"/>
+      <c r="J7" s="18"/>
+      <c r="K7" s="18"/>
+      <c r="L7" s="18"/>
+      <c r="M7" s="18"/>
+      <c r="N7" s="18"/>
+    </row>
+    <row r="8" spans="1:14">
+      <c r="A8" s="9"/>
+      <c r="B8" s="9"/>
+      <c r="C8" s="9"/>
+      <c r="D8" s="9"/>
+      <c r="E8" s="9"/>
+      <c r="F8" s="9"/>
+      <c r="G8" s="9"/>
+      <c r="H8" s="9"/>
+      <c r="I8" s="9"/>
+      <c r="J8" s="9"/>
+      <c r="K8" s="9"/>
+      <c r="L8" s="9"/>
+      <c r="M8" s="9"/>
+      <c r="N8" s="9"/>
+    </row>
+    <row r="9" spans="1:14" ht="36.75" customHeight="1">
+      <c r="A9" s="9"/>
+      <c r="B9" s="24" t="s">
         <v>179</v>
       </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="12"/>
-      <c r="B10" s="12"/>
-      <c r="C10" s="12"/>
-      <c r="D10" s="12"/>
-      <c r="E10" s="12"/>
-      <c r="F10" s="12"/>
-      <c r="G10" s="12"/>
-      <c r="H10" s="12"/>
-      <c r="I10" s="12"/>
-      <c r="J10" s="12"/>
-      <c r="K10" s="12"/>
-      <c r="L10" s="12"/>
-      <c r="M10" s="12"/>
-      <c r="N10" s="12"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="12"/>
-      <c r="B11" s="12"/>
-      <c r="C11" s="12"/>
-      <c r="D11" s="12"/>
-      <c r="E11" s="12"/>
-      <c r="F11" s="12"/>
-      <c r="G11" s="12"/>
-      <c r="H11" s="12"/>
-      <c r="I11" s="12"/>
-      <c r="J11" s="12"/>
-      <c r="K11" s="12"/>
-      <c r="L11" s="12"/>
-      <c r="M11" s="12"/>
-      <c r="N11" s="12"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="12"/>
-      <c r="B12" s="18" t="s">
+      <c r="C9" s="18"/>
+      <c r="D9" s="18"/>
+      <c r="E9" s="18"/>
+      <c r="F9" s="18"/>
+      <c r="G9" s="18"/>
+      <c r="H9" s="18"/>
+      <c r="I9" s="18"/>
+      <c r="J9" s="18"/>
+      <c r="K9" s="18"/>
+      <c r="L9" s="18"/>
+      <c r="M9" s="18"/>
+      <c r="N9" s="18"/>
+    </row>
+    <row r="10" spans="1:14">
+      <c r="A10" s="9"/>
+      <c r="B10" s="9"/>
+      <c r="C10" s="9"/>
+      <c r="D10" s="9"/>
+      <c r="E10" s="9"/>
+      <c r="F10" s="9"/>
+      <c r="G10" s="9"/>
+      <c r="H10" s="9"/>
+      <c r="I10" s="9"/>
+      <c r="J10" s="9"/>
+      <c r="K10" s="9"/>
+      <c r="L10" s="9"/>
+      <c r="M10" s="9"/>
+      <c r="N10" s="9"/>
+    </row>
+    <row r="11" spans="1:14">
+      <c r="A11" s="9"/>
+      <c r="B11" s="9"/>
+      <c r="C11" s="9"/>
+      <c r="D11" s="9"/>
+      <c r="E11" s="9"/>
+      <c r="F11" s="9"/>
+      <c r="G11" s="9"/>
+      <c r="H11" s="9"/>
+      <c r="I11" s="9"/>
+      <c r="J11" s="9"/>
+      <c r="K11" s="9"/>
+      <c r="L11" s="9"/>
+      <c r="M11" s="9"/>
+      <c r="N11" s="9"/>
+    </row>
+    <row r="12" spans="1:14">
+      <c r="A12" s="9"/>
+      <c r="B12" s="22" t="s">
         <v>181</v>
       </c>
-      <c r="G12" s="12"/>
-      <c r="H12" s="12"/>
-      <c r="I12" s="12"/>
-      <c r="J12" s="12"/>
-      <c r="K12" s="12"/>
-      <c r="L12" s="12"/>
-      <c r="M12" s="12"/>
-      <c r="N12" s="12"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="12"/>
-      <c r="B13" s="19" t="s">
+      <c r="C12" s="18"/>
+      <c r="D12" s="18"/>
+      <c r="E12" s="18"/>
+      <c r="F12" s="18"/>
+      <c r="G12" s="9"/>
+      <c r="H12" s="9"/>
+      <c r="I12" s="9"/>
+      <c r="J12" s="9"/>
+      <c r="K12" s="9"/>
+      <c r="L12" s="9"/>
+      <c r="M12" s="9"/>
+      <c r="N12" s="9"/>
+    </row>
+    <row r="13" spans="1:14">
+      <c r="A13" s="9"/>
+      <c r="B13" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="C13" s="19" t="s">
+      <c r="C13" s="10" t="s">
         <v>184</v>
       </c>
-      <c r="D13" s="19" t="s">
+      <c r="D13" s="10" t="s">
         <v>53</v>
       </c>
-      <c r="E13" s="19" t="s">
+      <c r="E13" s="10" t="s">
         <v>185</v>
       </c>
-      <c r="F13" s="19" t="s">
+      <c r="F13" s="10" t="s">
         <v>186</v>
       </c>
-      <c r="G13" s="12"/>
-      <c r="H13" s="12"/>
-      <c r="I13" s="12"/>
-      <c r="J13" s="12"/>
-      <c r="K13" s="12"/>
-      <c r="L13" s="12"/>
-      <c r="M13" s="12"/>
-      <c r="N13" s="12"/>
-    </row>
-    <row r="14" ht="27.0" customHeight="1">
-      <c r="A14" s="12"/>
-      <c r="B14" s="20" t="s">
+      <c r="G13" s="9"/>
+      <c r="H13" s="9"/>
+      <c r="I13" s="9"/>
+      <c r="J13" s="9"/>
+      <c r="K13" s="9"/>
+      <c r="L13" s="9"/>
+      <c r="M13" s="9"/>
+      <c r="N13" s="9"/>
+    </row>
+    <row r="14" spans="1:14" ht="27" customHeight="1">
+      <c r="A14" s="9"/>
+      <c r="B14" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="C14" s="20">
+      <c r="C14" s="11">
         <f>COUNTIFS('Test Cases'!$K$6:$K$23,B14)</f>
         <v>5</v>
       </c>
-      <c r="D14" s="20">
+      <c r="D14" s="11">
         <f>COUNTIFS('Test Cases'!$K$6:$K$23,B14,'Test Cases'!$L$6:$L$23,"Automated")</f>
-        <v>1</v>
-      </c>
-      <c r="E14" s="20">
+        <v>2</v>
+      </c>
+      <c r="E14" s="11">
         <f>COUNTIFS('Test Cases'!$K$6:$K$23,B14,'Test Cases'!$M$6:$M$23,"Pass")</f>
-        <v>1</v>
-      </c>
-      <c r="F14" s="21">
-        <f t="shared" ref="F14:F17" si="1">IFERROR(D14/C14,0)</f>
-        <v>0.2</v>
-      </c>
-      <c r="G14" s="12"/>
-      <c r="H14" s="12"/>
-      <c r="I14" s="12"/>
-      <c r="J14" s="12"/>
-      <c r="K14" s="12"/>
-      <c r="L14" s="12"/>
-      <c r="M14" s="12"/>
-      <c r="N14" s="12"/>
-    </row>
-    <row r="15" ht="27.0" customHeight="1">
-      <c r="A15" s="12"/>
-      <c r="B15" s="20" t="s">
+        <v>2</v>
+      </c>
+      <c r="F14" s="12">
+        <f t="shared" ref="F14:F17" si="0">IFERROR(D14/C14,0)</f>
+        <v>0.4</v>
+      </c>
+      <c r="G14" s="9"/>
+      <c r="H14" s="9"/>
+      <c r="I14" s="9"/>
+      <c r="J14" s="9"/>
+      <c r="K14" s="9"/>
+      <c r="L14" s="9"/>
+      <c r="M14" s="9"/>
+      <c r="N14" s="9"/>
+    </row>
+    <row r="15" spans="1:14" ht="27" customHeight="1">
+      <c r="A15" s="9"/>
+      <c r="B15" s="11" t="s">
         <v>40</v>
       </c>
-      <c r="C15" s="20">
+      <c r="C15" s="11">
         <f>COUNTIFS('Test Cases'!$K$6:$K$23,B15)</f>
         <v>5</v>
       </c>
-      <c r="D15" s="20">
+      <c r="D15" s="11">
         <f>COUNTIFS('Test Cases'!$K$6:$K$23,B15,'Test Cases'!$L$6:$L$23,"Automated")</f>
         <v>0</v>
       </c>
-      <c r="E15" s="20">
+      <c r="E15" s="11">
         <f>COUNTIFS('Test Cases'!$K$6:$K$23,B15,'Test Cases'!$M$6:$M$23,"Pass")</f>
         <v>0</v>
       </c>
-      <c r="F15" s="21">
+      <c r="F15" s="12">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G15" s="9"/>
+      <c r="H15" s="9"/>
+      <c r="I15" s="9"/>
+      <c r="J15" s="9"/>
+      <c r="K15" s="9"/>
+      <c r="L15" s="9"/>
+      <c r="M15" s="9"/>
+      <c r="N15" s="9"/>
+    </row>
+    <row r="16" spans="1:14" ht="27" customHeight="1">
+      <c r="A16" s="9"/>
+      <c r="B16" s="11" t="s">
+        <v>84</v>
+      </c>
+      <c r="C16" s="11">
+        <f>COUNTIFS('Test Cases'!$K$6:$K$23,B16)</f>
+        <v>4</v>
+      </c>
+      <c r="D16" s="11">
+        <f>COUNTIFS('Test Cases'!$K$6:$K$23,B16,'Test Cases'!$L$6:$L$23,"Automated")</f>
+        <v>0</v>
+      </c>
+      <c r="E16" s="11">
+        <f>COUNTIFS('Test Cases'!$K$6:$K$23,B16,'Test Cases'!$M$6:$M$23,"Pass")</f>
+        <v>0</v>
+      </c>
+      <c r="F16" s="12">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G16" s="9"/>
+      <c r="H16" s="9"/>
+      <c r="I16" s="9"/>
+      <c r="J16" s="9"/>
+      <c r="K16" s="9"/>
+      <c r="L16" s="9"/>
+      <c r="M16" s="9"/>
+      <c r="N16" s="9"/>
+    </row>
+    <row r="17" spans="1:14" ht="27" customHeight="1">
+      <c r="A17" s="9"/>
+      <c r="B17" s="11" t="s">
+        <v>107</v>
+      </c>
+      <c r="C17" s="11">
+        <f>COUNTIFS('Test Cases'!$K$6:$K$23,B17)</f>
+        <v>4</v>
+      </c>
+      <c r="D17" s="11">
+        <f>COUNTIFS('Test Cases'!$K$6:$K$23,B17,'Test Cases'!$L$6:$L$23,"Automated")</f>
+        <v>0</v>
+      </c>
+      <c r="E17" s="11">
+        <f>COUNTIFS('Test Cases'!$K$6:$K$23,B17,'Test Cases'!$M$6:$M$23,"Pass")</f>
+        <v>0</v>
+      </c>
+      <c r="F17" s="12">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G17" s="9"/>
+      <c r="H17" s="9"/>
+      <c r="I17" s="9"/>
+      <c r="J17" s="9"/>
+      <c r="K17" s="9"/>
+      <c r="L17" s="9"/>
+      <c r="M17" s="9"/>
+      <c r="N17" s="9"/>
+    </row>
+    <row r="18" spans="1:14">
+      <c r="A18" s="9"/>
+      <c r="B18" s="9"/>
+      <c r="C18" s="9"/>
+      <c r="D18" s="9"/>
+      <c r="E18" s="9"/>
+      <c r="F18" s="9"/>
+      <c r="G18" s="9"/>
+      <c r="H18" s="9"/>
+      <c r="I18" s="9"/>
+      <c r="J18" s="9"/>
+      <c r="K18" s="9"/>
+      <c r="L18" s="9"/>
+      <c r="M18" s="9"/>
+      <c r="N18" s="9"/>
+    </row>
+    <row r="19" spans="1:14">
+      <c r="A19" s="9"/>
+      <c r="B19" s="9"/>
+      <c r="C19" s="9"/>
+      <c r="D19" s="9"/>
+      <c r="E19" s="9"/>
+      <c r="F19" s="9"/>
+      <c r="G19" s="9"/>
+      <c r="H19" s="9"/>
+      <c r="I19" s="9"/>
+      <c r="J19" s="9"/>
+      <c r="K19" s="9"/>
+      <c r="L19" s="9"/>
+      <c r="M19" s="9"/>
+      <c r="N19" s="9"/>
+    </row>
+    <row r="20" spans="1:14">
+      <c r="A20" s="9"/>
+      <c r="B20" s="22" t="s">
+        <v>196</v>
+      </c>
+      <c r="C20" s="18"/>
+      <c r="D20" s="18"/>
+      <c r="E20" s="18"/>
+      <c r="F20" s="18"/>
+      <c r="G20" s="9"/>
+      <c r="H20" s="9"/>
+      <c r="I20" s="9"/>
+      <c r="J20" s="9"/>
+      <c r="K20" s="9"/>
+      <c r="L20" s="9"/>
+      <c r="M20" s="9"/>
+      <c r="N20" s="9"/>
+    </row>
+    <row r="21" spans="1:14" ht="15.75" customHeight="1">
+      <c r="A21" s="9"/>
+      <c r="B21" s="13" t="s">
+        <v>198</v>
+      </c>
+      <c r="C21" s="13" t="s">
+        <v>199</v>
+      </c>
+      <c r="D21" s="9"/>
+      <c r="E21" s="13" t="s">
+        <v>26</v>
+      </c>
+      <c r="F21" s="13" t="s">
+        <v>199</v>
+      </c>
+      <c r="G21" s="9"/>
+      <c r="H21" s="9"/>
+      <c r="I21" s="9"/>
+      <c r="J21" s="9"/>
+      <c r="K21" s="9"/>
+      <c r="L21" s="9"/>
+      <c r="M21" s="9"/>
+      <c r="N21" s="9"/>
+    </row>
+    <row r="22" spans="1:14" ht="15.75" customHeight="1">
+      <c r="A22" s="9"/>
+      <c r="B22" s="11" t="s">
+        <v>79</v>
+      </c>
+      <c r="C22" s="11">
+        <f>COUNTIFS('Test Cases'!$L$6:$L$24,B22)</f>
+        <v>16</v>
+      </c>
+      <c r="D22" s="9"/>
+      <c r="E22" s="11" t="s">
+        <v>82</v>
+      </c>
+      <c r="F22" s="11">
+        <f>COUNTIFS('Test Cases'!$M$6:$M$23,E22)</f>
+        <v>16</v>
+      </c>
+      <c r="G22" s="9"/>
+      <c r="H22" s="9"/>
+      <c r="I22" s="9"/>
+      <c r="J22" s="9"/>
+      <c r="K22" s="9"/>
+      <c r="L22" s="9"/>
+      <c r="M22" s="9"/>
+      <c r="N22" s="9"/>
+    </row>
+    <row r="23" spans="1:14" ht="15.75" customHeight="1">
+      <c r="A23" s="9"/>
+      <c r="B23" s="11" t="s">
+        <v>201</v>
+      </c>
+      <c r="C23" s="11">
+        <f>COUNTIFS('Test Cases'!$L$6:$L$23,B23)</f>
+        <v>0</v>
+      </c>
+      <c r="D23" s="9"/>
+      <c r="E23" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="F23" s="11">
+        <f>COUNTIFS('Test Cases'!$M$6:$M$23,E23)</f>
+        <v>2</v>
+      </c>
+      <c r="G23" s="9"/>
+      <c r="H23" s="9"/>
+      <c r="I23" s="9"/>
+      <c r="J23" s="9"/>
+      <c r="K23" s="9"/>
+      <c r="L23" s="9"/>
+      <c r="M23" s="9"/>
+      <c r="N23" s="9"/>
+    </row>
+    <row r="24" spans="1:14" ht="15.75" customHeight="1">
+      <c r="A24" s="9"/>
+      <c r="B24" s="11" t="s">
+        <v>53</v>
+      </c>
+      <c r="C24" s="11">
+        <f>COUNTIFS('Test Cases'!$L$6:$L$23,B24)</f>
+        <v>2</v>
+      </c>
+      <c r="D24" s="9"/>
+      <c r="E24" s="11" t="s">
+        <v>203</v>
+      </c>
+      <c r="F24" s="11">
+        <f>COUNTIFS('Test Cases'!$M$6:$M$23,E24)</f>
+        <v>0</v>
+      </c>
+      <c r="G24" s="9"/>
+      <c r="H24" s="9"/>
+      <c r="I24" s="9"/>
+      <c r="J24" s="9"/>
+      <c r="K24" s="9"/>
+      <c r="L24" s="9"/>
+      <c r="M24" s="9"/>
+      <c r="N24" s="9"/>
+    </row>
+    <row r="25" spans="1:14" ht="15.75" customHeight="1">
+      <c r="A25" s="9"/>
+      <c r="B25" s="11" t="s">
+        <v>204</v>
+      </c>
+      <c r="C25" s="11">
+        <f>COUNTIFS('Test Cases'!$L$6:$L$23,B25)</f>
+        <v>0</v>
+      </c>
+      <c r="D25" s="9"/>
+      <c r="E25" s="11" t="s">
+        <v>206</v>
+      </c>
+      <c r="F25" s="11">
+        <f>COUNTIFS('Test Cases'!$M$6:$M$23,E25)</f>
+        <v>0</v>
+      </c>
+      <c r="G25" s="9"/>
+      <c r="H25" s="9"/>
+      <c r="I25" s="9"/>
+      <c r="J25" s="9"/>
+      <c r="K25" s="9"/>
+      <c r="L25" s="9"/>
+      <c r="M25" s="9"/>
+      <c r="N25" s="9"/>
+    </row>
+    <row r="26" spans="1:14" ht="15.75" customHeight="1">
+      <c r="A26" s="9"/>
+      <c r="B26" s="9"/>
+      <c r="C26" s="9"/>
+      <c r="D26" s="9"/>
+      <c r="E26" s="9"/>
+      <c r="F26" s="9"/>
+      <c r="G26" s="9"/>
+      <c r="H26" s="9"/>
+      <c r="I26" s="9"/>
+      <c r="J26" s="9"/>
+      <c r="K26" s="9"/>
+      <c r="L26" s="9"/>
+      <c r="M26" s="9"/>
+      <c r="N26" s="9"/>
+    </row>
+    <row r="27" spans="1:14" ht="15.75" customHeight="1">
+      <c r="A27" s="9"/>
+      <c r="B27" s="9"/>
+      <c r="C27" s="9"/>
+      <c r="D27" s="9"/>
+      <c r="E27" s="9"/>
+      <c r="F27" s="9"/>
+      <c r="G27" s="9"/>
+      <c r="H27" s="9"/>
+      <c r="I27" s="9"/>
+      <c r="J27" s="9"/>
+      <c r="K27" s="9"/>
+      <c r="L27" s="9"/>
+      <c r="M27" s="9"/>
+      <c r="N27" s="9"/>
+    </row>
+    <row r="28" spans="1:14" ht="15.75" customHeight="1">
+      <c r="A28" s="9"/>
+      <c r="B28" s="22" t="s">
+        <v>210</v>
+      </c>
+      <c r="C28" s="18"/>
+      <c r="D28" s="18"/>
+      <c r="E28" s="18"/>
+      <c r="F28" s="18"/>
+      <c r="G28" s="9"/>
+      <c r="H28" s="9"/>
+      <c r="I28" s="9"/>
+      <c r="J28" s="9"/>
+      <c r="K28" s="9"/>
+      <c r="L28" s="9"/>
+      <c r="M28" s="9"/>
+      <c r="N28" s="9"/>
+    </row>
+    <row r="29" spans="1:14" ht="15.75" customHeight="1">
+      <c r="A29" s="9"/>
+      <c r="B29" s="13" t="s">
+        <v>211</v>
+      </c>
+      <c r="C29" s="13" t="s">
+        <v>184</v>
+      </c>
+      <c r="D29" s="13" t="s">
+        <v>53</v>
+      </c>
+      <c r="E29" s="13" t="s">
+        <v>185</v>
+      </c>
+      <c r="F29" s="13" t="s">
+        <v>186</v>
+      </c>
+      <c r="G29" s="9"/>
+      <c r="H29" s="9"/>
+      <c r="I29" s="9"/>
+      <c r="J29" s="9"/>
+      <c r="K29" s="9"/>
+      <c r="L29" s="9"/>
+      <c r="M29" s="9"/>
+      <c r="N29" s="9"/>
+    </row>
+    <row r="30" spans="1:14" ht="25.5" customHeight="1">
+      <c r="A30" s="9"/>
+      <c r="B30" s="14" t="str">
+        <f>'Test Scenarios'!B6</f>
+        <v>Input Fields</v>
+      </c>
+      <c r="C30" s="14">
+        <f>COUNTIFS('Test Cases'!$D$6:$D$23,B30)</f>
+        <v>1</v>
+      </c>
+      <c r="D30" s="14">
+        <f>COUNTIFS('Test Cases'!$D$6:$D$23,B30,'Test Cases'!$L$6:$L$23,"Automated")</f>
+        <v>1</v>
+      </c>
+      <c r="E30" s="14">
+        <f>COUNTIFS('Test Cases'!$D$6:$D$23,B30,'Test Cases'!$M$6:$M$23,"Pass")</f>
+        <v>1</v>
+      </c>
+      <c r="F30" s="15">
+        <f t="shared" ref="F30:F47" si="1">IFERROR(D30/C30,0)</f>
+        <v>1</v>
+      </c>
+      <c r="G30" s="9"/>
+      <c r="H30" s="9"/>
+      <c r="I30" s="9"/>
+      <c r="J30" s="9"/>
+      <c r="K30" s="9"/>
+      <c r="L30" s="9"/>
+      <c r="M30" s="9"/>
+      <c r="N30" s="9"/>
+    </row>
+    <row r="31" spans="1:14" ht="25.5" customHeight="1">
+      <c r="A31" s="9"/>
+      <c r="B31" s="14" t="str">
+        <f>'Test Scenarios'!B7</f>
+        <v>Buttons</v>
+      </c>
+      <c r="C31" s="14">
+        <f>COUNTIFS('Test Cases'!$D$6:$D$23,B31)</f>
+        <v>1</v>
+      </c>
+      <c r="D31" s="14">
+        <f>COUNTIFS('Test Cases'!$D$6:$D$23,B31,'Test Cases'!$L$6:$L$23,"Automated")</f>
+        <v>1</v>
+      </c>
+      <c r="E31" s="14">
+        <f>COUNTIFS('Test Cases'!$D$6:$D$23,B31,'Test Cases'!$M$6:$M$23,"Pass")</f>
+        <v>1</v>
+      </c>
+      <c r="F31" s="15">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="G31" s="9"/>
+      <c r="H31" s="9"/>
+      <c r="I31" s="9"/>
+      <c r="J31" s="9"/>
+      <c r="K31" s="9"/>
+      <c r="L31" s="9"/>
+      <c r="M31" s="9"/>
+      <c r="N31" s="9"/>
+    </row>
+    <row r="32" spans="1:14" ht="25.5" customHeight="1">
+      <c r="A32" s="9"/>
+      <c r="B32" s="14" t="str">
+        <f>'Test Scenarios'!B8</f>
+        <v>Forms</v>
+      </c>
+      <c r="C32" s="14">
+        <f>COUNTIFS('Test Cases'!$D$6:$D$23,B32)</f>
+        <v>1</v>
+      </c>
+      <c r="D32" s="14">
+        <f>COUNTIFS('Test Cases'!$D$6:$D$23,B32,'Test Cases'!$L$6:$L$23,"Automated")</f>
+        <v>0</v>
+      </c>
+      <c r="E32" s="14">
+        <f>COUNTIFS('Test Cases'!$D$6:$D$23,B32,'Test Cases'!$M$6:$M$23,"Pass")</f>
+        <v>0</v>
+      </c>
+      <c r="F32" s="15">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="G15" s="12"/>
-      <c r="H15" s="12"/>
-      <c r="I15" s="12"/>
-      <c r="J15" s="12"/>
-      <c r="K15" s="12"/>
-      <c r="L15" s="12"/>
-      <c r="M15" s="12"/>
-      <c r="N15" s="12"/>
-    </row>
-    <row r="16" ht="27.0" customHeight="1">
-      <c r="A16" s="12"/>
-      <c r="B16" s="20" t="s">
-        <v>84</v>
-      </c>
-      <c r="C16" s="20">
-        <f>COUNTIFS('Test Cases'!$K$6:$K$23,B16)</f>
-        <v>4</v>
-      </c>
-      <c r="D16" s="20">
-        <f>COUNTIFS('Test Cases'!$K$6:$K$23,B16,'Test Cases'!$L$6:$L$23,"Automated")</f>
+      <c r="G32" s="9"/>
+      <c r="H32" s="9"/>
+      <c r="I32" s="9"/>
+      <c r="J32" s="9"/>
+      <c r="K32" s="9"/>
+      <c r="L32" s="9"/>
+      <c r="M32" s="9"/>
+      <c r="N32" s="9"/>
+    </row>
+    <row r="33" spans="1:14" ht="25.5" customHeight="1">
+      <c r="A33" s="9"/>
+      <c r="B33" s="14" t="str">
+        <f>'Test Scenarios'!B9</f>
+        <v>Dropdowns</v>
+      </c>
+      <c r="C33" s="14">
+        <f>COUNTIFS('Test Cases'!$D$6:$D$23,B33)</f>
+        <v>1</v>
+      </c>
+      <c r="D33" s="14">
+        <f>COUNTIFS('Test Cases'!$D$6:$D$23,B33,'Test Cases'!$L$6:$L$23,"Automated")</f>
         <v>0</v>
       </c>
-      <c r="E16" s="20">
-        <f>COUNTIFS('Test Cases'!$K$6:$K$23,B16,'Test Cases'!$M$6:$M$23,"Pass")</f>
+      <c r="E33" s="14">
+        <f>COUNTIFS('Test Cases'!$D$6:$D$23,B33,'Test Cases'!$M$6:$M$23,"Pass")</f>
         <v>0</v>
       </c>
-      <c r="F16" s="21">
+      <c r="F33" s="15">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="G16" s="12"/>
-      <c r="H16" s="12"/>
-      <c r="I16" s="12"/>
-      <c r="J16" s="12"/>
-      <c r="K16" s="12"/>
-      <c r="L16" s="12"/>
-      <c r="M16" s="12"/>
-      <c r="N16" s="12"/>
-    </row>
-    <row r="17" ht="27.0" customHeight="1">
-      <c r="A17" s="12"/>
-      <c r="B17" s="20" t="s">
-        <v>107</v>
-      </c>
-      <c r="C17" s="20">
-        <f>COUNTIFS('Test Cases'!$K$6:$K$23,B17)</f>
-        <v>4</v>
-      </c>
-      <c r="D17" s="20">
-        <f>COUNTIFS('Test Cases'!$K$6:$K$23,B17,'Test Cases'!$L$6:$L$23,"Automated")</f>
+      <c r="G33" s="9"/>
+      <c r="H33" s="9"/>
+      <c r="I33" s="9"/>
+      <c r="J33" s="9"/>
+      <c r="K33" s="9"/>
+      <c r="L33" s="9"/>
+      <c r="M33" s="9"/>
+      <c r="N33" s="9"/>
+    </row>
+    <row r="34" spans="1:14" ht="25.5" customHeight="1">
+      <c r="A34" s="9"/>
+      <c r="B34" s="14" t="str">
+        <f>'Test Scenarios'!B10</f>
+        <v>Data Table</v>
+      </c>
+      <c r="C34" s="14">
+        <f>COUNTIFS('Test Cases'!$D$6:$D$23,B34)</f>
+        <v>1</v>
+      </c>
+      <c r="D34" s="14">
+        <f>COUNTIFS('Test Cases'!$D$6:$D$23,B34,'Test Cases'!$L$6:$L$23,"Automated")</f>
         <v>0</v>
       </c>
-      <c r="E17" s="20">
-        <f>COUNTIFS('Test Cases'!$K$6:$K$23,B17,'Test Cases'!$M$6:$M$23,"Pass")</f>
+      <c r="E34" s="14">
+        <f>COUNTIFS('Test Cases'!$D$6:$D$23,B34,'Test Cases'!$M$6:$M$23,"Pass")</f>
         <v>0</v>
       </c>
-      <c r="F17" s="21">
+      <c r="F34" s="15">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="G17" s="12"/>
-      <c r="H17" s="12"/>
-      <c r="I17" s="12"/>
-      <c r="J17" s="12"/>
-      <c r="K17" s="12"/>
-      <c r="L17" s="12"/>
-      <c r="M17" s="12"/>
-      <c r="N17" s="12"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="12"/>
-      <c r="B18" s="12"/>
-      <c r="C18" s="12"/>
-      <c r="D18" s="12"/>
-      <c r="E18" s="12"/>
-      <c r="F18" s="12"/>
-      <c r="G18" s="12"/>
-      <c r="H18" s="12"/>
-      <c r="I18" s="12"/>
-      <c r="J18" s="12"/>
-      <c r="K18" s="12"/>
-      <c r="L18" s="12"/>
-      <c r="M18" s="12"/>
-      <c r="N18" s="12"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="12"/>
-      <c r="B19" s="12"/>
-      <c r="C19" s="12"/>
-      <c r="D19" s="12"/>
-      <c r="E19" s="12"/>
-      <c r="F19" s="12"/>
-      <c r="G19" s="12"/>
-      <c r="H19" s="12"/>
-      <c r="I19" s="12"/>
-      <c r="J19" s="12"/>
-      <c r="K19" s="12"/>
-      <c r="L19" s="12"/>
-      <c r="M19" s="12"/>
-      <c r="N19" s="12"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="12"/>
-      <c r="B20" s="18" t="s">
-        <v>196</v>
-      </c>
-      <c r="G20" s="12"/>
-      <c r="H20" s="12"/>
-      <c r="I20" s="12"/>
-      <c r="J20" s="12"/>
-      <c r="K20" s="12"/>
-      <c r="L20" s="12"/>
-      <c r="M20" s="12"/>
-      <c r="N20" s="12"/>
-    </row>
-    <row r="21" ht="15.75" customHeight="1">
-      <c r="A21" s="12"/>
-      <c r="B21" s="22" t="s">
-        <v>198</v>
-      </c>
-      <c r="C21" s="22" t="s">
-        <v>199</v>
-      </c>
-      <c r="D21" s="12"/>
-      <c r="E21" s="22" t="s">
-        <v>26</v>
-      </c>
-      <c r="F21" s="22" t="s">
-        <v>199</v>
-      </c>
-      <c r="G21" s="12"/>
-      <c r="H21" s="12"/>
-      <c r="I21" s="12"/>
-      <c r="J21" s="12"/>
-      <c r="K21" s="12"/>
-      <c r="L21" s="12"/>
-      <c r="M21" s="12"/>
-      <c r="N21" s="12"/>
-    </row>
-    <row r="22" ht="15.75" customHeight="1">
-      <c r="A22" s="12"/>
-      <c r="B22" s="20" t="s">
-        <v>79</v>
-      </c>
-      <c r="C22" s="20">
-        <f>COUNTIFS('Test Cases'!$L$6:$L$24,B22)</f>
-        <v>17</v>
-      </c>
-      <c r="D22" s="12"/>
-      <c r="E22" s="20" t="s">
-        <v>82</v>
-      </c>
-      <c r="F22" s="20">
-        <f>COUNTIFS('Test Cases'!$M$6:$M$23,E22)</f>
-        <v>17</v>
-      </c>
-      <c r="G22" s="12"/>
-      <c r="H22" s="12"/>
-      <c r="I22" s="12"/>
-      <c r="J22" s="12"/>
-      <c r="K22" s="12"/>
-      <c r="L22" s="12"/>
-      <c r="M22" s="12"/>
-      <c r="N22" s="12"/>
-    </row>
-    <row r="23" ht="15.75" customHeight="1">
-      <c r="A23" s="12"/>
-      <c r="B23" s="20" t="s">
-        <v>201</v>
-      </c>
-      <c r="C23" s="20">
-        <f>COUNTIFS('Test Cases'!$L$6:$L$23,B23)</f>
-        <v>0</v>
-      </c>
-      <c r="D23" s="12"/>
-      <c r="E23" s="20" t="s">
-        <v>56</v>
-      </c>
-      <c r="F23" s="20">
-        <f>COUNTIFS('Test Cases'!$M$6:$M$23,E23)</f>
-        <v>1</v>
-      </c>
-      <c r="G23" s="12"/>
-      <c r="H23" s="12"/>
-      <c r="I23" s="12"/>
-      <c r="J23" s="12"/>
-      <c r="K23" s="12"/>
-      <c r="L23" s="12"/>
-      <c r="M23" s="12"/>
-      <c r="N23" s="12"/>
-    </row>
-    <row r="24" ht="15.75" customHeight="1">
-      <c r="A24" s="12"/>
-      <c r="B24" s="20" t="s">
-        <v>53</v>
-      </c>
-      <c r="C24" s="20">
-        <f>COUNTIFS('Test Cases'!$L$6:$L$23,B24)</f>
-        <v>1</v>
-      </c>
-      <c r="D24" s="12"/>
-      <c r="E24" s="20" t="s">
-        <v>203</v>
-      </c>
-      <c r="F24" s="20">
-        <f>COUNTIFS('Test Cases'!$M$6:$M$23,E24)</f>
-        <v>0</v>
-      </c>
-      <c r="G24" s="12"/>
-      <c r="H24" s="12"/>
-      <c r="I24" s="12"/>
-      <c r="J24" s="12"/>
-      <c r="K24" s="12"/>
-      <c r="L24" s="12"/>
-      <c r="M24" s="12"/>
-      <c r="N24" s="12"/>
-    </row>
-    <row r="25" ht="15.75" customHeight="1">
-      <c r="A25" s="12"/>
-      <c r="B25" s="20" t="s">
-        <v>204</v>
-      </c>
-      <c r="C25" s="20">
-        <f>COUNTIFS('Test Cases'!$L$6:$L$23,B25)</f>
-        <v>0</v>
-      </c>
-      <c r="D25" s="12"/>
-      <c r="E25" s="20" t="s">
-        <v>206</v>
-      </c>
-      <c r="F25" s="20">
-        <f>COUNTIFS('Test Cases'!$M$6:$M$23,E25)</f>
-        <v>0</v>
-      </c>
-      <c r="G25" s="12"/>
-      <c r="H25" s="12"/>
-      <c r="I25" s="12"/>
-      <c r="J25" s="12"/>
-      <c r="K25" s="12"/>
-      <c r="L25" s="12"/>
-      <c r="M25" s="12"/>
-      <c r="N25" s="12"/>
-    </row>
-    <row r="26" ht="15.75" customHeight="1">
-      <c r="A26" s="12"/>
-      <c r="B26" s="12"/>
-      <c r="C26" s="12"/>
-      <c r="D26" s="12"/>
-      <c r="E26" s="12"/>
-      <c r="F26" s="12"/>
-      <c r="G26" s="12"/>
-      <c r="H26" s="12"/>
-      <c r="I26" s="12"/>
-      <c r="J26" s="12"/>
-      <c r="K26" s="12"/>
-      <c r="L26" s="12"/>
-      <c r="M26" s="12"/>
-      <c r="N26" s="12"/>
-    </row>
-    <row r="27" ht="15.75" customHeight="1">
-      <c r="A27" s="12"/>
-      <c r="B27" s="12"/>
-      <c r="C27" s="12"/>
-      <c r="D27" s="12"/>
-      <c r="E27" s="12"/>
-      <c r="F27" s="12"/>
-      <c r="G27" s="12"/>
-      <c r="H27" s="12"/>
-      <c r="I27" s="12"/>
-      <c r="J27" s="12"/>
-      <c r="K27" s="12"/>
-      <c r="L27" s="12"/>
-      <c r="M27" s="12"/>
-      <c r="N27" s="12"/>
-    </row>
-    <row r="28" ht="15.75" customHeight="1">
-      <c r="A28" s="12"/>
-      <c r="B28" s="18" t="s">
-        <v>210</v>
-      </c>
-      <c r="G28" s="12"/>
-      <c r="H28" s="12"/>
-      <c r="I28" s="12"/>
-      <c r="J28" s="12"/>
-      <c r="K28" s="12"/>
-      <c r="L28" s="12"/>
-      <c r="M28" s="12"/>
-      <c r="N28" s="12"/>
-    </row>
-    <row r="29" ht="15.75" customHeight="1">
-      <c r="A29" s="12"/>
-      <c r="B29" s="22" t="s">
-        <v>211</v>
-      </c>
-      <c r="C29" s="22" t="s">
-        <v>184</v>
-      </c>
-      <c r="D29" s="22" t="s">
-        <v>53</v>
-      </c>
-      <c r="E29" s="22" t="s">
-        <v>185</v>
-      </c>
-      <c r="F29" s="22" t="s">
-        <v>186</v>
-      </c>
-      <c r="G29" s="12"/>
-      <c r="H29" s="12"/>
-      <c r="I29" s="12"/>
-      <c r="J29" s="12"/>
-      <c r="K29" s="12"/>
-      <c r="L29" s="12"/>
-      <c r="M29" s="12"/>
-      <c r="N29" s="12"/>
-    </row>
-    <row r="30" ht="25.5" customHeight="1">
-      <c r="A30" s="12"/>
-      <c r="B30" s="23" t="str">
-        <f>'Test Scenarios'!B6</f>
-        <v>Input Fields</v>
-      </c>
-      <c r="C30" s="23">
-        <f>COUNTIFS('Test Cases'!$D$6:$D$23,B30)</f>
-        <v>1</v>
-      </c>
-      <c r="D30" s="23">
-        <f>COUNTIFS('Test Cases'!$D$6:$D$23,B30,'Test Cases'!$L$6:$L$23,"Automated")</f>
-        <v>1</v>
-      </c>
-      <c r="E30" s="23">
-        <f>COUNTIFS('Test Cases'!$D$6:$D$23,B30,'Test Cases'!$M$6:$M$23,"Pass")</f>
-        <v>1</v>
-      </c>
-      <c r="F30" s="24">
-        <f t="shared" ref="F30:F47" si="2">IFERROR(D30/C30,0)</f>
-        <v>1</v>
-      </c>
-      <c r="G30" s="12"/>
-      <c r="H30" s="12"/>
-      <c r="I30" s="12"/>
-      <c r="J30" s="12"/>
-      <c r="K30" s="12"/>
-      <c r="L30" s="12"/>
-      <c r="M30" s="12"/>
-      <c r="N30" s="12"/>
-    </row>
-    <row r="31" ht="25.5" customHeight="1">
-      <c r="A31" s="12"/>
-      <c r="B31" s="23" t="str">
-        <f>'Test Scenarios'!B7</f>
-        <v>Buttons</v>
-      </c>
-      <c r="C31" s="23">
-        <f>COUNTIFS('Test Cases'!$D$6:$D$23,B31)</f>
-        <v>1</v>
-      </c>
-      <c r="D31" s="23">
-        <f>COUNTIFS('Test Cases'!$D$6:$D$23,B31,'Test Cases'!$L$6:$L$23,"Automated")</f>
-        <v>0</v>
-      </c>
-      <c r="E31" s="23">
-        <f>COUNTIFS('Test Cases'!$D$6:$D$23,B31,'Test Cases'!$M$6:$M$23,"Pass")</f>
-        <v>0</v>
-      </c>
-      <c r="F31" s="24">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="G31" s="12"/>
-      <c r="H31" s="12"/>
-      <c r="I31" s="12"/>
-      <c r="J31" s="12"/>
-      <c r="K31" s="12"/>
-      <c r="L31" s="12"/>
-      <c r="M31" s="12"/>
-      <c r="N31" s="12"/>
-    </row>
-    <row r="32" ht="25.5" customHeight="1">
-      <c r="A32" s="12"/>
-      <c r="B32" s="23" t="str">
-        <f>'Test Scenarios'!B8</f>
-        <v>Forms</v>
-      </c>
-      <c r="C32" s="23">
-        <f>COUNTIFS('Test Cases'!$D$6:$D$23,B32)</f>
-        <v>1</v>
-      </c>
-      <c r="D32" s="23">
-        <f>COUNTIFS('Test Cases'!$D$6:$D$23,B32,'Test Cases'!$L$6:$L$23,"Automated")</f>
-        <v>0</v>
-      </c>
-      <c r="E32" s="23">
-        <f>COUNTIFS('Test Cases'!$D$6:$D$23,B32,'Test Cases'!$M$6:$M$23,"Pass")</f>
-        <v>0</v>
-      </c>
-      <c r="F32" s="24">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="G32" s="12"/>
-      <c r="H32" s="12"/>
-      <c r="I32" s="12"/>
-      <c r="J32" s="12"/>
-      <c r="K32" s="12"/>
-      <c r="L32" s="12"/>
-      <c r="M32" s="12"/>
-      <c r="N32" s="12"/>
-    </row>
-    <row r="33" ht="25.5" customHeight="1">
-      <c r="A33" s="12"/>
-      <c r="B33" s="23" t="str">
-        <f>'Test Scenarios'!B9</f>
-        <v>Dropdowns</v>
-      </c>
-      <c r="C33" s="23">
-        <f>COUNTIFS('Test Cases'!$D$6:$D$23,B33)</f>
-        <v>1</v>
-      </c>
-      <c r="D33" s="23">
-        <f>COUNTIFS('Test Cases'!$D$6:$D$23,B33,'Test Cases'!$L$6:$L$23,"Automated")</f>
-        <v>0</v>
-      </c>
-      <c r="E33" s="23">
-        <f>COUNTIFS('Test Cases'!$D$6:$D$23,B33,'Test Cases'!$M$6:$M$23,"Pass")</f>
-        <v>0</v>
-      </c>
-      <c r="F33" s="24">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="G33" s="12"/>
-      <c r="H33" s="12"/>
-      <c r="I33" s="12"/>
-      <c r="J33" s="12"/>
-      <c r="K33" s="12"/>
-      <c r="L33" s="12"/>
-      <c r="M33" s="12"/>
-      <c r="N33" s="12"/>
-    </row>
-    <row r="34" ht="25.5" customHeight="1">
-      <c r="A34" s="12"/>
-      <c r="B34" s="23" t="str">
-        <f>'Test Scenarios'!B10</f>
-        <v>Data Table</v>
-      </c>
-      <c r="C34" s="23">
-        <f>COUNTIFS('Test Cases'!$D$6:$D$23,B34)</f>
-        <v>1</v>
-      </c>
-      <c r="D34" s="23">
-        <f>COUNTIFS('Test Cases'!$D$6:$D$23,B34,'Test Cases'!$L$6:$L$23,"Automated")</f>
-        <v>0</v>
-      </c>
-      <c r="E34" s="23">
-        <f>COUNTIFS('Test Cases'!$D$6:$D$23,B34,'Test Cases'!$M$6:$M$23,"Pass")</f>
-        <v>0</v>
-      </c>
-      <c r="F34" s="24">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="G34" s="12"/>
-      <c r="H34" s="12"/>
-      <c r="I34" s="12"/>
-      <c r="J34" s="12"/>
-      <c r="K34" s="12"/>
-      <c r="L34" s="12"/>
-      <c r="M34" s="12"/>
-      <c r="N34" s="12"/>
-    </row>
-    <row r="35" ht="25.5" customHeight="1">
-      <c r="A35" s="12"/>
-      <c r="B35" s="23" t="str">
+      <c r="G34" s="9"/>
+      <c r="H34" s="9"/>
+      <c r="I34" s="9"/>
+      <c r="J34" s="9"/>
+      <c r="K34" s="9"/>
+      <c r="L34" s="9"/>
+      <c r="M34" s="9"/>
+      <c r="N34" s="9"/>
+    </row>
+    <row r="35" spans="1:14" ht="25.5" customHeight="1">
+      <c r="A35" s="9"/>
+      <c r="B35" s="14" t="str">
         <f>'Test Scenarios'!B11</f>
         <v>Alerts &amp; Dialogs</v>
       </c>
-      <c r="C35" s="23">
+      <c r="C35" s="14">
         <f>COUNTIFS('Test Cases'!$D$6:$D$23,B35)</f>
         <v>1</v>
       </c>
-      <c r="D35" s="23">
+      <c r="D35" s="14">
         <f>COUNTIFS('Test Cases'!$D$6:$D$23,B35,'Test Cases'!$L$6:$L$23,"Automated")</f>
         <v>0</v>
       </c>
-      <c r="E35" s="23">
+      <c r="E35" s="14">
         <f>COUNTIFS('Test Cases'!$D$6:$D$23,B35,'Test Cases'!$M$6:$M$23,"Pass")</f>
         <v>0</v>
       </c>
-      <c r="F35" s="24">
-        <f t="shared" si="2"/>
+      <c r="F35" s="15">
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="G35" s="12"/>
-      <c r="H35" s="12"/>
-      <c r="I35" s="12"/>
-      <c r="J35" s="12"/>
-      <c r="K35" s="12"/>
-      <c r="L35" s="12"/>
-      <c r="M35" s="12"/>
-      <c r="N35" s="12"/>
-    </row>
-    <row r="36" ht="25.5" customHeight="1">
-      <c r="A36" s="12"/>
-      <c r="B36" s="23" t="str">
+      <c r="G35" s="9"/>
+      <c r="H35" s="9"/>
+      <c r="I35" s="9"/>
+      <c r="J35" s="9"/>
+      <c r="K35" s="9"/>
+      <c r="L35" s="9"/>
+      <c r="M35" s="9"/>
+      <c r="N35" s="9"/>
+    </row>
+    <row r="36" spans="1:14" ht="25.5" customHeight="1">
+      <c r="A36" s="9"/>
+      <c r="B36" s="14" t="str">
         <f>'Test Scenarios'!B12</f>
         <v>Radio &amp; Checkbox</v>
       </c>
-      <c r="C36" s="23">
+      <c r="C36" s="14">
         <f>COUNTIFS('Test Cases'!$D$6:$D$23,B36)</f>
         <v>1</v>
       </c>
-      <c r="D36" s="23">
+      <c r="D36" s="14">
         <f>COUNTIFS('Test Cases'!$D$6:$D$23,B36,'Test Cases'!$L$6:$L$23,"Automated")</f>
         <v>0</v>
       </c>
-      <c r="E36" s="23">
+      <c r="E36" s="14">
         <f>COUNTIFS('Test Cases'!$D$6:$D$23,B36,'Test Cases'!$M$6:$M$23,"Pass")</f>
         <v>0</v>
       </c>
-      <c r="F36" s="24">
-        <f t="shared" si="2"/>
+      <c r="F36" s="15">
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="G36" s="12"/>
-      <c r="H36" s="12"/>
-      <c r="I36" s="12"/>
-      <c r="J36" s="12"/>
-      <c r="K36" s="12"/>
-      <c r="L36" s="12"/>
-      <c r="M36" s="12"/>
-      <c r="N36" s="12"/>
-    </row>
-    <row r="37" ht="25.5" customHeight="1">
-      <c r="A37" s="12"/>
-      <c r="B37" s="23" t="str">
+      <c r="G36" s="9"/>
+      <c r="H36" s="9"/>
+      <c r="I36" s="9"/>
+      <c r="J36" s="9"/>
+      <c r="K36" s="9"/>
+      <c r="L36" s="9"/>
+      <c r="M36" s="9"/>
+      <c r="N36" s="9"/>
+    </row>
+    <row r="37" spans="1:14" ht="25.5" customHeight="1">
+      <c r="A37" s="9"/>
+      <c r="B37" s="14" t="str">
         <f>'Test Scenarios'!B13</f>
         <v>Date Picker</v>
       </c>
-      <c r="C37" s="23">
+      <c r="C37" s="14">
         <f>COUNTIFS('Test Cases'!$D$6:$D$23,B37)</f>
         <v>1</v>
       </c>
-      <c r="D37" s="23">
+      <c r="D37" s="14">
         <f>COUNTIFS('Test Cases'!$D$6:$D$23,B37,'Test Cases'!$L$6:$L$23,"Automated")</f>
         <v>0</v>
       </c>
-      <c r="E37" s="23">
+      <c r="E37" s="14">
         <f>COUNTIFS('Test Cases'!$D$6:$D$23,B37,'Test Cases'!$M$6:$M$23,"Pass")</f>
         <v>0</v>
       </c>
-      <c r="F37" s="24">
-        <f t="shared" si="2"/>
+      <c r="F37" s="15">
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="G37" s="12"/>
-      <c r="H37" s="12"/>
-      <c r="I37" s="12"/>
-      <c r="J37" s="12"/>
-      <c r="K37" s="12"/>
-      <c r="L37" s="12"/>
-      <c r="M37" s="12"/>
-      <c r="N37" s="12"/>
-    </row>
-    <row r="38" ht="25.5" customHeight="1">
-      <c r="A38" s="12"/>
-      <c r="B38" s="23" t="str">
+      <c r="G37" s="9"/>
+      <c r="H37" s="9"/>
+      <c r="I37" s="9"/>
+      <c r="J37" s="9"/>
+      <c r="K37" s="9"/>
+      <c r="L37" s="9"/>
+      <c r="M37" s="9"/>
+      <c r="N37" s="9"/>
+    </row>
+    <row r="38" spans="1:14" ht="25.5" customHeight="1">
+      <c r="A38" s="9"/>
+      <c r="B38" s="14" t="str">
         <f>'Test Scenarios'!B14</f>
         <v>Links</v>
       </c>
-      <c r="C38" s="23">
+      <c r="C38" s="14">
         <f>COUNTIFS('Test Cases'!$D$6:$D$23,B38)</f>
         <v>1</v>
       </c>
-      <c r="D38" s="23">
+      <c r="D38" s="14">
         <f>COUNTIFS('Test Cases'!$D$6:$D$23,B38,'Test Cases'!$L$6:$L$23,"Automated")</f>
         <v>0</v>
       </c>
-      <c r="E38" s="23">
+      <c r="E38" s="14">
         <f>COUNTIFS('Test Cases'!$D$6:$D$23,B38,'Test Cases'!$M$6:$M$23,"Pass")</f>
         <v>0</v>
       </c>
-      <c r="F38" s="24">
-        <f t="shared" si="2"/>
+      <c r="F38" s="15">
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="G38" s="12"/>
-      <c r="H38" s="12"/>
-      <c r="I38" s="12"/>
-      <c r="J38" s="12"/>
-      <c r="K38" s="12"/>
-      <c r="L38" s="12"/>
-      <c r="M38" s="12"/>
-      <c r="N38" s="12"/>
-    </row>
-    <row r="39" ht="25.5" customHeight="1">
-      <c r="A39" s="12"/>
-      <c r="B39" s="23" t="str">
+      <c r="G38" s="9"/>
+      <c r="H38" s="9"/>
+      <c r="I38" s="9"/>
+      <c r="J38" s="9"/>
+      <c r="K38" s="9"/>
+      <c r="L38" s="9"/>
+      <c r="M38" s="9"/>
+      <c r="N38" s="9"/>
+    </row>
+    <row r="39" spans="1:14" ht="25.5" customHeight="1">
+      <c r="A39" s="9"/>
+      <c r="B39" s="14" t="str">
         <f>'Test Scenarios'!B15</f>
         <v>Tabs &amp; Windows</v>
       </c>
-      <c r="C39" s="23">
+      <c r="C39" s="14">
         <f>COUNTIFS('Test Cases'!$D$6:$D$23,B39)</f>
         <v>1</v>
       </c>
-      <c r="D39" s="23">
+      <c r="D39" s="14">
         <f>COUNTIFS('Test Cases'!$D$6:$D$23,B39,'Test Cases'!$L$6:$L$23,"Automated")</f>
         <v>0</v>
       </c>
-      <c r="E39" s="23">
+      <c r="E39" s="14">
         <f>COUNTIFS('Test Cases'!$D$6:$D$23,B39,'Test Cases'!$M$6:$M$23,"Pass")</f>
         <v>0</v>
       </c>
-      <c r="F39" s="24">
-        <f t="shared" si="2"/>
+      <c r="F39" s="15">
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="G39" s="12"/>
-      <c r="H39" s="12"/>
-      <c r="I39" s="12"/>
-      <c r="J39" s="12"/>
-      <c r="K39" s="12"/>
-      <c r="L39" s="12"/>
-      <c r="M39" s="12"/>
-      <c r="N39" s="12"/>
-    </row>
-    <row r="40" ht="25.5" customHeight="1">
-      <c r="A40" s="12"/>
-      <c r="B40" s="23" t="str">
+      <c r="G39" s="9"/>
+      <c r="H39" s="9"/>
+      <c r="I39" s="9"/>
+      <c r="J39" s="9"/>
+      <c r="K39" s="9"/>
+      <c r="L39" s="9"/>
+      <c r="M39" s="9"/>
+      <c r="N39" s="9"/>
+    </row>
+    <row r="40" spans="1:14" ht="25.5" customHeight="1">
+      <c r="A40" s="9"/>
+      <c r="B40" s="14" t="str">
         <f>'Test Scenarios'!B16</f>
         <v>Dynamic Waits</v>
       </c>
-      <c r="C40" s="23">
+      <c r="C40" s="14">
         <f>COUNTIFS('Test Cases'!$D$6:$D$23,B40)</f>
         <v>1</v>
       </c>
-      <c r="D40" s="23">
+      <c r="D40" s="14">
         <f>COUNTIFS('Test Cases'!$D$6:$D$23,B40,'Test Cases'!$L$6:$L$23,"Automated")</f>
         <v>0</v>
       </c>
-      <c r="E40" s="23">
+      <c r="E40" s="14">
         <f>COUNTIFS('Test Cases'!$D$6:$D$23,B40,'Test Cases'!$M$6:$M$23,"Pass")</f>
         <v>0</v>
       </c>
-      <c r="F40" s="24">
-        <f t="shared" si="2"/>
+      <c r="F40" s="15">
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="G40" s="12"/>
-      <c r="H40" s="12"/>
-      <c r="I40" s="12"/>
-      <c r="J40" s="12"/>
-      <c r="K40" s="12"/>
-      <c r="L40" s="12"/>
-      <c r="M40" s="12"/>
-      <c r="N40" s="12"/>
-    </row>
-    <row r="41" ht="25.5" customHeight="1">
-      <c r="A41" s="12"/>
-      <c r="B41" s="23" t="str">
+      <c r="G40" s="9"/>
+      <c r="H40" s="9"/>
+      <c r="I40" s="9"/>
+      <c r="J40" s="9"/>
+      <c r="K40" s="9"/>
+      <c r="L40" s="9"/>
+      <c r="M40" s="9"/>
+      <c r="N40" s="9"/>
+    </row>
+    <row r="41" spans="1:14" ht="25.5" customHeight="1">
+      <c r="A41" s="9"/>
+      <c r="B41" s="14" t="str">
         <f>'Test Scenarios'!B17</f>
         <v>Multi Select</v>
       </c>
-      <c r="C41" s="23">
+      <c r="C41" s="14">
         <f>COUNTIFS('Test Cases'!$D$6:$D$23,B41)</f>
         <v>1</v>
       </c>
-      <c r="D41" s="23">
+      <c r="D41" s="14">
         <f>COUNTIFS('Test Cases'!$D$6:$D$23,B41,'Test Cases'!$L$6:$L$23,"Automated")</f>
         <v>0</v>
       </c>
-      <c r="E41" s="23">
+      <c r="E41" s="14">
         <f>COUNTIFS('Test Cases'!$D$6:$D$23,B41,'Test Cases'!$M$6:$M$23,"Pass")</f>
         <v>0</v>
       </c>
-      <c r="F41" s="24">
-        <f t="shared" si="2"/>
+      <c r="F41" s="15">
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="G41" s="12"/>
-      <c r="H41" s="12"/>
-      <c r="I41" s="12"/>
-      <c r="J41" s="12"/>
-      <c r="K41" s="12"/>
-      <c r="L41" s="12"/>
-      <c r="M41" s="12"/>
-      <c r="N41" s="12"/>
-    </row>
-    <row r="42" ht="25.5" customHeight="1">
-      <c r="A42" s="12"/>
-      <c r="B42" s="23" t="str">
+      <c r="G41" s="9"/>
+      <c r="H41" s="9"/>
+      <c r="I41" s="9"/>
+      <c r="J41" s="9"/>
+      <c r="K41" s="9"/>
+      <c r="L41" s="9"/>
+      <c r="M41" s="9"/>
+      <c r="N41" s="9"/>
+    </row>
+    <row r="42" spans="1:14" ht="25.5" customHeight="1">
+      <c r="A42" s="9"/>
+      <c r="B42" s="14" t="str">
         <f>'Test Scenarios'!B18</f>
         <v>File Upload</v>
       </c>
-      <c r="C42" s="23">
+      <c r="C42" s="14">
         <f>COUNTIFS('Test Cases'!$D$6:$D$23,B42)</f>
         <v>1</v>
       </c>
-      <c r="D42" s="23">
+      <c r="D42" s="14">
         <f>COUNTIFS('Test Cases'!$D$6:$D$23,B42,'Test Cases'!$L$6:$L$23,"Automated")</f>
         <v>0</v>
       </c>
-      <c r="E42" s="23">
+      <c r="E42" s="14">
         <f>COUNTIFS('Test Cases'!$D$6:$D$23,B42,'Test Cases'!$M$6:$M$23,"Pass")</f>
         <v>0</v>
       </c>
-      <c r="F42" s="24">
-        <f t="shared" si="2"/>
+      <c r="F42" s="15">
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="G42" s="12"/>
-      <c r="H42" s="12"/>
-      <c r="I42" s="12"/>
-      <c r="J42" s="12"/>
-      <c r="K42" s="12"/>
-      <c r="L42" s="12"/>
-      <c r="M42" s="12"/>
-      <c r="N42" s="12"/>
-    </row>
-    <row r="43" ht="25.5" customHeight="1">
-      <c r="A43" s="12"/>
-      <c r="B43" s="23" t="str">
+      <c r="G42" s="9"/>
+      <c r="H42" s="9"/>
+      <c r="I42" s="9"/>
+      <c r="J42" s="9"/>
+      <c r="K42" s="9"/>
+      <c r="L42" s="9"/>
+      <c r="M42" s="9"/>
+      <c r="N42" s="9"/>
+    </row>
+    <row r="43" spans="1:14" ht="25.5" customHeight="1">
+      <c r="A43" s="9"/>
+      <c r="B43" s="14" t="str">
         <f>'Test Scenarios'!B19</f>
         <v>Drag &amp; Drop</v>
       </c>
-      <c r="C43" s="23">
+      <c r="C43" s="14">
         <f>COUNTIFS('Test Cases'!$D$6:$D$23,B43)</f>
         <v>1</v>
       </c>
-      <c r="D43" s="23">
+      <c r="D43" s="14">
         <f>COUNTIFS('Test Cases'!$D$6:$D$23,B43,'Test Cases'!$L$6:$L$23,"Automated")</f>
         <v>0</v>
       </c>
-      <c r="E43" s="23">
+      <c r="E43" s="14">
         <f>COUNTIFS('Test Cases'!$D$6:$D$23,B43,'Test Cases'!$M$6:$M$23,"Pass")</f>
         <v>0</v>
       </c>
-      <c r="F43" s="24">
-        <f t="shared" si="2"/>
+      <c r="F43" s="15">
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="G43" s="12"/>
-      <c r="H43" s="12"/>
-      <c r="I43" s="12"/>
-      <c r="J43" s="12"/>
-      <c r="K43" s="12"/>
-      <c r="L43" s="12"/>
-      <c r="M43" s="12"/>
-      <c r="N43" s="12"/>
-    </row>
-    <row r="44" ht="25.5" customHeight="1">
-      <c r="A44" s="12"/>
-      <c r="B44" s="23" t="str">
+      <c r="G43" s="9"/>
+      <c r="H43" s="9"/>
+      <c r="I43" s="9"/>
+      <c r="J43" s="9"/>
+      <c r="K43" s="9"/>
+      <c r="L43" s="9"/>
+      <c r="M43" s="9"/>
+      <c r="N43" s="9"/>
+    </row>
+    <row r="44" spans="1:14" ht="25.5" customHeight="1">
+      <c r="A44" s="9"/>
+      <c r="B44" s="14" t="str">
         <f>'Test Scenarios'!B20</f>
         <v>iFrames</v>
       </c>
-      <c r="C44" s="23">
+      <c r="C44" s="14">
         <f>COUNTIFS('Test Cases'!$D$6:$D$23,B44)</f>
         <v>1</v>
       </c>
-      <c r="D44" s="23">
+      <c r="D44" s="14">
         <f>COUNTIFS('Test Cases'!$D$6:$D$23,B44,'Test Cases'!$L$6:$L$23,"Automated")</f>
         <v>0</v>
       </c>
-      <c r="E44" s="23">
+      <c r="E44" s="14">
         <f>COUNTIFS('Test Cases'!$D$6:$D$23,B44,'Test Cases'!$M$6:$M$23,"Pass")</f>
         <v>0</v>
       </c>
-      <c r="F44" s="24">
-        <f t="shared" si="2"/>
+      <c r="F44" s="15">
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="G44" s="12"/>
-      <c r="H44" s="12"/>
-      <c r="I44" s="12"/>
-      <c r="J44" s="12"/>
-      <c r="K44" s="12"/>
-      <c r="L44" s="12"/>
-      <c r="M44" s="12"/>
-      <c r="N44" s="12"/>
-    </row>
-    <row r="45" ht="25.5" customHeight="1">
-      <c r="A45" s="12"/>
-      <c r="B45" s="23" t="str">
+      <c r="G44" s="9"/>
+      <c r="H44" s="9"/>
+      <c r="I44" s="9"/>
+      <c r="J44" s="9"/>
+      <c r="K44" s="9"/>
+      <c r="L44" s="9"/>
+      <c r="M44" s="9"/>
+      <c r="N44" s="9"/>
+    </row>
+    <row r="45" spans="1:14" ht="25.5" customHeight="1">
+      <c r="A45" s="9"/>
+      <c r="B45" s="14" t="str">
         <f>'Test Scenarios'!B21</f>
         <v>Shadow DOM</v>
       </c>
-      <c r="C45" s="23">
+      <c r="C45" s="14">
         <f>COUNTIFS('Test Cases'!$D$6:$D$23,B45)</f>
         <v>1</v>
       </c>
-      <c r="D45" s="23">
+      <c r="D45" s="14">
         <f>COUNTIFS('Test Cases'!$D$6:$D$23,B45,'Test Cases'!$L$6:$L$23,"Automated")</f>
         <v>0</v>
       </c>
-      <c r="E45" s="23">
+      <c r="E45" s="14">
         <f>COUNTIFS('Test Cases'!$D$6:$D$23,B45,'Test Cases'!$M$6:$M$23,"Pass")</f>
         <v>0</v>
       </c>
-      <c r="F45" s="24">
-        <f t="shared" si="2"/>
+      <c r="F45" s="15">
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="G45" s="12"/>
-      <c r="H45" s="12"/>
-      <c r="I45" s="12"/>
-      <c r="J45" s="12"/>
-      <c r="K45" s="12"/>
-      <c r="L45" s="12"/>
-      <c r="M45" s="12"/>
-      <c r="N45" s="12"/>
-    </row>
-    <row r="46" ht="25.5" customHeight="1">
-      <c r="A46" s="12"/>
-      <c r="B46" s="23" t="str">
+      <c r="G45" s="9"/>
+      <c r="H45" s="9"/>
+      <c r="I45" s="9"/>
+      <c r="J45" s="9"/>
+      <c r="K45" s="9"/>
+      <c r="L45" s="9"/>
+      <c r="M45" s="9"/>
+      <c r="N45" s="9"/>
+    </row>
+    <row r="46" spans="1:14" ht="25.5" customHeight="1">
+      <c r="A46" s="9"/>
+      <c r="B46" s="14" t="str">
         <f>'Test Scenarios'!B22</f>
         <v>Modal Windows</v>
       </c>
-      <c r="C46" s="23">
+      <c r="C46" s="14">
         <f>COUNTIFS('Test Cases'!$D$6:$D$23,B46)</f>
         <v>1</v>
       </c>
-      <c r="D46" s="23">
+      <c r="D46" s="14">
         <f>COUNTIFS('Test Cases'!$D$6:$D$23,B46,'Test Cases'!$L$6:$L$23,"Automated")</f>
         <v>0</v>
       </c>
-      <c r="E46" s="23">
+      <c r="E46" s="14">
         <f>COUNTIFS('Test Cases'!$D$6:$D$23,B46,'Test Cases'!$M$6:$M$23,"Pass")</f>
         <v>0</v>
       </c>
-      <c r="F46" s="24">
-        <f t="shared" si="2"/>
+      <c r="F46" s="15">
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="G46" s="12"/>
-      <c r="H46" s="12"/>
-      <c r="I46" s="12"/>
-      <c r="J46" s="12"/>
-      <c r="K46" s="12"/>
-      <c r="L46" s="12"/>
-      <c r="M46" s="12"/>
-      <c r="N46" s="12"/>
-    </row>
-    <row r="47" ht="25.5" customHeight="1">
-      <c r="A47" s="12"/>
-      <c r="B47" s="23" t="str">
+      <c r="G46" s="9"/>
+      <c r="H46" s="9"/>
+      <c r="I46" s="9"/>
+      <c r="J46" s="9"/>
+      <c r="K46" s="9"/>
+      <c r="L46" s="9"/>
+      <c r="M46" s="9"/>
+      <c r="N46" s="9"/>
+    </row>
+    <row r="47" spans="1:14" ht="25.5" customHeight="1">
+      <c r="A47" s="9"/>
+      <c r="B47" s="14" t="str">
         <f>'Test Scenarios'!B23</f>
         <v>Infinite Scroll</v>
       </c>
-      <c r="C47" s="23">
+      <c r="C47" s="14">
         <f>COUNTIFS('Test Cases'!$D$6:$D$23,B47)</f>
         <v>1</v>
       </c>
-      <c r="D47" s="23">
+      <c r="D47" s="14">
         <f>COUNTIFS('Test Cases'!$D$6:$D$23,B47,'Test Cases'!$L$6:$L$23,"Automated")</f>
         <v>0</v>
       </c>
-      <c r="E47" s="23">
+      <c r="E47" s="14">
         <f>COUNTIFS('Test Cases'!$D$6:$D$23,B47,'Test Cases'!$M$6:$M$23,"Pass")</f>
         <v>0</v>
       </c>
-      <c r="F47" s="24">
-        <f t="shared" si="2"/>
+      <c r="F47" s="15">
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="G47" s="12"/>
-      <c r="H47" s="12"/>
-      <c r="I47" s="12"/>
-      <c r="J47" s="12"/>
-      <c r="K47" s="12"/>
-      <c r="L47" s="12"/>
-      <c r="M47" s="12"/>
-      <c r="N47" s="12"/>
-    </row>
-    <row r="48" ht="15.75" customHeight="1">
-      <c r="A48" s="12"/>
-      <c r="B48" s="12"/>
-      <c r="C48" s="12"/>
-      <c r="D48" s="12"/>
-      <c r="E48" s="12"/>
-      <c r="F48" s="12"/>
-      <c r="G48" s="12"/>
-      <c r="H48" s="12"/>
-      <c r="I48" s="12"/>
-      <c r="J48" s="12"/>
-      <c r="K48" s="12"/>
-      <c r="L48" s="12"/>
-      <c r="M48" s="12"/>
-      <c r="N48" s="12"/>
+      <c r="G47" s="9"/>
+      <c r="H47" s="9"/>
+      <c r="I47" s="9"/>
+      <c r="J47" s="9"/>
+      <c r="K47" s="9"/>
+      <c r="L47" s="9"/>
+      <c r="M47" s="9"/>
+      <c r="N47" s="9"/>
+    </row>
+    <row r="48" spans="1:14" ht="15.75" customHeight="1">
+      <c r="A48" s="9"/>
+      <c r="B48" s="9"/>
+      <c r="C48" s="9"/>
+      <c r="D48" s="9"/>
+      <c r="E48" s="9"/>
+      <c r="F48" s="9"/>
+      <c r="G48" s="9"/>
+      <c r="H48" s="9"/>
+      <c r="I48" s="9"/>
+      <c r="J48" s="9"/>
+      <c r="K48" s="9"/>
+      <c r="L48" s="9"/>
+      <c r="M48" s="9"/>
+      <c r="N48" s="9"/>
     </row>
     <row r="49" ht="15.75" customHeight="1"/>
     <row r="50" ht="15.75" customHeight="1"/>
@@ -4126,6 +4425,17 @@
     <row r="1000" ht="15.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="18">
+    <mergeCell ref="I6:J7"/>
+    <mergeCell ref="K6:L7"/>
+    <mergeCell ref="M6:N7"/>
+    <mergeCell ref="B9:N9"/>
+    <mergeCell ref="D6:E7"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="B20:F20"/>
+    <mergeCell ref="B28:F28"/>
+    <mergeCell ref="B5:C5"/>
+    <mergeCell ref="B6:C7"/>
+    <mergeCell ref="F6:H7"/>
     <mergeCell ref="B1:N2"/>
     <mergeCell ref="B3:N3"/>
     <mergeCell ref="D5:E5"/>
@@ -4133,17 +4443,6 @@
     <mergeCell ref="I5:J5"/>
     <mergeCell ref="K5:L5"/>
     <mergeCell ref="M5:N5"/>
-    <mergeCell ref="D6:E7"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B20:F20"/>
-    <mergeCell ref="B28:F28"/>
-    <mergeCell ref="B5:C5"/>
-    <mergeCell ref="B6:C7"/>
-    <mergeCell ref="F6:H7"/>
-    <mergeCell ref="I6:J7"/>
-    <mergeCell ref="K6:L7"/>
-    <mergeCell ref="M6:N7"/>
-    <mergeCell ref="B9:N9"/>
   </mergeCells>
   <conditionalFormatting sqref="F30:F47">
     <cfRule type="colorScale" priority="1">
@@ -4157,509 +4456,528 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <printOptions/>
-  <pageMargins bottom="0.75" footer="0.0" header="0.0" left="0.7" right="0.7" top="0.75"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup orientation="landscape"/>
   <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr>
     <tabColor rgb="FF147D86"/>
-    <pageSetUpPr/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.0"/>
+  <dimension ref="A1:G1000"/>
+  <sheetFormatPr defaultColWidth="12.625" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="15.0"/>
-    <col customWidth="1" min="2" max="2" width="24.0"/>
-    <col customWidth="1" min="3" max="3" width="17.0"/>
-    <col customWidth="1" min="4" max="4" width="65.0"/>
-    <col customWidth="1" min="5" max="5" width="57.0"/>
-    <col customWidth="1" min="6" max="7" width="17.0"/>
-    <col customWidth="1" min="8" max="25" width="8.63"/>
+    <col min="1" max="1" width="15" customWidth="1"/>
+    <col min="2" max="2" width="24" customWidth="1"/>
+    <col min="3" max="3" width="17" customWidth="1"/>
+    <col min="4" max="4" width="65" customWidth="1"/>
+    <col min="5" max="5" width="57" customWidth="1"/>
+    <col min="6" max="7" width="17" customWidth="1"/>
+    <col min="8" max="25" width="8.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="25.5" customHeight="1">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:7" ht="25.5" customHeight="1">
+      <c r="A1" s="25" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="2" ht="25.5" customHeight="1"/>
-    <row r="3" ht="27.75" customHeight="1">
-      <c r="A3" s="2" t="s">
+      <c r="B1" s="18"/>
+      <c r="C1" s="18"/>
+      <c r="D1" s="18"/>
+      <c r="E1" s="18"/>
+      <c r="F1" s="18"/>
+      <c r="G1" s="18"/>
+    </row>
+    <row r="2" spans="1:7" ht="25.5" customHeight="1">
+      <c r="A2" s="18"/>
+      <c r="B2" s="18"/>
+      <c r="C2" s="18"/>
+      <c r="D2" s="18"/>
+      <c r="E2" s="18"/>
+      <c r="F2" s="18"/>
+      <c r="G2" s="18"/>
+    </row>
+    <row r="3" spans="1:7" ht="27.75" customHeight="1">
+      <c r="A3" s="19" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="3" t="s">
+      <c r="B3" s="18"/>
+      <c r="C3" s="18"/>
+      <c r="D3" s="18"/>
+      <c r="E3" s="18"/>
+      <c r="F3" s="18"/>
+      <c r="G3" s="18"/>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="B5" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="C5" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D5" s="3" t="s">
+      <c r="D5" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="E5" s="3" t="s">
+      <c r="E5" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="F5" s="3" t="s">
+      <c r="F5" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="G5" s="3" t="s">
+      <c r="G5" s="1" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="6" ht="42.0" customHeight="1">
-      <c r="A6" s="5" t="s">
+    <row r="6" spans="1:7" ht="42" customHeight="1">
+      <c r="A6" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="B6" s="5" t="s">
+      <c r="B6" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="C6" s="5" t="s">
+      <c r="C6" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="D6" s="5" t="s">
+      <c r="D6" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="E6" s="5" t="s">
+      <c r="E6" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="F6" s="5" t="s">
+      <c r="F6" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="G6" s="6" t="s">
+      <c r="G6" s="3" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="7" ht="42.0" customHeight="1">
-      <c r="A7" s="5" t="s">
+    <row r="7" spans="1:7" ht="42" customHeight="1">
+      <c r="A7" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="B7" s="5" t="s">
+      <c r="B7" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="C7" s="5" t="s">
+      <c r="C7" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="D7" s="5" t="s">
+      <c r="D7" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="E7" s="5" t="s">
+      <c r="E7" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="F7" s="5" t="s">
+      <c r="F7" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="G7" s="5" t="s">
+      <c r="G7" s="3" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="42" customHeight="1">
+      <c r="A8" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="G8" s="3" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="8" ht="42.0" customHeight="1">
-      <c r="A8" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="B8" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="C8" s="5" t="s">
+    <row r="9" spans="1:7" ht="42" customHeight="1">
+      <c r="A9" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="G9" s="3" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" ht="42" customHeight="1">
+      <c r="A10" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="C10" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="D8" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="E8" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="F8" s="5" t="s">
+      <c r="D10" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="F10" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="G8" s="5" t="s">
+      <c r="G10" s="3" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="9" ht="42.0" customHeight="1">
-      <c r="A9" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B9" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="C9" s="5" t="s">
+    <row r="11" spans="1:7" ht="42" customHeight="1">
+      <c r="A11" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="F11" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="G11" s="3" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" ht="42" customHeight="1">
+      <c r="A12" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="C12" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="D9" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="E9" s="5" t="s">
-        <v>48</v>
-      </c>
-      <c r="F9" s="5" t="s">
+      <c r="D12" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="F12" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G12" s="3" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" ht="42" customHeight="1">
+      <c r="A13" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="F13" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="G9" s="5" t="s">
+      <c r="G13" s="3" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="10" ht="42.0" customHeight="1">
-      <c r="A10" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="B10" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="C10" s="5" t="s">
+    <row r="14" spans="1:7" ht="42" customHeight="1">
+      <c r="A14" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D14" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" ht="42" customHeight="1">
+      <c r="A15" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="C15" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="D10" s="5" t="s">
-        <v>54</v>
-      </c>
-      <c r="E10" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="F10" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="G10" s="5" t="s">
+      <c r="D15" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="F15" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="G15" s="3" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="11" ht="42.0" customHeight="1">
-      <c r="A11" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="B11" s="5" t="s">
-        <v>58</v>
-      </c>
-      <c r="C11" s="5" t="s">
+    <row r="16" spans="1:7" ht="42" customHeight="1">
+      <c r="A16" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="D16" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="E16" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="F16" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="G16" s="3" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" ht="42" customHeight="1">
+      <c r="A17" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="C17" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="D11" s="5" t="s">
-        <v>59</v>
-      </c>
-      <c r="E11" s="5" t="s">
-        <v>60</v>
-      </c>
-      <c r="F11" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="G11" s="5" t="s">
+      <c r="D17" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="F17" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="G17" s="3" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="12" ht="42.0" customHeight="1">
-      <c r="A12" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="B12" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="C12" s="5" t="s">
+    <row r="18" spans="1:7" ht="42" customHeight="1">
+      <c r="A18" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="D18" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="F18" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="G18" s="3" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" ht="42" customHeight="1">
+      <c r="A19" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="D19" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="E19" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="F19" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="G19" s="3" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" ht="42" customHeight="1">
+      <c r="A20" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="D20" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="F20" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="G20" s="3" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" ht="42" customHeight="1">
+      <c r="A21" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="D21" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="E21" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="F21" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="G21" s="3" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" ht="42" customHeight="1">
+      <c r="A22" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="C22" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="D12" s="5" t="s">
-        <v>64</v>
-      </c>
-      <c r="E12" s="5" t="s">
-        <v>65</v>
-      </c>
-      <c r="F12" s="5" t="s">
+      <c r="D22" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="F22" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="G12" s="5" t="s">
+      <c r="G22" s="3" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="13" ht="42.0" customHeight="1">
-      <c r="A13" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="B13" s="5" t="s">
-        <v>67</v>
-      </c>
-      <c r="C13" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="D13" s="5" t="s">
-        <v>69</v>
-      </c>
-      <c r="E13" s="5" t="s">
-        <v>71</v>
-      </c>
-      <c r="F13" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="G13" s="5" t="s">
+    <row r="23" spans="1:7" ht="42" customHeight="1">
+      <c r="A23" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="D23" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="E23" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="F23" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="G23" s="3" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="14" ht="42.0" customHeight="1">
-      <c r="A14" s="5" t="s">
-        <v>74</v>
-      </c>
-      <c r="B14" s="5" t="s">
-        <v>75</v>
-      </c>
-      <c r="C14" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="D14" s="5" t="s">
-        <v>76</v>
-      </c>
-      <c r="E14" s="5" t="s">
-        <v>77</v>
-      </c>
-      <c r="F14" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="G14" s="5" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="15" ht="42.0" customHeight="1">
-      <c r="A15" s="5" t="s">
-        <v>78</v>
-      </c>
-      <c r="B15" s="5" t="s">
-        <v>80</v>
-      </c>
-      <c r="C15" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="D15" s="5" t="s">
-        <v>81</v>
-      </c>
-      <c r="E15" s="5" t="s">
-        <v>83</v>
-      </c>
-      <c r="F15" s="5" t="s">
-        <v>84</v>
-      </c>
-      <c r="G15" s="5" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="16" ht="42.0" customHeight="1">
-      <c r="A16" s="5" t="s">
-        <v>85</v>
-      </c>
-      <c r="B16" s="5" t="s">
-        <v>86</v>
-      </c>
-      <c r="C16" s="5" t="s">
+    <row r="24" spans="1:7" ht="42" customHeight="1">
+      <c r="A24" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="C24" s="3" t="s">
         <v>87</v>
       </c>
-      <c r="D16" s="5" t="s">
-        <v>89</v>
-      </c>
-      <c r="E16" s="5" t="s">
-        <v>90</v>
-      </c>
-      <c r="F16" s="5" t="s">
-        <v>84</v>
-      </c>
-      <c r="G16" s="5" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="17" ht="42.0" customHeight="1">
-      <c r="A17" s="5" t="s">
-        <v>91</v>
-      </c>
-      <c r="B17" s="5" t="s">
-        <v>93</v>
-      </c>
-      <c r="C17" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="D17" s="5" t="s">
-        <v>95</v>
-      </c>
-      <c r="E17" s="5" t="s">
-        <v>96</v>
-      </c>
-      <c r="F17" s="5" t="s">
-        <v>84</v>
-      </c>
-      <c r="G17" s="5" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="18" ht="42.0" customHeight="1">
-      <c r="A18" s="5" t="s">
-        <v>99</v>
-      </c>
-      <c r="B18" s="5" t="s">
-        <v>100</v>
-      </c>
-      <c r="C18" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="D18" s="5" t="s">
-        <v>101</v>
-      </c>
-      <c r="E18" s="5" t="s">
-        <v>102</v>
-      </c>
-      <c r="F18" s="5" t="s">
-        <v>84</v>
-      </c>
-      <c r="G18" s="5" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="19" ht="42.0" customHeight="1">
-      <c r="A19" s="5" t="s">
-        <v>103</v>
-      </c>
-      <c r="B19" s="5" t="s">
-        <v>104</v>
-      </c>
-      <c r="C19" s="5" t="s">
-        <v>87</v>
-      </c>
-      <c r="D19" s="5" t="s">
-        <v>105</v>
-      </c>
-      <c r="E19" s="5" t="s">
-        <v>106</v>
-      </c>
-      <c r="F19" s="5" t="s">
-        <v>107</v>
-      </c>
-      <c r="G19" s="5" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="20" ht="42.0" customHeight="1">
-      <c r="A20" s="5" t="s">
-        <v>109</v>
-      </c>
-      <c r="B20" s="5" t="s">
-        <v>110</v>
-      </c>
-      <c r="C20" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="D20" s="5" t="s">
-        <v>111</v>
-      </c>
-      <c r="E20" s="5" t="s">
-        <v>112</v>
-      </c>
-      <c r="F20" s="5" t="s">
-        <v>107</v>
-      </c>
-      <c r="G20" s="5" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="21" ht="42.0" customHeight="1">
-      <c r="A21" s="5" t="s">
-        <v>115</v>
-      </c>
-      <c r="B21" s="5" t="s">
-        <v>116</v>
-      </c>
-      <c r="C21" s="5" t="s">
-        <v>87</v>
-      </c>
-      <c r="D21" s="5" t="s">
-        <v>118</v>
-      </c>
-      <c r="E21" s="5" t="s">
-        <v>120</v>
-      </c>
-      <c r="F21" s="5" t="s">
-        <v>107</v>
-      </c>
-      <c r="G21" s="5" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="22" ht="42.0" customHeight="1">
-      <c r="A22" s="5" t="s">
-        <v>121</v>
-      </c>
-      <c r="B22" s="5" t="s">
-        <v>122</v>
-      </c>
-      <c r="C22" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="D22" s="5" t="s">
-        <v>123</v>
-      </c>
-      <c r="E22" s="5" t="s">
-        <v>124</v>
-      </c>
-      <c r="F22" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="G22" s="5" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="23" ht="42.0" customHeight="1">
-      <c r="A23" s="5" t="s">
-        <v>125</v>
-      </c>
-      <c r="B23" s="5" t="s">
-        <v>126</v>
-      </c>
-      <c r="C23" s="5" t="s">
-        <v>87</v>
-      </c>
-      <c r="D23" s="5" t="s">
-        <v>127</v>
-      </c>
-      <c r="E23" s="5" t="s">
-        <v>128</v>
-      </c>
-      <c r="F23" s="5" t="s">
-        <v>107</v>
-      </c>
-      <c r="G23" s="5" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="24" ht="42.0" customHeight="1">
-      <c r="A24" s="5" t="s">
-        <v>130</v>
-      </c>
-      <c r="B24" s="5" t="s">
-        <v>131</v>
-      </c>
-      <c r="C24" s="5" t="s">
-        <v>87</v>
-      </c>
-      <c r="D24" s="5" t="s">
+      <c r="D24" s="3" t="s">
         <v>132</v>
       </c>
-      <c r="E24" s="5" t="s">
+      <c r="E24" s="3" t="s">
         <v>133</v>
       </c>
-      <c r="F24" s="5" t="s">
+      <c r="F24" s="3" t="s">
         <v>135</v>
       </c>
-      <c r="G24" s="5" t="s">
+      <c r="G24" s="3" t="s">
         <v>136</v>
       </c>
     </row>
-    <row r="25" ht="15.75" customHeight="1"/>
-    <row r="26" ht="15.75" customHeight="1"/>
-    <row r="27" ht="15.75" customHeight="1"/>
-    <row r="28" ht="15.75" customHeight="1"/>
-    <row r="29" ht="15.75" customHeight="1"/>
-    <row r="30" ht="15.75" customHeight="1"/>
-    <row r="31" ht="15.75" customHeight="1"/>
-    <row r="32" ht="15.75" customHeight="1"/>
+    <row r="25" spans="1:7" ht="15.75" customHeight="1"/>
+    <row r="26" spans="1:7" ht="15.75" customHeight="1"/>
+    <row r="27" spans="1:7" ht="15.75" customHeight="1"/>
+    <row r="28" spans="1:7" ht="15.75" customHeight="1"/>
+    <row r="29" spans="1:7" ht="15.75" customHeight="1"/>
+    <row r="30" spans="1:7" ht="15.75" customHeight="1"/>
+    <row r="31" spans="1:7" ht="15.75" customHeight="1"/>
+    <row r="32" spans="1:7" ht="15.75" customHeight="1"/>
     <row r="33" ht="15.75" customHeight="1"/>
     <row r="34" ht="15.75" customHeight="1"/>
     <row r="35" ht="15.75" customHeight="1"/>
@@ -5633,2084 +5951,2126 @@
     <mergeCell ref="A1:G2"/>
     <mergeCell ref="A3:G3"/>
   </mergeCells>
-  <dataValidations>
-    <dataValidation type="list" allowBlank="1" sqref="G6:G24">
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" sqref="G6:G24" xr:uid="{00000000-0002-0000-0100-000000000000}">
       <formula1>"Not Started,In Progress,Complete,Planned"</formula1>
     </dataValidation>
   </dataValidations>
-  <printOptions/>
-  <pageMargins bottom="0.75" footer="0.0" header="0.0" left="0.7" right="0.7" top="0.75"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup orientation="landscape"/>
-  <drawing r:id="rId1"/>
   <tableParts count="1">
-    <tablePart r:id="rId3"/>
+    <tablePart r:id="rId1"/>
   </tableParts>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <sheetPr>
     <tabColor rgb="FF2865A5"/>
-    <pageSetUpPr/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.0"/>
+  <dimension ref="A1:O1000"/>
+  <sheetFormatPr defaultColWidth="12.625" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="14.0"/>
-    <col customWidth="1" min="2" max="2" width="11.0"/>
-    <col customWidth="1" min="3" max="3" width="46.0"/>
-    <col customWidth="1" min="4" max="4" width="21.0"/>
-    <col customWidth="1" min="5" max="5" width="38.0"/>
-    <col customWidth="1" min="6" max="6" width="70.0"/>
-    <col customWidth="1" min="7" max="7" width="45.0"/>
-    <col customWidth="1" min="8" max="8" width="70.0"/>
-    <col customWidth="1" min="9" max="10" width="13.0"/>
-    <col customWidth="1" min="11" max="13" width="17.0"/>
-    <col customWidth="1" min="14" max="14" width="52.0"/>
-    <col customWidth="1" min="15" max="15" width="12.0"/>
-    <col customWidth="1" min="16" max="26" width="8.63"/>
+    <col min="1" max="1" width="14" customWidth="1"/>
+    <col min="2" max="2" width="11" customWidth="1"/>
+    <col min="3" max="3" width="46" customWidth="1"/>
+    <col min="4" max="4" width="21" customWidth="1"/>
+    <col min="5" max="5" width="38" customWidth="1"/>
+    <col min="6" max="6" width="70" customWidth="1"/>
+    <col min="7" max="7" width="45" customWidth="1"/>
+    <col min="8" max="8" width="70" customWidth="1"/>
+    <col min="9" max="10" width="13" customWidth="1"/>
+    <col min="11" max="13" width="17" customWidth="1"/>
+    <col min="14" max="14" width="52" customWidth="1"/>
+    <col min="15" max="15" width="12" customWidth="1"/>
+    <col min="16" max="26" width="8.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="25.5" customHeight="1">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:15" ht="25.5" customHeight="1">
+      <c r="A1" s="25" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="2" ht="25.5" customHeight="1"/>
-    <row r="3" ht="27.75" customHeight="1">
-      <c r="A3" s="2" t="s">
+      <c r="B1" s="25"/>
+      <c r="C1" s="25"/>
+      <c r="D1" s="25"/>
+      <c r="E1" s="25"/>
+      <c r="F1" s="25"/>
+      <c r="G1" s="25"/>
+      <c r="H1" s="25"/>
+      <c r="I1" s="25"/>
+      <c r="J1" s="25"/>
+      <c r="K1" s="25"/>
+      <c r="L1" s="25"/>
+      <c r="M1" s="25"/>
+      <c r="N1" s="25"/>
+      <c r="O1" s="25"/>
+    </row>
+    <row r="2" spans="1:15" ht="25.5" customHeight="1">
+      <c r="A2" s="25"/>
+      <c r="B2" s="25"/>
+      <c r="C2" s="25"/>
+      <c r="D2" s="25"/>
+      <c r="E2" s="25"/>
+      <c r="F2" s="25"/>
+      <c r="G2" s="25"/>
+      <c r="H2" s="25"/>
+      <c r="I2" s="25"/>
+      <c r="J2" s="25"/>
+      <c r="K2" s="25"/>
+      <c r="L2" s="25"/>
+      <c r="M2" s="25"/>
+      <c r="N2" s="25"/>
+      <c r="O2" s="25"/>
+    </row>
+    <row r="3" spans="1:15" ht="27.75" customHeight="1">
+      <c r="A3" s="19" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="5" ht="36.75" customHeight="1">
-      <c r="A5" s="4" t="s">
+      <c r="B3" s="19"/>
+      <c r="C3" s="19"/>
+      <c r="D3" s="19"/>
+      <c r="E3" s="19"/>
+      <c r="F3" s="19"/>
+      <c r="G3" s="19"/>
+      <c r="H3" s="19"/>
+      <c r="I3" s="19"/>
+      <c r="J3" s="19"/>
+      <c r="K3" s="19"/>
+      <c r="L3" s="19"/>
+      <c r="M3" s="19"/>
+      <c r="N3" s="19"/>
+      <c r="O3" s="19"/>
+    </row>
+    <row r="5" spans="1:15" ht="36.75" customHeight="1">
+      <c r="A5" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="4" t="s">
+      <c r="B5" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="C5" s="4" t="s">
+      <c r="C5" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D5" s="4" t="s">
+      <c r="D5" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="E5" s="4" t="s">
+      <c r="E5" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="F5" s="4" t="s">
+      <c r="F5" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="G5" s="4" t="s">
+      <c r="G5" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="H5" s="4" t="s">
+      <c r="H5" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="I5" s="4" t="s">
+      <c r="I5" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="J5" s="4" t="s">
+      <c r="J5" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="K5" s="4" t="s">
+      <c r="K5" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="L5" s="4" t="s">
+      <c r="L5" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="M5" s="4" t="s">
+      <c r="M5" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="N5" s="4" t="s">
+      <c r="N5" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="O5" s="4" t="s">
+      <c r="O5" s="2" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="6" ht="163.5" customHeight="1">
-      <c r="A6" s="7" t="s">
+    <row r="6" spans="1:15" ht="163.5" customHeight="1">
+      <c r="A6" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="B6" s="7" t="s">
+      <c r="B6" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="C6" s="8" t="s">
+      <c r="C6" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="D6" s="8" t="s">
+      <c r="D6" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="E6" s="8" t="s">
+      <c r="E6" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="F6" s="9" t="s">
+      <c r="F6" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="G6" s="8" t="s">
+      <c r="G6" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="H6" s="8" t="s">
+      <c r="H6" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="I6" s="8" t="s">
+      <c r="I6" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="J6" s="8" t="s">
+      <c r="J6" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="K6" s="8" t="s">
+      <c r="K6" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="L6" s="9" t="s">
+      <c r="L6" s="26" t="s">
         <v>53</v>
       </c>
-      <c r="M6" s="9" t="s">
+      <c r="M6" s="26" t="s">
         <v>56</v>
       </c>
-      <c r="N6" s="8" t="s">
+      <c r="N6" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="O6" s="8">
-        <v>8.0</v>
-      </c>
-    </row>
-    <row r="7" ht="145.5" customHeight="1">
-      <c r="A7" s="10" t="s">
+      <c r="O6" s="5">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15" ht="145.5" customHeight="1">
+      <c r="A7" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="B7" s="10" t="s">
+      <c r="B7" s="7" t="s">
         <v>63</v>
       </c>
-      <c r="C7" s="11" t="s">
+      <c r="C7" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="D7" s="11" t="s">
+      <c r="D7" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="E7" s="11" t="s">
+      <c r="E7" s="8" t="s">
         <v>68</v>
       </c>
-      <c r="F7" s="11" t="s">
+      <c r="F7" s="8" t="s">
         <v>70</v>
       </c>
-      <c r="G7" s="11" t="s">
+      <c r="G7" s="8" t="s">
         <v>72</v>
       </c>
-      <c r="H7" s="11" t="s">
+      <c r="H7" s="8" t="s">
         <v>73</v>
       </c>
-      <c r="I7" s="11" t="s">
+      <c r="I7" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="J7" s="11" t="s">
+      <c r="J7" s="8" t="s">
         <v>50</v>
       </c>
-      <c r="K7" s="11" t="s">
+      <c r="K7" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="L7" s="11" t="s">
+      <c r="L7" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="M7" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="N7" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="O7" s="8">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15" ht="199.5" customHeight="1">
+      <c r="A8" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="D8" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="E8" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="F8" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="G8" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="H8" s="5" t="s">
+        <v>98</v>
+      </c>
+      <c r="I8" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="J8" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="K8" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="L8" s="5" t="s">
         <v>79</v>
       </c>
-      <c r="M7" s="11" t="s">
+      <c r="M8" s="5" t="s">
         <v>82</v>
       </c>
-      <c r="N7" s="11" t="s">
-        <v>32</v>
-      </c>
-      <c r="O7" s="11">
-        <v>7.0</v>
-      </c>
-    </row>
-    <row r="8" ht="199.5" customHeight="1">
-      <c r="A8" s="7" t="s">
-        <v>35</v>
-      </c>
-      <c r="B8" s="7" t="s">
-        <v>88</v>
-      </c>
-      <c r="C8" s="8" t="s">
-        <v>38</v>
-      </c>
-      <c r="D8" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="E8" s="8" t="s">
-        <v>92</v>
-      </c>
-      <c r="F8" s="8" t="s">
-        <v>94</v>
-      </c>
-      <c r="G8" s="8" t="s">
-        <v>97</v>
-      </c>
-      <c r="H8" s="8" t="s">
-        <v>98</v>
-      </c>
-      <c r="I8" s="8" t="s">
+      <c r="N8" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="O8" s="5">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15" ht="145.5" customHeight="1">
+      <c r="A9" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="B9" s="7" t="s">
+        <v>108</v>
+      </c>
+      <c r="C9" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="D9" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="E9" s="8" t="s">
+        <v>113</v>
+      </c>
+      <c r="F9" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="G9" s="8" t="s">
+        <v>117</v>
+      </c>
+      <c r="H9" s="8" t="s">
+        <v>119</v>
+      </c>
+      <c r="I9" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="J8" s="8" t="s">
+      <c r="J9" s="8" t="s">
         <v>50</v>
       </c>
-      <c r="K8" s="8" t="s">
+      <c r="K9" s="8" t="s">
         <v>40</v>
       </c>
-      <c r="L8" s="8" t="s">
+      <c r="L9" s="8" t="s">
         <v>79</v>
       </c>
-      <c r="M8" s="8" t="s">
+      <c r="M9" s="8" t="s">
         <v>82</v>
       </c>
-      <c r="N8" s="8" t="s">
-        <v>39</v>
-      </c>
-      <c r="O8" s="8">
-        <v>10.0</v>
-      </c>
-    </row>
-    <row r="9" ht="145.5" customHeight="1">
-      <c r="A9" s="10" t="s">
-        <v>43</v>
-      </c>
-      <c r="B9" s="10" t="s">
-        <v>108</v>
-      </c>
-      <c r="C9" s="11" t="s">
-        <v>46</v>
-      </c>
-      <c r="D9" s="11" t="s">
-        <v>44</v>
-      </c>
-      <c r="E9" s="11" t="s">
-        <v>113</v>
-      </c>
-      <c r="F9" s="11" t="s">
-        <v>114</v>
-      </c>
-      <c r="G9" s="11" t="s">
-        <v>117</v>
-      </c>
-      <c r="H9" s="11" t="s">
-        <v>119</v>
-      </c>
-      <c r="I9" s="11" t="s">
+      <c r="N9" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="O9" s="8">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15" ht="217.5" customHeight="1">
+      <c r="A10" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="C10" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="D10" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="E10" s="5" t="s">
+        <v>134</v>
+      </c>
+      <c r="F10" s="5" t="s">
+        <v>137</v>
+      </c>
+      <c r="G10" s="5" t="s">
+        <v>138</v>
+      </c>
+      <c r="H10" s="5" t="s">
+        <v>139</v>
+      </c>
+      <c r="I10" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="J9" s="11" t="s">
+      <c r="J10" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="K9" s="11" t="s">
+      <c r="K10" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="L9" s="11" t="s">
+      <c r="L10" s="5" t="s">
         <v>79</v>
       </c>
-      <c r="M9" s="11" t="s">
+      <c r="M10" s="5" t="s">
         <v>82</v>
       </c>
-      <c r="N9" s="11" t="s">
-        <v>48</v>
-      </c>
-      <c r="O9" s="11">
-        <v>7.0</v>
-      </c>
-    </row>
-    <row r="10" ht="217.5" customHeight="1">
-      <c r="A10" s="7" t="s">
-        <v>51</v>
-      </c>
-      <c r="B10" s="7" t="s">
-        <v>129</v>
-      </c>
-      <c r="C10" s="8" t="s">
-        <v>54</v>
-      </c>
-      <c r="D10" s="8" t="s">
-        <v>52</v>
-      </c>
-      <c r="E10" s="8" t="s">
-        <v>134</v>
-      </c>
-      <c r="F10" s="8" t="s">
-        <v>137</v>
-      </c>
-      <c r="G10" s="8" t="s">
-        <v>138</v>
-      </c>
-      <c r="H10" s="8" t="s">
-        <v>139</v>
-      </c>
-      <c r="I10" s="8" t="s">
+      <c r="N10" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="O10" s="5">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15" ht="145.5" customHeight="1">
+      <c r="A11" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="B11" s="7" t="s">
+        <v>140</v>
+      </c>
+      <c r="C11" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="D11" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="E11" s="8" t="s">
+        <v>141</v>
+      </c>
+      <c r="F11" s="8" t="s">
+        <v>142</v>
+      </c>
+      <c r="G11" s="8" t="s">
+        <v>143</v>
+      </c>
+      <c r="H11" s="8" t="s">
+        <v>144</v>
+      </c>
+      <c r="I11" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="J10" s="8" t="s">
+      <c r="J11" s="8" t="s">
         <v>50</v>
       </c>
-      <c r="K10" s="8" t="s">
+      <c r="K11" s="8" t="s">
         <v>40</v>
       </c>
-      <c r="L10" s="8" t="s">
+      <c r="L11" s="8" t="s">
         <v>79</v>
       </c>
-      <c r="M10" s="8" t="s">
+      <c r="M11" s="8" t="s">
         <v>82</v>
       </c>
-      <c r="N10" s="8" t="s">
-        <v>55</v>
-      </c>
-      <c r="O10" s="8">
-        <v>11.0</v>
-      </c>
-    </row>
-    <row r="11" ht="145.5" customHeight="1">
-      <c r="A11" s="10" t="s">
-        <v>57</v>
-      </c>
-      <c r="B11" s="10" t="s">
-        <v>140</v>
-      </c>
-      <c r="C11" s="11" t="s">
-        <v>59</v>
-      </c>
-      <c r="D11" s="11" t="s">
-        <v>58</v>
-      </c>
-      <c r="E11" s="11" t="s">
-        <v>141</v>
-      </c>
-      <c r="F11" s="11" t="s">
-        <v>142</v>
-      </c>
-      <c r="G11" s="11" t="s">
-        <v>143</v>
-      </c>
-      <c r="H11" s="11" t="s">
-        <v>144</v>
-      </c>
-      <c r="I11" s="11" t="s">
+      <c r="N11" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="O11" s="8">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15" ht="127.5" customHeight="1">
+      <c r="A12" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="B12" s="4" t="s">
+        <v>145</v>
+      </c>
+      <c r="C12" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="D12" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="E12" s="5" t="s">
+        <v>146</v>
+      </c>
+      <c r="F12" s="5" t="s">
+        <v>147</v>
+      </c>
+      <c r="G12" s="5" t="s">
+        <v>148</v>
+      </c>
+      <c r="H12" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="I12" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="J11" s="11" t="s">
+      <c r="J12" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="K11" s="11" t="s">
+      <c r="K12" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="L12" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="M12" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="N12" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="O12" s="5">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15" ht="127.5" customHeight="1">
+      <c r="A13" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="B13" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="C13" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="D13" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="E13" s="8" t="s">
+        <v>151</v>
+      </c>
+      <c r="F13" s="8" t="s">
+        <v>152</v>
+      </c>
+      <c r="G13" s="8" t="s">
+        <v>153</v>
+      </c>
+      <c r="H13" s="8" t="s">
+        <v>154</v>
+      </c>
+      <c r="I13" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="J13" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="K13" s="8" t="s">
         <v>40</v>
       </c>
-      <c r="L11" s="11" t="s">
+      <c r="L13" s="8" t="s">
         <v>79</v>
       </c>
-      <c r="M11" s="11" t="s">
+      <c r="M13" s="8" t="s">
         <v>82</v>
       </c>
-      <c r="N11" s="11" t="s">
-        <v>60</v>
-      </c>
-      <c r="O11" s="11">
-        <v>7.0</v>
-      </c>
-    </row>
-    <row r="12" ht="127.5" customHeight="1">
-      <c r="A12" s="7" t="s">
-        <v>61</v>
-      </c>
-      <c r="B12" s="7" t="s">
-        <v>145</v>
-      </c>
-      <c r="C12" s="8" t="s">
-        <v>64</v>
-      </c>
-      <c r="D12" s="8" t="s">
-        <v>62</v>
-      </c>
-      <c r="E12" s="8" t="s">
-        <v>146</v>
-      </c>
-      <c r="F12" s="8" t="s">
-        <v>147</v>
-      </c>
-      <c r="G12" s="8" t="s">
-        <v>148</v>
-      </c>
-      <c r="H12" s="8" t="s">
-        <v>149</v>
-      </c>
-      <c r="I12" s="8" t="s">
+      <c r="N13" s="8" t="s">
+        <v>71</v>
+      </c>
+      <c r="O13" s="8">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15" ht="127.5" customHeight="1">
+      <c r="A14" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="B14" s="4" t="s">
+        <v>155</v>
+      </c>
+      <c r="C14" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="D14" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="E14" s="5" t="s">
+        <v>156</v>
+      </c>
+      <c r="F14" s="5" t="s">
+        <v>157</v>
+      </c>
+      <c r="G14" s="5" t="s">
+        <v>158</v>
+      </c>
+      <c r="H14" s="5" t="s">
+        <v>159</v>
+      </c>
+      <c r="I14" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="J12" s="8" t="s">
+      <c r="J14" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="K12" s="8" t="s">
+      <c r="K14" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="L12" s="8" t="s">
+      <c r="L14" s="5" t="s">
         <v>79</v>
       </c>
-      <c r="M12" s="8" t="s">
+      <c r="M14" s="5" t="s">
         <v>82</v>
       </c>
-      <c r="N12" s="8" t="s">
-        <v>65</v>
-      </c>
-      <c r="O12" s="8">
-        <v>6.0</v>
-      </c>
-    </row>
-    <row r="13" ht="127.5" customHeight="1">
-      <c r="A13" s="10" t="s">
-        <v>66</v>
-      </c>
-      <c r="B13" s="10" t="s">
-        <v>150</v>
-      </c>
-      <c r="C13" s="11" t="s">
-        <v>69</v>
-      </c>
-      <c r="D13" s="11" t="s">
-        <v>67</v>
-      </c>
-      <c r="E13" s="11" t="s">
-        <v>151</v>
-      </c>
-      <c r="F13" s="11" t="s">
-        <v>152</v>
-      </c>
-      <c r="G13" s="11" t="s">
-        <v>153</v>
-      </c>
-      <c r="H13" s="11" t="s">
-        <v>154</v>
-      </c>
-      <c r="I13" s="11" t="s">
+      <c r="N14" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="O14" s="5">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15" ht="109.5" customHeight="1">
+      <c r="A15" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="B15" s="7" t="s">
+        <v>162</v>
+      </c>
+      <c r="C15" s="8" t="s">
+        <v>81</v>
+      </c>
+      <c r="D15" s="8" t="s">
+        <v>80</v>
+      </c>
+      <c r="E15" s="8" t="s">
+        <v>169</v>
+      </c>
+      <c r="F15" s="8" t="s">
+        <v>170</v>
+      </c>
+      <c r="G15" s="8" t="s">
+        <v>171</v>
+      </c>
+      <c r="H15" s="8" t="s">
+        <v>172</v>
+      </c>
+      <c r="I15" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="J13" s="11" t="s">
+      <c r="J15" s="8" t="s">
         <v>50</v>
       </c>
-      <c r="K13" s="11" t="s">
-        <v>40</v>
-      </c>
-      <c r="L13" s="11" t="s">
+      <c r="K15" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="L15" s="8" t="s">
         <v>79</v>
       </c>
-      <c r="M13" s="11" t="s">
+      <c r="M15" s="8" t="s">
         <v>82</v>
       </c>
-      <c r="N13" s="11" t="s">
-        <v>71</v>
-      </c>
-      <c r="O13" s="11">
-        <v>6.0</v>
-      </c>
-    </row>
-    <row r="14" ht="127.5" customHeight="1">
-      <c r="A14" s="7" t="s">
-        <v>74</v>
-      </c>
-      <c r="B14" s="7" t="s">
-        <v>155</v>
-      </c>
-      <c r="C14" s="8" t="s">
-        <v>76</v>
-      </c>
-      <c r="D14" s="8" t="s">
-        <v>75</v>
-      </c>
-      <c r="E14" s="8" t="s">
-        <v>156</v>
-      </c>
-      <c r="F14" s="8" t="s">
-        <v>157</v>
-      </c>
-      <c r="G14" s="8" t="s">
-        <v>158</v>
-      </c>
-      <c r="H14" s="8" t="s">
-        <v>159</v>
-      </c>
-      <c r="I14" s="8" t="s">
+      <c r="N15" s="8" t="s">
+        <v>83</v>
+      </c>
+      <c r="O15" s="8">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15" ht="163.5" customHeight="1">
+      <c r="A16" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="B16" s="4" t="s">
+        <v>173</v>
+      </c>
+      <c r="C16" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="D16" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="E16" s="5" t="s">
+        <v>174</v>
+      </c>
+      <c r="F16" s="5" t="s">
+        <v>175</v>
+      </c>
+      <c r="G16" s="5" t="s">
+        <v>176</v>
+      </c>
+      <c r="H16" s="5" t="s">
+        <v>177</v>
+      </c>
+      <c r="I16" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="J14" s="8" t="s">
+      <c r="J16" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="K14" s="8" t="s">
+      <c r="K16" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="L16" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="M16" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="N16" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="O16" s="5">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="17" spans="1:15" ht="127.5" customHeight="1">
+      <c r="A17" s="7" t="s">
+        <v>91</v>
+      </c>
+      <c r="B17" s="7" t="s">
+        <v>178</v>
+      </c>
+      <c r="C17" s="8" t="s">
+        <v>95</v>
+      </c>
+      <c r="D17" s="8" t="s">
+        <v>93</v>
+      </c>
+      <c r="E17" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="F17" s="8" t="s">
+        <v>182</v>
+      </c>
+      <c r="G17" s="8" t="s">
+        <v>183</v>
+      </c>
+      <c r="H17" s="8" t="s">
+        <v>187</v>
+      </c>
+      <c r="I17" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="J17" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="K17" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="L17" s="8" t="s">
+        <v>79</v>
+      </c>
+      <c r="M17" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="N17" s="8" t="s">
+        <v>96</v>
+      </c>
+      <c r="O17" s="8">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="18" spans="1:15" ht="163.5" customHeight="1">
+      <c r="A18" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="B18" s="4" t="s">
+        <v>188</v>
+      </c>
+      <c r="C18" s="5" t="s">
+        <v>101</v>
+      </c>
+      <c r="D18" s="5" t="s">
+        <v>100</v>
+      </c>
+      <c r="E18" s="5" t="s">
+        <v>189</v>
+      </c>
+      <c r="F18" s="5" t="s">
+        <v>190</v>
+      </c>
+      <c r="G18" s="5" t="s">
+        <v>191</v>
+      </c>
+      <c r="H18" s="5" t="s">
+        <v>192</v>
+      </c>
+      <c r="I18" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="J18" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="K18" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="L18" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="M18" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="N18" s="5" t="s">
+        <v>102</v>
+      </c>
+      <c r="O18" s="5">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="19" spans="1:15" ht="145.5" customHeight="1">
+      <c r="A19" s="7" t="s">
+        <v>103</v>
+      </c>
+      <c r="B19" s="7" t="s">
+        <v>193</v>
+      </c>
+      <c r="C19" s="8" t="s">
+        <v>105</v>
+      </c>
+      <c r="D19" s="8" t="s">
+        <v>104</v>
+      </c>
+      <c r="E19" s="8" t="s">
+        <v>194</v>
+      </c>
+      <c r="F19" s="8" t="s">
+        <v>195</v>
+      </c>
+      <c r="G19" s="8" t="s">
+        <v>197</v>
+      </c>
+      <c r="H19" s="8" t="s">
+        <v>200</v>
+      </c>
+      <c r="I19" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="J19" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="K19" s="8" t="s">
+        <v>107</v>
+      </c>
+      <c r="L19" s="8" t="s">
+        <v>79</v>
+      </c>
+      <c r="M19" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="N19" s="8" t="s">
+        <v>106</v>
+      </c>
+      <c r="O19" s="8">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="20" spans="1:15" ht="145.5" customHeight="1">
+      <c r="A20" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="B20" s="4" t="s">
+        <v>202</v>
+      </c>
+      <c r="C20" s="5" t="s">
+        <v>111</v>
+      </c>
+      <c r="D20" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="E20" s="5" t="s">
+        <v>205</v>
+      </c>
+      <c r="F20" s="5" t="s">
+        <v>207</v>
+      </c>
+      <c r="G20" s="5" t="s">
+        <v>208</v>
+      </c>
+      <c r="H20" s="5" t="s">
+        <v>209</v>
+      </c>
+      <c r="I20" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="J20" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="K20" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="L20" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="M20" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="N20" s="5" t="s">
+        <v>112</v>
+      </c>
+      <c r="O20" s="5">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="21" spans="1:15" ht="163.5" customHeight="1">
+      <c r="A21" s="7" t="s">
+        <v>115</v>
+      </c>
+      <c r="B21" s="7" t="s">
+        <v>212</v>
+      </c>
+      <c r="C21" s="8" t="s">
+        <v>118</v>
+      </c>
+      <c r="D21" s="8" t="s">
+        <v>116</v>
+      </c>
+      <c r="E21" s="8" t="s">
+        <v>213</v>
+      </c>
+      <c r="F21" s="8" t="s">
+        <v>214</v>
+      </c>
+      <c r="G21" s="8" t="s">
+        <v>215</v>
+      </c>
+      <c r="H21" s="8" t="s">
+        <v>216</v>
+      </c>
+      <c r="I21" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="J21" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="K21" s="8" t="s">
+        <v>107</v>
+      </c>
+      <c r="L21" s="8" t="s">
+        <v>79</v>
+      </c>
+      <c r="M21" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="N21" s="8" t="s">
+        <v>120</v>
+      </c>
+      <c r="O21" s="8">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="22" spans="1:15" ht="127.5" customHeight="1">
+      <c r="A22" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="B22" s="4" t="s">
+        <v>217</v>
+      </c>
+      <c r="C22" s="5" t="s">
+        <v>123</v>
+      </c>
+      <c r="D22" s="5" t="s">
+        <v>122</v>
+      </c>
+      <c r="E22" s="5" t="s">
+        <v>218</v>
+      </c>
+      <c r="F22" s="5" t="s">
+        <v>219</v>
+      </c>
+      <c r="G22" s="5" t="s">
+        <v>220</v>
+      </c>
+      <c r="H22" s="5" t="s">
+        <v>221</v>
+      </c>
+      <c r="I22" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="J22" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="K22" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="L14" s="8" t="s">
+      <c r="L22" s="5" t="s">
         <v>79</v>
       </c>
-      <c r="M14" s="8" t="s">
+      <c r="M22" s="5" t="s">
         <v>82</v>
       </c>
-      <c r="N14" s="8" t="s">
-        <v>77</v>
-      </c>
-      <c r="O14" s="8">
-        <v>6.0</v>
-      </c>
-    </row>
-    <row r="15" ht="109.5" customHeight="1">
-      <c r="A15" s="10" t="s">
-        <v>78</v>
-      </c>
-      <c r="B15" s="10" t="s">
-        <v>162</v>
-      </c>
-      <c r="C15" s="11" t="s">
-        <v>81</v>
-      </c>
-      <c r="D15" s="11" t="s">
-        <v>80</v>
-      </c>
-      <c r="E15" s="11" t="s">
-        <v>169</v>
-      </c>
-      <c r="F15" s="11" t="s">
-        <v>170</v>
-      </c>
-      <c r="G15" s="11" t="s">
-        <v>171</v>
-      </c>
-      <c r="H15" s="11" t="s">
-        <v>172</v>
-      </c>
-      <c r="I15" s="11" t="s">
+      <c r="N22" s="5" t="s">
+        <v>124</v>
+      </c>
+      <c r="O22" s="5">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="23" spans="1:15" ht="145.5" customHeight="1">
+      <c r="A23" s="7" t="s">
+        <v>125</v>
+      </c>
+      <c r="B23" s="7" t="s">
+        <v>222</v>
+      </c>
+      <c r="C23" s="8" t="s">
+        <v>127</v>
+      </c>
+      <c r="D23" s="8" t="s">
+        <v>126</v>
+      </c>
+      <c r="E23" s="8" t="s">
+        <v>223</v>
+      </c>
+      <c r="F23" s="8" t="s">
+        <v>224</v>
+      </c>
+      <c r="G23" s="8" t="s">
+        <v>225</v>
+      </c>
+      <c r="H23" s="8" t="s">
+        <v>226</v>
+      </c>
+      <c r="I23" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="J15" s="11" t="s">
+      <c r="J23" s="8" t="s">
         <v>50</v>
       </c>
-      <c r="K15" s="11" t="s">
-        <v>84</v>
-      </c>
-      <c r="L15" s="11" t="s">
+      <c r="K23" s="8" t="s">
+        <v>107</v>
+      </c>
+      <c r="L23" s="8" t="s">
         <v>79</v>
       </c>
-      <c r="M15" s="11" t="s">
+      <c r="M23" s="8" t="s">
         <v>82</v>
       </c>
-      <c r="N15" s="11" t="s">
-        <v>83</v>
-      </c>
-      <c r="O15" s="11">
-        <v>5.0</v>
-      </c>
-    </row>
-    <row r="16" ht="163.5" customHeight="1">
-      <c r="A16" s="7" t="s">
-        <v>85</v>
-      </c>
-      <c r="B16" s="7" t="s">
-        <v>173</v>
-      </c>
-      <c r="C16" s="8" t="s">
-        <v>89</v>
-      </c>
-      <c r="D16" s="8" t="s">
-        <v>86</v>
-      </c>
-      <c r="E16" s="8" t="s">
-        <v>174</v>
-      </c>
-      <c r="F16" s="8" t="s">
-        <v>175</v>
-      </c>
-      <c r="G16" s="8" t="s">
-        <v>176</v>
-      </c>
-      <c r="H16" s="8" t="s">
-        <v>177</v>
-      </c>
-      <c r="I16" s="8" t="s">
-        <v>49</v>
-      </c>
-      <c r="J16" s="8" t="s">
-        <v>50</v>
-      </c>
-      <c r="K16" s="8" t="s">
-        <v>84</v>
-      </c>
-      <c r="L16" s="8" t="s">
-        <v>79</v>
-      </c>
-      <c r="M16" s="8" t="s">
-        <v>82</v>
-      </c>
-      <c r="N16" s="8" t="s">
-        <v>90</v>
-      </c>
-      <c r="O16" s="8">
-        <v>8.0</v>
-      </c>
-    </row>
-    <row r="17" ht="127.5" customHeight="1">
-      <c r="A17" s="10" t="s">
-        <v>91</v>
-      </c>
-      <c r="B17" s="10" t="s">
-        <v>178</v>
-      </c>
-      <c r="C17" s="11" t="s">
-        <v>95</v>
-      </c>
-      <c r="D17" s="11" t="s">
-        <v>93</v>
-      </c>
-      <c r="E17" s="11" t="s">
-        <v>180</v>
-      </c>
-      <c r="F17" s="11" t="s">
-        <v>182</v>
-      </c>
-      <c r="G17" s="11" t="s">
-        <v>183</v>
-      </c>
-      <c r="H17" s="11" t="s">
-        <v>187</v>
-      </c>
-      <c r="I17" s="11" t="s">
-        <v>49</v>
-      </c>
-      <c r="J17" s="11" t="s">
-        <v>50</v>
-      </c>
-      <c r="K17" s="11" t="s">
-        <v>84</v>
-      </c>
-      <c r="L17" s="11" t="s">
-        <v>79</v>
-      </c>
-      <c r="M17" s="11" t="s">
-        <v>82</v>
-      </c>
-      <c r="N17" s="11" t="s">
-        <v>96</v>
-      </c>
-      <c r="O17" s="11">
-        <v>6.0</v>
-      </c>
-    </row>
-    <row r="18" ht="163.5" customHeight="1">
-      <c r="A18" s="7" t="s">
-        <v>99</v>
-      </c>
-      <c r="B18" s="7" t="s">
-        <v>188</v>
-      </c>
-      <c r="C18" s="8" t="s">
-        <v>101</v>
-      </c>
-      <c r="D18" s="8" t="s">
-        <v>100</v>
-      </c>
-      <c r="E18" s="8" t="s">
-        <v>189</v>
-      </c>
-      <c r="F18" s="8" t="s">
-        <v>190</v>
-      </c>
-      <c r="G18" s="8" t="s">
-        <v>191</v>
-      </c>
-      <c r="H18" s="8" t="s">
-        <v>192</v>
-      </c>
-      <c r="I18" s="8" t="s">
-        <v>49</v>
-      </c>
-      <c r="J18" s="8" t="s">
-        <v>50</v>
-      </c>
-      <c r="K18" s="8" t="s">
-        <v>84</v>
-      </c>
-      <c r="L18" s="8" t="s">
-        <v>79</v>
-      </c>
-      <c r="M18" s="8" t="s">
-        <v>82</v>
-      </c>
-      <c r="N18" s="8" t="s">
-        <v>102</v>
-      </c>
-      <c r="O18" s="8">
-        <v>8.0</v>
-      </c>
-    </row>
-    <row r="19" ht="145.5" customHeight="1">
-      <c r="A19" s="10" t="s">
-        <v>103</v>
-      </c>
-      <c r="B19" s="10" t="s">
-        <v>193</v>
-      </c>
-      <c r="C19" s="11" t="s">
-        <v>105</v>
-      </c>
-      <c r="D19" s="11" t="s">
-        <v>104</v>
-      </c>
-      <c r="E19" s="11" t="s">
-        <v>194</v>
-      </c>
-      <c r="F19" s="11" t="s">
-        <v>195</v>
-      </c>
-      <c r="G19" s="11" t="s">
-        <v>197</v>
-      </c>
-      <c r="H19" s="11" t="s">
-        <v>200</v>
-      </c>
-      <c r="I19" s="11" t="s">
-        <v>49</v>
-      </c>
-      <c r="J19" s="11" t="s">
-        <v>50</v>
-      </c>
-      <c r="K19" s="11" t="s">
-        <v>107</v>
-      </c>
-      <c r="L19" s="11" t="s">
-        <v>79</v>
-      </c>
-      <c r="M19" s="11" t="s">
-        <v>82</v>
-      </c>
-      <c r="N19" s="11" t="s">
-        <v>106</v>
-      </c>
-      <c r="O19" s="11">
-        <v>7.0</v>
-      </c>
-    </row>
-    <row r="20" ht="145.5" customHeight="1">
-      <c r="A20" s="7" t="s">
-        <v>109</v>
-      </c>
-      <c r="B20" s="7" t="s">
-        <v>202</v>
-      </c>
-      <c r="C20" s="8" t="s">
-        <v>111</v>
-      </c>
-      <c r="D20" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="E20" s="8" t="s">
-        <v>205</v>
-      </c>
-      <c r="F20" s="8" t="s">
-        <v>207</v>
-      </c>
-      <c r="G20" s="8" t="s">
-        <v>208</v>
-      </c>
-      <c r="H20" s="8" t="s">
-        <v>209</v>
-      </c>
-      <c r="I20" s="8" t="s">
-        <v>49</v>
-      </c>
-      <c r="J20" s="8" t="s">
-        <v>50</v>
-      </c>
-      <c r="K20" s="8" t="s">
-        <v>107</v>
-      </c>
-      <c r="L20" s="8" t="s">
-        <v>79</v>
-      </c>
-      <c r="M20" s="8" t="s">
-        <v>82</v>
-      </c>
-      <c r="N20" s="8" t="s">
-        <v>112</v>
-      </c>
-      <c r="O20" s="8">
-        <v>7.0</v>
-      </c>
-    </row>
-    <row r="21" ht="163.5" customHeight="1">
-      <c r="A21" s="10" t="s">
-        <v>115</v>
-      </c>
-      <c r="B21" s="10" t="s">
-        <v>212</v>
-      </c>
-      <c r="C21" s="11" t="s">
-        <v>118</v>
-      </c>
-      <c r="D21" s="11" t="s">
-        <v>116</v>
-      </c>
-      <c r="E21" s="11" t="s">
-        <v>213</v>
-      </c>
-      <c r="F21" s="11" t="s">
-        <v>214</v>
-      </c>
-      <c r="G21" s="11" t="s">
-        <v>215</v>
-      </c>
-      <c r="H21" s="11" t="s">
-        <v>216</v>
-      </c>
-      <c r="I21" s="11" t="s">
-        <v>49</v>
-      </c>
-      <c r="J21" s="11" t="s">
-        <v>50</v>
-      </c>
-      <c r="K21" s="11" t="s">
-        <v>107</v>
-      </c>
-      <c r="L21" s="11" t="s">
-        <v>79</v>
-      </c>
-      <c r="M21" s="11" t="s">
-        <v>82</v>
-      </c>
-      <c r="N21" s="11" t="s">
-        <v>120</v>
-      </c>
-      <c r="O21" s="11">
-        <v>8.0</v>
-      </c>
-    </row>
-    <row r="22" ht="127.5" customHeight="1">
-      <c r="A22" s="7" t="s">
-        <v>121</v>
-      </c>
-      <c r="B22" s="7" t="s">
-        <v>217</v>
-      </c>
-      <c r="C22" s="8" t="s">
-        <v>123</v>
-      </c>
-      <c r="D22" s="8" t="s">
-        <v>122</v>
-      </c>
-      <c r="E22" s="8" t="s">
-        <v>218</v>
-      </c>
-      <c r="F22" s="8" t="s">
-        <v>219</v>
-      </c>
-      <c r="G22" s="8" t="s">
-        <v>220</v>
-      </c>
-      <c r="H22" s="8" t="s">
-        <v>221</v>
-      </c>
-      <c r="I22" s="8" t="s">
-        <v>49</v>
-      </c>
-      <c r="J22" s="8" t="s">
-        <v>50</v>
-      </c>
-      <c r="K22" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="L22" s="8" t="s">
-        <v>79</v>
-      </c>
-      <c r="M22" s="8" t="s">
-        <v>82</v>
-      </c>
-      <c r="N22" s="8" t="s">
-        <v>124</v>
-      </c>
-      <c r="O22" s="8">
-        <v>6.0</v>
-      </c>
-    </row>
-    <row r="23" ht="145.5" customHeight="1">
-      <c r="A23" s="10" t="s">
-        <v>125</v>
-      </c>
-      <c r="B23" s="10" t="s">
-        <v>222</v>
-      </c>
-      <c r="C23" s="11" t="s">
-        <v>127</v>
-      </c>
-      <c r="D23" s="11" t="s">
-        <v>126</v>
-      </c>
-      <c r="E23" s="11" t="s">
-        <v>223</v>
-      </c>
-      <c r="F23" s="11" t="s">
-        <v>224</v>
-      </c>
-      <c r="G23" s="11" t="s">
-        <v>225</v>
-      </c>
-      <c r="H23" s="11" t="s">
-        <v>226</v>
-      </c>
-      <c r="I23" s="11" t="s">
-        <v>49</v>
-      </c>
-      <c r="J23" s="11" t="s">
-        <v>50</v>
-      </c>
-      <c r="K23" s="11" t="s">
-        <v>107</v>
-      </c>
-      <c r="L23" s="11" t="s">
-        <v>79</v>
-      </c>
-      <c r="M23" s="11" t="s">
-        <v>82</v>
-      </c>
-      <c r="N23" s="11" t="s">
+      <c r="N23" s="8" t="s">
         <v>128</v>
       </c>
-      <c r="O23" s="11">
-        <v>7.0</v>
-      </c>
-    </row>
-    <row r="24" ht="57.0" customHeight="1">
-      <c r="A24" s="7" t="s">
+      <c r="O23" s="8">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="24" spans="1:15" ht="57" customHeight="1">
+      <c r="A24" s="4" t="s">
         <v>130</v>
       </c>
-      <c r="B24" s="7" t="s">
+      <c r="B24" s="4" t="s">
         <v>227</v>
       </c>
-      <c r="C24" s="8" t="s">
+      <c r="C24" s="5" t="s">
         <v>132</v>
       </c>
-      <c r="D24" s="8" t="s">
+      <c r="D24" s="5" t="s">
         <v>131</v>
       </c>
-      <c r="E24" s="8" t="s">
+      <c r="E24" s="5" t="s">
         <v>228</v>
       </c>
-      <c r="F24" s="8" t="s">
+      <c r="F24" s="5" t="s">
         <v>229</v>
       </c>
-      <c r="G24" s="8" t="s">
+      <c r="G24" s="5" t="s">
         <v>230</v>
       </c>
-      <c r="H24" s="8" t="s">
+      <c r="H24" s="5" t="s">
         <v>230</v>
       </c>
-      <c r="I24" s="8" t="s">
+      <c r="I24" s="5" t="s">
         <v>136</v>
       </c>
-      <c r="J24" s="8" t="s">
+      <c r="J24" s="5" t="s">
         <v>231</v>
       </c>
-      <c r="K24" s="8" t="s">
+      <c r="K24" s="5" t="s">
         <v>135</v>
       </c>
-      <c r="L24" s="8" t="s">
+      <c r="L24" s="5" t="s">
         <v>136</v>
       </c>
-      <c r="M24" s="8" t="s">
+      <c r="M24" s="5" t="s">
         <v>136</v>
       </c>
-      <c r="N24" s="8" t="s">
+      <c r="N24" s="5" t="s">
         <v>133</v>
       </c>
-      <c r="O24" s="8">
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="25" ht="144.0" customHeight="1">
-      <c r="L25" s="25"/>
-      <c r="M25" s="25"/>
-    </row>
-    <row r="26" ht="166.5" customHeight="1">
-      <c r="L26" s="25"/>
-      <c r="M26" s="25"/>
-    </row>
-    <row r="27" ht="189.75" customHeight="1">
-      <c r="L27" s="25"/>
-      <c r="M27" s="25"/>
-    </row>
-    <row r="28" ht="189.75" customHeight="1">
-      <c r="L28" s="25"/>
-      <c r="M28" s="25"/>
-      <c r="N28" s="25"/>
-    </row>
-    <row r="29" ht="213.0" customHeight="1">
-      <c r="L29" s="25"/>
-      <c r="M29" s="25"/>
-    </row>
-    <row r="30" ht="235.5" customHeight="1">
-      <c r="L30" s="25"/>
-      <c r="M30" s="25"/>
-      <c r="N30" s="25"/>
-    </row>
-    <row r="31" ht="189.75" customHeight="1">
-      <c r="L31" s="25"/>
-      <c r="M31" s="25"/>
-    </row>
-    <row r="32" ht="166.5" customHeight="1">
-      <c r="L32" s="25"/>
-      <c r="M32" s="25"/>
-    </row>
-    <row r="33" ht="189.75" customHeight="1">
-      <c r="L33" s="25"/>
-      <c r="M33" s="25"/>
-      <c r="N33" s="25"/>
-    </row>
-    <row r="34" ht="189.75" customHeight="1">
-      <c r="L34" s="25"/>
-      <c r="M34" s="25"/>
-    </row>
-    <row r="35" ht="189.75" customHeight="1">
-      <c r="L35" s="25"/>
-      <c r="M35" s="25"/>
-    </row>
-    <row r="36" ht="144.0" customHeight="1">
-      <c r="L36" s="25"/>
-      <c r="M36" s="25"/>
-      <c r="N36" s="25"/>
-    </row>
-    <row r="37" ht="144.0" customHeight="1">
-      <c r="L37" s="25"/>
-      <c r="M37" s="25"/>
-    </row>
-    <row r="38" ht="166.5" customHeight="1">
-      <c r="L38" s="25"/>
-      <c r="M38" s="25"/>
-    </row>
-    <row r="39" ht="166.5" customHeight="1">
-      <c r="L39" s="25"/>
-      <c r="M39" s="25"/>
-      <c r="N39" s="25"/>
-    </row>
-    <row r="40" ht="166.5" customHeight="1">
-      <c r="L40" s="25"/>
-      <c r="M40" s="25"/>
-    </row>
-    <row r="41" ht="144.0" customHeight="1">
-      <c r="L41" s="25"/>
-      <c r="M41" s="25"/>
-    </row>
-    <row r="42" ht="189.75" customHeight="1">
-      <c r="L42" s="25"/>
-      <c r="M42" s="25"/>
-      <c r="N42" s="25"/>
-    </row>
-    <row r="43" ht="166.5" customHeight="1">
-      <c r="L43" s="25"/>
-      <c r="M43" s="25"/>
-    </row>
-    <row r="44" ht="189.75" customHeight="1">
-      <c r="L44" s="25"/>
-      <c r="M44" s="25"/>
-    </row>
-    <row r="45" ht="189.75" customHeight="1">
-      <c r="L45" s="25"/>
-      <c r="M45" s="25"/>
-      <c r="N45" s="25"/>
-    </row>
-    <row r="46" ht="144.0" customHeight="1">
-      <c r="L46" s="25"/>
-      <c r="M46" s="25"/>
-    </row>
-    <row r="47" ht="189.75" customHeight="1">
-      <c r="L47" s="25"/>
-      <c r="M47" s="25"/>
-    </row>
-    <row r="48" ht="213.0" customHeight="1">
-      <c r="L48" s="25"/>
-      <c r="M48" s="25"/>
-    </row>
-    <row r="49" ht="189.75" customHeight="1">
-      <c r="L49" s="25"/>
-      <c r="M49" s="25"/>
-      <c r="N49" s="25"/>
-    </row>
-    <row r="50" ht="189.75" customHeight="1">
-      <c r="L50" s="25"/>
-      <c r="M50" s="25"/>
-    </row>
-    <row r="51" ht="189.75" customHeight="1">
-      <c r="L51" s="25"/>
-      <c r="M51" s="25"/>
-      <c r="N51" s="25"/>
-    </row>
-    <row r="52" ht="189.75" customHeight="1">
-      <c r="L52" s="25"/>
-      <c r="M52" s="25"/>
-    </row>
-    <row r="53" ht="189.75" customHeight="1">
-      <c r="L53" s="25"/>
-      <c r="M53" s="25"/>
-    </row>
-    <row r="54" ht="189.75" customHeight="1">
-      <c r="L54" s="25"/>
-      <c r="M54" s="25"/>
-    </row>
-    <row r="55" ht="189.75" customHeight="1">
-      <c r="L55" s="25"/>
-      <c r="M55" s="25"/>
-    </row>
-    <row r="56" ht="189.75" customHeight="1">
-      <c r="L56" s="25"/>
-      <c r="M56" s="25"/>
-      <c r="N56" s="25"/>
-    </row>
-    <row r="57" ht="189.75" customHeight="1">
-      <c r="L57" s="25"/>
-      <c r="M57" s="25"/>
-    </row>
-    <row r="58" ht="189.75" customHeight="1">
-      <c r="L58" s="25"/>
-      <c r="M58" s="25"/>
-    </row>
-    <row r="59" ht="189.75" customHeight="1">
-      <c r="L59" s="25"/>
-      <c r="M59" s="25"/>
-    </row>
-    <row r="60" ht="189.75" customHeight="1">
-      <c r="L60" s="25"/>
-      <c r="M60" s="25"/>
-    </row>
-    <row r="61" ht="189.75" customHeight="1">
-      <c r="L61" s="25"/>
-      <c r="M61" s="25"/>
-      <c r="N61" s="25"/>
-    </row>
-    <row r="62" ht="189.75" customHeight="1">
-      <c r="L62" s="25"/>
-      <c r="M62" s="25"/>
-    </row>
-    <row r="63" ht="189.75" customHeight="1">
-      <c r="L63" s="25"/>
-      <c r="M63" s="25"/>
-    </row>
-    <row r="64" ht="144.0" customHeight="1">
-      <c r="L64" s="25"/>
-      <c r="M64" s="25"/>
-      <c r="N64" s="25"/>
-    </row>
-    <row r="65" ht="189.75" customHeight="1">
-      <c r="L65" s="25"/>
-      <c r="M65" s="25"/>
-    </row>
-    <row r="66" ht="189.75" customHeight="1">
-      <c r="L66" s="25"/>
-      <c r="M66" s="25"/>
-    </row>
-    <row r="67" ht="189.75" customHeight="1">
-      <c r="L67" s="25"/>
-      <c r="M67" s="25"/>
-    </row>
-    <row r="68" ht="189.75" customHeight="1">
-      <c r="L68" s="25"/>
-      <c r="M68" s="25"/>
-    </row>
-    <row r="69" ht="189.75" customHeight="1">
-      <c r="L69" s="25"/>
-      <c r="M69" s="25"/>
-    </row>
-    <row r="70" ht="166.5" customHeight="1">
-      <c r="L70" s="25"/>
-      <c r="M70" s="25"/>
-      <c r="N70" s="25"/>
-    </row>
-    <row r="71" ht="189.75" customHeight="1">
-      <c r="L71" s="25"/>
-      <c r="M71" s="25"/>
-      <c r="N71" s="25"/>
-    </row>
-    <row r="72" ht="189.75" customHeight="1">
-      <c r="L72" s="25"/>
-      <c r="M72" s="25"/>
-    </row>
-    <row r="73" ht="189.75" customHeight="1">
-      <c r="L73" s="25"/>
-      <c r="M73" s="25"/>
-    </row>
-    <row r="74" ht="189.75" customHeight="1">
-      <c r="L74" s="25"/>
-      <c r="M74" s="25"/>
-    </row>
-    <row r="75" ht="189.75" customHeight="1">
-      <c r="L75" s="25"/>
-      <c r="M75" s="25"/>
-    </row>
-    <row r="76" ht="189.75" customHeight="1">
-      <c r="L76" s="25"/>
-      <c r="M76" s="25"/>
-    </row>
-    <row r="77" ht="166.5" customHeight="1">
-      <c r="L77" s="25"/>
-      <c r="M77" s="25"/>
-      <c r="N77" s="25"/>
-    </row>
-    <row r="78" ht="166.5" customHeight="1">
-      <c r="L78" s="25"/>
-      <c r="M78" s="25"/>
-    </row>
-    <row r="79" ht="189.75" customHeight="1">
-      <c r="L79" s="25"/>
-      <c r="M79" s="25"/>
-    </row>
-    <row r="80" ht="166.5" customHeight="1">
-      <c r="L80" s="25"/>
-      <c r="M80" s="25"/>
-      <c r="N80" s="25"/>
-    </row>
-    <row r="81" ht="189.75" customHeight="1">
-      <c r="L81" s="25"/>
-      <c r="M81" s="25"/>
-    </row>
-    <row r="82" ht="189.75" customHeight="1">
-      <c r="L82" s="25"/>
-      <c r="M82" s="25"/>
-    </row>
-    <row r="83" ht="189.75" customHeight="1">
-      <c r="L83" s="25"/>
-      <c r="M83" s="25"/>
-    </row>
-    <row r="84" ht="213.0" customHeight="1">
-      <c r="L84" s="25"/>
-      <c r="M84" s="25"/>
-      <c r="N84" s="25"/>
-    </row>
-    <row r="85" ht="36.0" customHeight="1"/>
-    <row r="86" ht="36.0" customHeight="1"/>
-    <row r="87" ht="36.0" customHeight="1"/>
-    <row r="88" ht="36.0" customHeight="1">
-      <c r="M88" s="25"/>
-      <c r="N88" s="25"/>
-    </row>
-    <row r="89" ht="36.0" customHeight="1"/>
-    <row r="90" ht="36.0" customHeight="1"/>
-    <row r="91" ht="36.0" customHeight="1">
-      <c r="M91" s="25"/>
-      <c r="N91" s="25"/>
-    </row>
-    <row r="92" ht="36.0" customHeight="1"/>
-    <row r="93" ht="36.0" customHeight="1"/>
-    <row r="94" ht="36.0" customHeight="1"/>
-    <row r="95" ht="36.0" customHeight="1"/>
-    <row r="96" ht="36.0" customHeight="1"/>
-    <row r="97" ht="36.0" customHeight="1">
-      <c r="M97" s="25"/>
-      <c r="N97" s="25"/>
-    </row>
-    <row r="98" ht="36.0" customHeight="1"/>
-    <row r="99" ht="36.0" customHeight="1"/>
-    <row r="100" ht="36.0" customHeight="1"/>
-    <row r="101" ht="36.0" customHeight="1"/>
-    <row r="102" ht="36.0" customHeight="1">
-      <c r="M102" s="25"/>
-      <c r="N102" s="25"/>
-    </row>
-    <row r="103" ht="36.0" customHeight="1"/>
-    <row r="104" ht="36.0" customHeight="1"/>
-    <row r="105" ht="36.0" customHeight="1">
-      <c r="M105" s="25"/>
-      <c r="N105" s="25"/>
-    </row>
-    <row r="106" ht="36.0" customHeight="1"/>
-    <row r="107" ht="36.0" customHeight="1"/>
-    <row r="108" ht="36.0" customHeight="1">
-      <c r="M108" s="25"/>
-      <c r="N108" s="25"/>
-    </row>
-    <row r="109" ht="36.0" customHeight="1"/>
-    <row r="110" ht="36.0" customHeight="1"/>
-    <row r="111" ht="36.0" customHeight="1"/>
-    <row r="112" ht="36.0" customHeight="1">
-      <c r="M112" s="25"/>
-      <c r="N112" s="25"/>
-    </row>
-    <row r="113" ht="36.0" customHeight="1"/>
-    <row r="114" ht="36.0" customHeight="1">
-      <c r="M114" s="25"/>
-      <c r="N114" s="25"/>
-    </row>
-    <row r="115" ht="36.0" customHeight="1"/>
-    <row r="116" ht="36.0" customHeight="1"/>
-    <row r="117" ht="36.0" customHeight="1"/>
-    <row r="118" ht="36.0" customHeight="1">
-      <c r="M118" s="25"/>
-      <c r="N118" s="25"/>
-    </row>
-    <row r="119" ht="36.0" customHeight="1"/>
-    <row r="120" ht="36.0" customHeight="1">
-      <c r="M120" s="25"/>
-      <c r="N120" s="25"/>
-    </row>
-    <row r="121" ht="36.0" customHeight="1"/>
-    <row r="122" ht="36.0" customHeight="1"/>
-    <row r="123" ht="36.0" customHeight="1"/>
-    <row r="124" ht="36.0" customHeight="1"/>
-    <row r="125" ht="36.0" customHeight="1">
-      <c r="M125" s="25"/>
-      <c r="N125" s="25"/>
-    </row>
-    <row r="126" ht="36.0" customHeight="1"/>
-    <row r="127" ht="36.0" customHeight="1"/>
-    <row r="128" ht="36.0" customHeight="1"/>
-    <row r="129" ht="36.0" customHeight="1"/>
-    <row r="130" ht="36.0" customHeight="1"/>
-    <row r="131" ht="36.0" customHeight="1">
-      <c r="M131" s="25"/>
-      <c r="N131" s="25"/>
-    </row>
-    <row r="132" ht="36.0" customHeight="1">
-      <c r="M132" s="25"/>
-      <c r="N132" s="25"/>
-    </row>
-    <row r="133" ht="36.0" customHeight="1"/>
-    <row r="134" ht="36.0" customHeight="1"/>
-    <row r="135" ht="36.0" customHeight="1"/>
-    <row r="136" ht="36.0" customHeight="1"/>
-    <row r="137" ht="36.0" customHeight="1">
-      <c r="M137" s="25"/>
-      <c r="N137" s="25"/>
-    </row>
-    <row r="138" ht="36.0" customHeight="1"/>
-    <row r="139" ht="36.0" customHeight="1">
-      <c r="M139" s="25"/>
-      <c r="N139" s="25"/>
-    </row>
-    <row r="140" ht="36.0" customHeight="1"/>
-    <row r="141" ht="36.0" customHeight="1"/>
-    <row r="142" ht="36.0" customHeight="1"/>
-    <row r="143" ht="36.0" customHeight="1">
-      <c r="M143" s="25"/>
-      <c r="N143" s="25"/>
-    </row>
-    <row r="144" ht="36.0" customHeight="1">
-      <c r="M144" s="25"/>
-      <c r="N144" s="25"/>
-    </row>
-    <row r="145" ht="36.0" customHeight="1"/>
-    <row r="146" ht="36.0" customHeight="1"/>
-    <row r="147" ht="36.0" customHeight="1"/>
-    <row r="148" ht="36.0" customHeight="1"/>
-    <row r="149" ht="36.0" customHeight="1">
-      <c r="M149" s="25"/>
-      <c r="N149" s="25"/>
-    </row>
-    <row r="150" ht="36.0" customHeight="1">
-      <c r="M150" s="25"/>
-      <c r="N150" s="25"/>
-    </row>
-    <row r="151" ht="36.0" customHeight="1"/>
-    <row r="152" ht="36.0" customHeight="1"/>
-    <row r="153" ht="36.0" customHeight="1"/>
-    <row r="154" ht="36.0" customHeight="1"/>
-    <row r="155" ht="36.0" customHeight="1"/>
-    <row r="156" ht="36.0" customHeight="1">
-      <c r="M156" s="25"/>
-      <c r="N156" s="25"/>
-    </row>
-    <row r="157" ht="36.0" customHeight="1">
-      <c r="M157" s="25"/>
-      <c r="N157" s="25"/>
-    </row>
-    <row r="158" ht="36.0" customHeight="1"/>
-    <row r="159" ht="36.0" customHeight="1"/>
-    <row r="160" ht="36.0" customHeight="1"/>
-    <row r="161" ht="36.0" customHeight="1"/>
-    <row r="162" ht="36.0" customHeight="1">
-      <c r="M162" s="25"/>
-      <c r="N162" s="25"/>
-    </row>
-    <row r="163" ht="36.0" customHeight="1"/>
-    <row r="164" ht="36.0" customHeight="1">
-      <c r="M164" s="25"/>
-      <c r="N164" s="25"/>
-    </row>
-    <row r="165" ht="36.0" customHeight="1"/>
-    <row r="166" ht="36.0" customHeight="1"/>
-    <row r="167" ht="36.0" customHeight="1">
-      <c r="M167" s="25"/>
-      <c r="N167" s="25"/>
-    </row>
-    <row r="168" ht="36.0" customHeight="1"/>
-    <row r="169" ht="36.0" customHeight="1"/>
-    <row r="170" ht="36.0" customHeight="1"/>
-    <row r="171" ht="36.0" customHeight="1"/>
-    <row r="172" ht="36.0" customHeight="1">
-      <c r="M172" s="25"/>
-      <c r="N172" s="25"/>
-    </row>
-    <row r="173" ht="36.0" customHeight="1">
-      <c r="M173" s="25"/>
-      <c r="N173" s="25"/>
-    </row>
-    <row r="174" ht="36.0" customHeight="1"/>
-    <row r="175" ht="36.0" customHeight="1"/>
-    <row r="176" ht="36.0" customHeight="1"/>
-    <row r="177" ht="36.0" customHeight="1"/>
-    <row r="178" ht="36.0" customHeight="1"/>
-    <row r="179" ht="36.0" customHeight="1">
-      <c r="M179" s="25"/>
-      <c r="N179" s="25"/>
-    </row>
-    <row r="180" ht="36.0" customHeight="1"/>
-    <row r="181" ht="36.0" customHeight="1">
-      <c r="M181" s="25"/>
-      <c r="N181" s="25"/>
-    </row>
-    <row r="182" ht="36.0" customHeight="1"/>
-    <row r="183" ht="36.0" customHeight="1"/>
-    <row r="184" ht="36.0" customHeight="1"/>
-    <row r="185" ht="36.0" customHeight="1">
-      <c r="M185" s="25"/>
-      <c r="N185" s="25"/>
-    </row>
-    <row r="186" ht="36.0" customHeight="1"/>
-    <row r="187" ht="36.0" customHeight="1"/>
-    <row r="188" ht="36.0" customHeight="1">
-      <c r="M188" s="25"/>
-      <c r="N188" s="25"/>
-    </row>
-    <row r="189" ht="36.0" customHeight="1"/>
-    <row r="190" ht="36.0" customHeight="1">
-      <c r="M190" s="25"/>
-      <c r="N190" s="25"/>
-    </row>
-    <row r="191" ht="36.0" customHeight="1"/>
-    <row r="192" ht="36.0" customHeight="1"/>
-    <row r="193" ht="36.0" customHeight="1"/>
-    <row r="194" ht="36.0" customHeight="1">
-      <c r="M194" s="25"/>
-      <c r="N194" s="25"/>
-    </row>
-    <row r="195" ht="36.0" customHeight="1">
-      <c r="M195" s="25"/>
-      <c r="N195" s="25"/>
-    </row>
-    <row r="196" ht="36.0" customHeight="1"/>
-    <row r="197" ht="36.0" customHeight="1"/>
-    <row r="198" ht="36.0" customHeight="1"/>
-    <row r="199" ht="36.0" customHeight="1"/>
-    <row r="200" ht="36.0" customHeight="1"/>
-    <row r="201" ht="36.0" customHeight="1">
-      <c r="M201" s="25"/>
-      <c r="N201" s="25"/>
-    </row>
-    <row r="202" ht="36.0" customHeight="1"/>
-    <row r="203" ht="36.0" customHeight="1"/>
-    <row r="204" ht="36.0" customHeight="1"/>
-    <row r="205" ht="36.0" customHeight="1"/>
-    <row r="206" ht="36.0" customHeight="1">
-      <c r="M206" s="25"/>
-      <c r="N206" s="25"/>
-    </row>
-    <row r="207" ht="36.0" customHeight="1"/>
-    <row r="208" ht="36.0" customHeight="1">
-      <c r="M208" s="25"/>
-      <c r="N208" s="25"/>
-    </row>
-    <row r="209" ht="36.0" customHeight="1"/>
-    <row r="210" ht="36.0" customHeight="1"/>
-    <row r="211" ht="36.0" customHeight="1"/>
-    <row r="212" ht="36.0" customHeight="1">
-      <c r="M212" s="25"/>
-      <c r="N212" s="25"/>
-    </row>
-    <row r="213" ht="36.0" customHeight="1"/>
-    <row r="214" ht="36.0" customHeight="1"/>
-    <row r="215" ht="36.0" customHeight="1">
-      <c r="M215" s="25"/>
-      <c r="N215" s="25"/>
-    </row>
-    <row r="216" ht="36.0" customHeight="1"/>
-    <row r="217" ht="36.0" customHeight="1">
-      <c r="M217" s="25"/>
-      <c r="N217" s="25"/>
-    </row>
-    <row r="218" ht="36.0" customHeight="1"/>
-    <row r="219" ht="36.0" customHeight="1"/>
-    <row r="220" ht="36.0" customHeight="1">
-      <c r="M220" s="25"/>
-      <c r="N220" s="25"/>
-    </row>
-    <row r="221" ht="36.0" customHeight="1"/>
-    <row r="222" ht="36.0" customHeight="1"/>
-    <row r="223" ht="36.0" customHeight="1">
-      <c r="M223" s="25"/>
-      <c r="N223" s="25"/>
-    </row>
-    <row r="224" ht="36.0" customHeight="1"/>
-    <row r="225" ht="15.75" customHeight="1">
-      <c r="M225" s="25"/>
-      <c r="N225" s="25"/>
-    </row>
-    <row r="226" ht="15.75" customHeight="1"/>
-    <row r="227" ht="15.75" customHeight="1"/>
-    <row r="228" ht="15.75" customHeight="1">
-      <c r="M228" s="25"/>
-      <c r="N228" s="25"/>
-    </row>
-    <row r="229" ht="15.75" customHeight="1"/>
-    <row r="230" ht="15.75" customHeight="1"/>
-    <row r="231" ht="15.75" customHeight="1">
-      <c r="M231" s="25"/>
-      <c r="N231" s="25"/>
-    </row>
-    <row r="232" ht="15.75" customHeight="1"/>
-    <row r="233" ht="15.75" customHeight="1"/>
-    <row r="234" ht="15.75" customHeight="1">
-      <c r="M234" s="25"/>
-      <c r="N234" s="25"/>
-    </row>
-    <row r="235" ht="15.75" customHeight="1"/>
-    <row r="236" ht="15.75" customHeight="1"/>
-    <row r="237" ht="15.75" customHeight="1">
-      <c r="M237" s="25"/>
-      <c r="N237" s="25"/>
-    </row>
-    <row r="238" ht="15.75" customHeight="1"/>
-    <row r="239" ht="15.75" customHeight="1"/>
-    <row r="240" ht="15.75" customHeight="1">
-      <c r="M240" s="25"/>
-      <c r="N240" s="25"/>
-    </row>
-    <row r="241" ht="15.75" customHeight="1"/>
-    <row r="242" ht="15.75" customHeight="1"/>
-    <row r="243" ht="15.75" customHeight="1">
-      <c r="M243" s="25"/>
-      <c r="N243" s="25"/>
-    </row>
-    <row r="244" ht="15.75" customHeight="1"/>
-    <row r="245" ht="15.75" customHeight="1"/>
-    <row r="246" ht="15.75" customHeight="1">
-      <c r="M246" s="25"/>
-      <c r="N246" s="25"/>
-    </row>
-    <row r="247" ht="15.75" customHeight="1"/>
-    <row r="248" ht="15.75" customHeight="1">
-      <c r="M248" s="25"/>
-      <c r="N248" s="25"/>
-    </row>
-    <row r="249" ht="15.75" customHeight="1"/>
-    <row r="250" ht="15.75" customHeight="1"/>
-    <row r="251" ht="15.75" customHeight="1"/>
-    <row r="252" ht="15.75" customHeight="1">
-      <c r="M252" s="25"/>
-      <c r="N252" s="25"/>
-    </row>
-    <row r="253" ht="15.75" customHeight="1"/>
-    <row r="254" ht="15.75" customHeight="1"/>
-    <row r="255" ht="15.75" customHeight="1">
-      <c r="M255" s="25"/>
-      <c r="N255" s="25"/>
-    </row>
-    <row r="256" ht="15.75" customHeight="1"/>
-    <row r="257" ht="15.75" customHeight="1"/>
-    <row r="258" ht="15.75" customHeight="1"/>
-    <row r="259" ht="15.75" customHeight="1">
-      <c r="M259" s="25"/>
-      <c r="N259" s="25"/>
-    </row>
-    <row r="260" ht="15.75" customHeight="1"/>
-    <row r="261" ht="15.75" customHeight="1">
-      <c r="M261" s="25"/>
-      <c r="N261" s="25"/>
-    </row>
-    <row r="262" ht="15.75" customHeight="1"/>
-    <row r="263" ht="15.75" customHeight="1"/>
-    <row r="264" ht="15.75" customHeight="1"/>
-    <row r="265" ht="15.75" customHeight="1">
-      <c r="M265" s="25"/>
-      <c r="N265" s="25"/>
-    </row>
-    <row r="266" ht="15.75" customHeight="1"/>
-    <row r="267" ht="15.75" customHeight="1"/>
-    <row r="268" ht="15.75" customHeight="1">
-      <c r="M268" s="25"/>
-      <c r="N268" s="25"/>
-    </row>
-    <row r="269" ht="15.75" customHeight="1"/>
-    <row r="270" ht="15.75" customHeight="1"/>
-    <row r="271" ht="15.75" customHeight="1">
-      <c r="M271" s="25"/>
-      <c r="N271" s="25"/>
-    </row>
-    <row r="272" ht="15.75" customHeight="1"/>
-    <row r="273" ht="15.75" customHeight="1"/>
-    <row r="274" ht="15.75" customHeight="1"/>
-    <row r="275" ht="15.75" customHeight="1">
-      <c r="M275" s="25"/>
-      <c r="N275" s="25"/>
-    </row>
-    <row r="276" ht="15.75" customHeight="1"/>
-    <row r="277" ht="15.75" customHeight="1">
-      <c r="M277" s="25"/>
-      <c r="N277" s="25"/>
-    </row>
-    <row r="278" ht="15.75" customHeight="1"/>
-    <row r="279" ht="15.75" customHeight="1"/>
-    <row r="280" ht="15.75" customHeight="1">
-      <c r="M280" s="25"/>
-      <c r="N280" s="25"/>
-    </row>
-    <row r="281" ht="15.75" customHeight="1"/>
-    <row r="282" ht="15.75" customHeight="1"/>
-    <row r="283" ht="15.75" customHeight="1">
-      <c r="M283" s="25"/>
-      <c r="N283" s="25"/>
-    </row>
-    <row r="284" ht="15.75" customHeight="1"/>
-    <row r="285" ht="15.75" customHeight="1"/>
-    <row r="286" ht="15.75" customHeight="1"/>
-    <row r="287" ht="15.75" customHeight="1">
-      <c r="M287" s="25"/>
-      <c r="N287" s="25"/>
-    </row>
-    <row r="288" ht="15.75" customHeight="1"/>
-    <row r="289" ht="15.75" customHeight="1">
-      <c r="M289" s="25"/>
-      <c r="N289" s="25"/>
-    </row>
-    <row r="290" ht="15.75" customHeight="1"/>
-    <row r="291" ht="15.75" customHeight="1"/>
-    <row r="292" ht="15.75" customHeight="1"/>
-    <row r="293" ht="15.75" customHeight="1"/>
-    <row r="294" ht="15.75" customHeight="1"/>
-    <row r="295" ht="15.75" customHeight="1">
-      <c r="M295" s="25"/>
-      <c r="N295" s="25"/>
-    </row>
-    <row r="296" ht="15.75" customHeight="1"/>
-    <row r="297" ht="15.75" customHeight="1"/>
-    <row r="298" ht="15.75" customHeight="1"/>
-    <row r="299" ht="15.75" customHeight="1"/>
-    <row r="300" ht="15.75" customHeight="1"/>
-    <row r="301" ht="15.75" customHeight="1">
-      <c r="M301" s="25"/>
-      <c r="N301" s="25"/>
-    </row>
-    <row r="302" ht="15.75" customHeight="1">
-      <c r="M302" s="25"/>
-      <c r="N302" s="25"/>
-    </row>
-    <row r="303" ht="15.75" customHeight="1"/>
-    <row r="304" ht="15.75" customHeight="1"/>
-    <row r="305" ht="15.75" customHeight="1"/>
-    <row r="306" ht="15.75" customHeight="1"/>
-    <row r="307" ht="15.75" customHeight="1">
-      <c r="M307" s="25"/>
-      <c r="N307" s="25"/>
-    </row>
-    <row r="308" ht="15.75" customHeight="1"/>
-    <row r="309" ht="15.75" customHeight="1">
-      <c r="M309" s="25"/>
-      <c r="N309" s="25"/>
-    </row>
-    <row r="310" ht="15.75" customHeight="1"/>
-    <row r="311" ht="15.75" customHeight="1"/>
-    <row r="312" ht="15.75" customHeight="1"/>
-    <row r="313" ht="15.75" customHeight="1">
-      <c r="M313" s="25"/>
-      <c r="N313" s="25"/>
-    </row>
-    <row r="314" ht="15.75" customHeight="1"/>
-    <row r="315" ht="15.75" customHeight="1"/>
-    <row r="316" ht="15.75" customHeight="1">
-      <c r="M316" s="25"/>
-      <c r="N316" s="25"/>
-    </row>
-    <row r="317" ht="15.75" customHeight="1"/>
-    <row r="318" ht="15.75" customHeight="1"/>
-    <row r="319" ht="15.75" customHeight="1">
-      <c r="M319" s="25"/>
-      <c r="N319" s="25"/>
-    </row>
-    <row r="320" ht="15.75" customHeight="1"/>
-    <row r="321" ht="15.75" customHeight="1"/>
-    <row r="322" ht="15.75" customHeight="1"/>
-    <row r="323" ht="15.75" customHeight="1">
-      <c r="M323" s="25"/>
-      <c r="N323" s="25"/>
-    </row>
-    <row r="324" ht="15.75" customHeight="1"/>
-    <row r="325" ht="15.75" customHeight="1">
-      <c r="M325" s="25"/>
-      <c r="N325" s="25"/>
-    </row>
-    <row r="326" ht="15.75" customHeight="1"/>
-    <row r="327" ht="15.75" customHeight="1"/>
-    <row r="328" ht="15.75" customHeight="1"/>
-    <row r="329" ht="15.75" customHeight="1"/>
-    <row r="330" ht="15.75" customHeight="1">
-      <c r="M330" s="25"/>
-      <c r="N330" s="25"/>
-    </row>
-    <row r="331" ht="15.75" customHeight="1">
-      <c r="M331" s="25"/>
-      <c r="N331" s="25"/>
-    </row>
-    <row r="332" ht="15.75" customHeight="1"/>
-    <row r="333" ht="15.75" customHeight="1"/>
-    <row r="334" ht="15.75" customHeight="1"/>
-    <row r="335" ht="15.75" customHeight="1"/>
-    <row r="336" ht="15.75" customHeight="1"/>
-    <row r="337" ht="15.75" customHeight="1">
-      <c r="M337" s="25"/>
-      <c r="N337" s="25"/>
-    </row>
-    <row r="338" ht="15.75" customHeight="1"/>
-    <row r="339" ht="15.75" customHeight="1"/>
-    <row r="340" ht="15.75" customHeight="1"/>
-    <row r="341" ht="15.75" customHeight="1"/>
-    <row r="342" ht="15.75" customHeight="1"/>
-    <row r="343" ht="15.75" customHeight="1">
-      <c r="M343" s="25"/>
-      <c r="N343" s="25"/>
-    </row>
-    <row r="344" ht="15.75" customHeight="1">
-      <c r="M344" s="25"/>
-      <c r="N344" s="25"/>
-    </row>
-    <row r="345" ht="15.75" customHeight="1"/>
-    <row r="346" ht="15.75" customHeight="1"/>
-    <row r="347" ht="15.75" customHeight="1"/>
-    <row r="348" ht="15.75" customHeight="1"/>
-    <row r="349" ht="15.75" customHeight="1">
-      <c r="M349" s="25"/>
-      <c r="N349" s="25"/>
-    </row>
-    <row r="350" ht="15.75" customHeight="1"/>
-    <row r="351" ht="15.75" customHeight="1">
-      <c r="M351" s="25"/>
-      <c r="N351" s="25"/>
-    </row>
-    <row r="352" ht="15.75" customHeight="1"/>
-    <row r="353" ht="15.75" customHeight="1"/>
-    <row r="354" ht="15.75" customHeight="1">
-      <c r="M354" s="25"/>
-      <c r="N354" s="25"/>
-    </row>
-    <row r="355" ht="15.75" customHeight="1"/>
-    <row r="356" ht="15.75" customHeight="1"/>
-    <row r="357" ht="15.75" customHeight="1"/>
-    <row r="358" ht="15.75" customHeight="1">
-      <c r="M358" s="25"/>
-      <c r="N358" s="25"/>
-    </row>
-    <row r="359" ht="15.75" customHeight="1"/>
-    <row r="360" ht="15.75" customHeight="1">
-      <c r="M360" s="25"/>
-      <c r="N360" s="25"/>
-    </row>
-    <row r="361" ht="15.75" customHeight="1"/>
-    <row r="362" ht="15.75" customHeight="1"/>
-    <row r="363" ht="15.75" customHeight="1"/>
-    <row r="364" ht="15.75" customHeight="1"/>
-    <row r="365" ht="15.75" customHeight="1">
-      <c r="M365" s="25"/>
-      <c r="N365" s="25"/>
-    </row>
-    <row r="366" ht="15.75" customHeight="1">
-      <c r="M366" s="25"/>
-      <c r="N366" s="25"/>
-    </row>
-    <row r="367" ht="15.75" customHeight="1"/>
-    <row r="368" ht="15.75" customHeight="1"/>
-    <row r="369" ht="15.75" customHeight="1"/>
-    <row r="370" ht="15.75" customHeight="1"/>
-    <row r="371" ht="15.75" customHeight="1"/>
-    <row r="372" ht="15.75" customHeight="1">
-      <c r="M372" s="25"/>
-      <c r="N372" s="25"/>
-    </row>
-    <row r="373" ht="15.75" customHeight="1"/>
-    <row r="374" ht="15.75" customHeight="1"/>
-    <row r="375" ht="15.75" customHeight="1"/>
-    <row r="376" ht="15.75" customHeight="1"/>
-    <row r="377" ht="15.75" customHeight="1"/>
-    <row r="378" ht="15.75" customHeight="1">
-      <c r="M378" s="25"/>
-      <c r="N378" s="25"/>
-    </row>
-    <row r="379" ht="15.75" customHeight="1">
-      <c r="M379" s="25"/>
-      <c r="N379" s="25"/>
-    </row>
-    <row r="380" ht="15.75" customHeight="1"/>
-    <row r="381" ht="15.75" customHeight="1"/>
-    <row r="382" ht="15.75" customHeight="1"/>
-    <row r="383" ht="15.75" customHeight="1"/>
-    <row r="384" ht="15.75" customHeight="1">
-      <c r="M384" s="25"/>
-      <c r="N384" s="25"/>
-    </row>
-    <row r="385" ht="15.75" customHeight="1"/>
-    <row r="386" ht="15.75" customHeight="1">
-      <c r="M386" s="25"/>
-      <c r="N386" s="25"/>
-    </row>
-    <row r="387" ht="15.75" customHeight="1"/>
-    <row r="388" ht="15.75" customHeight="1"/>
-    <row r="389" ht="15.75" customHeight="1"/>
-    <row r="390" ht="15.75" customHeight="1">
-      <c r="M390" s="25"/>
-      <c r="N390" s="25"/>
-    </row>
-    <row r="391" ht="15.75" customHeight="1"/>
-    <row r="392" ht="15.75" customHeight="1"/>
-    <row r="393" ht="15.75" customHeight="1">
-      <c r="M393" s="25"/>
-      <c r="N393" s="25"/>
-    </row>
-    <row r="394" ht="15.75" customHeight="1"/>
-    <row r="395" ht="15.75" customHeight="1"/>
-    <row r="396" ht="15.75" customHeight="1">
-      <c r="M396" s="25"/>
-      <c r="N396" s="25"/>
-    </row>
-    <row r="397" ht="15.75" customHeight="1"/>
-    <row r="398" ht="15.75" customHeight="1"/>
-    <row r="399" ht="15.75" customHeight="1"/>
-    <row r="400" ht="15.75" customHeight="1">
-      <c r="M400" s="25"/>
-      <c r="N400" s="25"/>
-    </row>
-    <row r="401" ht="15.75" customHeight="1"/>
-    <row r="402" ht="15.75" customHeight="1">
-      <c r="M402" s="25"/>
-      <c r="N402" s="25"/>
-    </row>
-    <row r="403" ht="15.75" customHeight="1"/>
-    <row r="404" ht="15.75" customHeight="1"/>
-    <row r="405" ht="15.75" customHeight="1">
-      <c r="M405" s="25"/>
-      <c r="N405" s="25"/>
-    </row>
-    <row r="406" ht="15.75" customHeight="1"/>
-    <row r="407" ht="15.75" customHeight="1"/>
-    <row r="408" ht="15.75" customHeight="1">
-      <c r="M408" s="25"/>
-      <c r="N408" s="25"/>
-    </row>
-    <row r="409" ht="15.75" customHeight="1"/>
-    <row r="410" ht="15.75" customHeight="1"/>
-    <row r="411" ht="15.75" customHeight="1"/>
-    <row r="412" ht="15.75" customHeight="1">
-      <c r="M412" s="25"/>
-      <c r="N412" s="25"/>
-    </row>
-    <row r="413" ht="15.75" customHeight="1"/>
-    <row r="414" ht="15.75" customHeight="1">
-      <c r="M414" s="25"/>
-      <c r="N414" s="25"/>
-    </row>
-    <row r="415" ht="15.75" customHeight="1"/>
-    <row r="416" ht="15.75" customHeight="1"/>
-    <row r="417" ht="15.75" customHeight="1"/>
-    <row r="418" ht="15.75" customHeight="1"/>
-    <row r="419" ht="15.75" customHeight="1">
-      <c r="M419" s="25"/>
-      <c r="N419" s="25"/>
-    </row>
-    <row r="420" ht="15.75" customHeight="1">
-      <c r="M420" s="25"/>
-      <c r="N420" s="25"/>
-    </row>
-    <row r="421" ht="15.75" customHeight="1"/>
-    <row r="422" ht="15.75" customHeight="1"/>
-    <row r="423" ht="15.75" customHeight="1"/>
-    <row r="424" ht="15.75" customHeight="1"/>
-    <row r="425" ht="15.75" customHeight="1"/>
-    <row r="426" ht="15.75" customHeight="1">
-      <c r="M426" s="25"/>
-      <c r="N426" s="25"/>
-    </row>
-    <row r="427" ht="15.75" customHeight="1"/>
-    <row r="428" ht="15.75" customHeight="1"/>
-    <row r="429" ht="15.75" customHeight="1"/>
-    <row r="430" ht="15.75" customHeight="1"/>
-    <row r="431" ht="15.75" customHeight="1">
-      <c r="M431" s="25"/>
-      <c r="N431" s="25"/>
-    </row>
-    <row r="432" ht="15.75" customHeight="1"/>
-    <row r="433" ht="15.75" customHeight="1">
-      <c r="M433" s="25"/>
-      <c r="N433" s="25"/>
-    </row>
-    <row r="434" ht="15.75" customHeight="1"/>
-    <row r="435" ht="15.75" customHeight="1"/>
-    <row r="436" ht="15.75" customHeight="1">
-      <c r="M436" s="25"/>
-      <c r="N436" s="25"/>
-    </row>
-    <row r="437" ht="15.75" customHeight="1"/>
-    <row r="438" ht="15.75" customHeight="1"/>
-    <row r="439" ht="15.75" customHeight="1"/>
-    <row r="440" ht="15.75" customHeight="1">
-      <c r="M440" s="25"/>
-      <c r="N440" s="25"/>
-    </row>
-    <row r="441" ht="15.75" customHeight="1"/>
-    <row r="442" ht="15.75" customHeight="1">
-      <c r="M442" s="25"/>
-      <c r="N442" s="25"/>
-    </row>
-    <row r="443" ht="15.75" customHeight="1"/>
-    <row r="444" ht="15.75" customHeight="1"/>
-    <row r="445" ht="15.75" customHeight="1"/>
-    <row r="446" ht="15.75" customHeight="1">
-      <c r="M446" s="25"/>
-      <c r="N446" s="25"/>
-    </row>
-    <row r="447" ht="15.75" customHeight="1">
-      <c r="M447" s="25"/>
-      <c r="N447" s="25"/>
-    </row>
-    <row r="448" ht="15.75" customHeight="1"/>
-    <row r="449" ht="15.75" customHeight="1"/>
-    <row r="450" ht="15.75" customHeight="1"/>
-    <row r="451" ht="15.75" customHeight="1"/>
-    <row r="452" ht="15.75" customHeight="1"/>
-    <row r="453" ht="15.75" customHeight="1">
-      <c r="M453" s="25"/>
-      <c r="N453" s="25"/>
-    </row>
-    <row r="454" ht="15.75" customHeight="1"/>
-    <row r="455" ht="15.75" customHeight="1"/>
-    <row r="456" ht="15.75" customHeight="1"/>
-    <row r="457" ht="15.75" customHeight="1"/>
-    <row r="458" ht="15.75" customHeight="1"/>
-    <row r="459" ht="15.75" customHeight="1">
-      <c r="M459" s="25"/>
-      <c r="N459" s="25"/>
-    </row>
-    <row r="460" ht="15.75" customHeight="1">
-      <c r="M460" s="25"/>
-      <c r="N460" s="25"/>
-    </row>
-    <row r="461" ht="15.75" customHeight="1"/>
-    <row r="462" ht="15.75" customHeight="1"/>
-    <row r="463" ht="15.75" customHeight="1"/>
-    <row r="464" ht="15.75" customHeight="1"/>
-    <row r="465" ht="15.75" customHeight="1">
-      <c r="M465" s="25"/>
-      <c r="N465" s="25"/>
-    </row>
-    <row r="466" ht="15.75" customHeight="1"/>
-    <row r="467" ht="15.75" customHeight="1">
-      <c r="M467" s="25"/>
-      <c r="N467" s="25"/>
-    </row>
-    <row r="468" ht="15.75" customHeight="1"/>
-    <row r="469" ht="15.75" customHeight="1"/>
-    <row r="470" ht="15.75" customHeight="1"/>
-    <row r="471" ht="15.75" customHeight="1"/>
-    <row r="472" ht="15.75" customHeight="1"/>
-    <row r="473" ht="15.75" customHeight="1"/>
-    <row r="474" ht="15.75" customHeight="1">
-      <c r="M474" s="25"/>
-      <c r="N474" s="25"/>
-    </row>
-    <row r="475" ht="15.75" customHeight="1"/>
-    <row r="476" ht="15.75" customHeight="1"/>
-    <row r="477" ht="15.75" customHeight="1"/>
-    <row r="478" ht="15.75" customHeight="1"/>
-    <row r="479" ht="15.75" customHeight="1"/>
-    <row r="480" ht="15.75" customHeight="1"/>
-    <row r="481" ht="15.75" customHeight="1">
-      <c r="M481" s="25"/>
-      <c r="N481" s="25"/>
-    </row>
-    <row r="482" ht="15.75" customHeight="1"/>
-    <row r="483" ht="15.75" customHeight="1"/>
-    <row r="484" ht="15.75" customHeight="1"/>
-    <row r="485" ht="15.75" customHeight="1"/>
-    <row r="486" ht="15.75" customHeight="1"/>
-    <row r="487" ht="15.75" customHeight="1"/>
-    <row r="488" ht="15.75" customHeight="1">
-      <c r="M488" s="25"/>
-      <c r="N488" s="25"/>
-    </row>
-    <row r="489" ht="15.75" customHeight="1"/>
-    <row r="490" ht="15.75" customHeight="1"/>
-    <row r="491" ht="15.75" customHeight="1"/>
-    <row r="492" ht="15.75" customHeight="1"/>
-    <row r="493" ht="15.75" customHeight="1"/>
-    <row r="494" ht="15.75" customHeight="1">
-      <c r="M494" s="25"/>
-      <c r="N494" s="25"/>
-    </row>
-    <row r="495" ht="15.75" customHeight="1"/>
-    <row r="496" ht="15.75" customHeight="1"/>
-    <row r="497" ht="15.75" customHeight="1"/>
-    <row r="498" ht="15.75" customHeight="1"/>
-    <row r="499" ht="15.75" customHeight="1"/>
-    <row r="500" ht="15.75" customHeight="1">
-      <c r="M500" s="25"/>
-      <c r="N500" s="25"/>
-    </row>
-    <row r="501" ht="15.75" customHeight="1"/>
-    <row r="502" ht="15.75" customHeight="1"/>
-    <row r="503" ht="15.75" customHeight="1"/>
-    <row r="504" ht="15.75" customHeight="1"/>
-    <row r="505" ht="15.75" customHeight="1"/>
-    <row r="506" ht="15.75" customHeight="1"/>
-    <row r="507" ht="15.75" customHeight="1">
-      <c r="M507" s="25"/>
-      <c r="N507" s="25"/>
-    </row>
-    <row r="508" ht="15.75" customHeight="1"/>
-    <row r="509" ht="15.75" customHeight="1"/>
-    <row r="510" ht="15.75" customHeight="1"/>
-    <row r="511" ht="15.75" customHeight="1"/>
-    <row r="512" ht="15.75" customHeight="1"/>
-    <row r="513" ht="15.75" customHeight="1">
-      <c r="M513" s="25"/>
-      <c r="N513" s="25"/>
-    </row>
-    <row r="514" ht="15.75" customHeight="1"/>
-    <row r="515" ht="15.75" customHeight="1"/>
-    <row r="516" ht="15.75" customHeight="1"/>
-    <row r="517" ht="15.75" customHeight="1"/>
-    <row r="518" ht="15.75" customHeight="1"/>
-    <row r="519" ht="15.75" customHeight="1"/>
-    <row r="520" ht="15.75" customHeight="1">
-      <c r="M520" s="25"/>
-      <c r="N520" s="25"/>
-    </row>
-    <row r="521" ht="15.75" customHeight="1"/>
-    <row r="522" ht="15.75" customHeight="1"/>
-    <row r="523" ht="15.75" customHeight="1"/>
-    <row r="524" ht="15.75" customHeight="1"/>
-    <row r="525" ht="15.75" customHeight="1"/>
-    <row r="526" ht="15.75" customHeight="1"/>
-    <row r="527" ht="15.75" customHeight="1">
-      <c r="M527" s="25"/>
-      <c r="N527" s="25"/>
-    </row>
-    <row r="528" ht="15.75" customHeight="1"/>
-    <row r="529" ht="15.75" customHeight="1"/>
-    <row r="530" ht="15.75" customHeight="1"/>
-    <row r="531" ht="15.75" customHeight="1"/>
-    <row r="532" ht="15.75" customHeight="1"/>
-    <row r="533" ht="15.75" customHeight="1"/>
-    <row r="534" ht="15.75" customHeight="1">
-      <c r="M534" s="25"/>
-      <c r="N534" s="25"/>
-    </row>
-    <row r="535" ht="15.75" customHeight="1"/>
-    <row r="536" ht="15.75" customHeight="1"/>
-    <row r="537" ht="15.75" customHeight="1"/>
-    <row r="538" ht="15.75" customHeight="1"/>
-    <row r="539" ht="15.75" customHeight="1"/>
-    <row r="540" ht="15.75" customHeight="1"/>
-    <row r="541" ht="15.75" customHeight="1"/>
-    <row r="542" ht="15.75" customHeight="1"/>
-    <row r="543" ht="15.75" customHeight="1"/>
-    <row r="544" ht="15.75" customHeight="1"/>
+      <c r="O24" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:15" ht="144" customHeight="1">
+      <c r="L25" s="16"/>
+      <c r="M25" s="16"/>
+    </row>
+    <row r="26" spans="1:15" ht="166.5" customHeight="1">
+      <c r="L26" s="16"/>
+      <c r="M26" s="16"/>
+    </row>
+    <row r="27" spans="1:15" ht="189.75" customHeight="1">
+      <c r="L27" s="16"/>
+      <c r="M27" s="16"/>
+    </row>
+    <row r="28" spans="1:15" ht="189.75" customHeight="1">
+      <c r="L28" s="16"/>
+      <c r="M28" s="16"/>
+      <c r="N28" s="16"/>
+    </row>
+    <row r="29" spans="1:15" ht="213" customHeight="1">
+      <c r="L29" s="16"/>
+      <c r="M29" s="16"/>
+    </row>
+    <row r="30" spans="1:15" ht="235.5" customHeight="1">
+      <c r="L30" s="16"/>
+      <c r="M30" s="16"/>
+      <c r="N30" s="16"/>
+    </row>
+    <row r="31" spans="1:15" ht="189.75" customHeight="1">
+      <c r="L31" s="16"/>
+      <c r="M31" s="16"/>
+    </row>
+    <row r="32" spans="1:15" ht="166.5" customHeight="1">
+      <c r="L32" s="16"/>
+      <c r="M32" s="16"/>
+    </row>
+    <row r="33" spans="12:14" ht="189.75" customHeight="1">
+      <c r="L33" s="16"/>
+      <c r="M33" s="16"/>
+      <c r="N33" s="16"/>
+    </row>
+    <row r="34" spans="12:14" ht="189.75" customHeight="1">
+      <c r="L34" s="16"/>
+      <c r="M34" s="16"/>
+    </row>
+    <row r="35" spans="12:14" ht="189.75" customHeight="1">
+      <c r="L35" s="16"/>
+      <c r="M35" s="16"/>
+    </row>
+    <row r="36" spans="12:14" ht="144" customHeight="1">
+      <c r="L36" s="16"/>
+      <c r="M36" s="16"/>
+      <c r="N36" s="16"/>
+    </row>
+    <row r="37" spans="12:14" ht="144" customHeight="1">
+      <c r="L37" s="16"/>
+      <c r="M37" s="16"/>
+    </row>
+    <row r="38" spans="12:14" ht="166.5" customHeight="1">
+      <c r="L38" s="16"/>
+      <c r="M38" s="16"/>
+    </row>
+    <row r="39" spans="12:14" ht="166.5" customHeight="1">
+      <c r="L39" s="16"/>
+      <c r="M39" s="16"/>
+      <c r="N39" s="16"/>
+    </row>
+    <row r="40" spans="12:14" ht="166.5" customHeight="1">
+      <c r="L40" s="16"/>
+      <c r="M40" s="16"/>
+    </row>
+    <row r="41" spans="12:14" ht="144" customHeight="1">
+      <c r="L41" s="16"/>
+      <c r="M41" s="16"/>
+    </row>
+    <row r="42" spans="12:14" ht="189.75" customHeight="1">
+      <c r="L42" s="16"/>
+      <c r="M42" s="16"/>
+      <c r="N42" s="16"/>
+    </row>
+    <row r="43" spans="12:14" ht="166.5" customHeight="1">
+      <c r="L43" s="16"/>
+      <c r="M43" s="16"/>
+    </row>
+    <row r="44" spans="12:14" ht="189.75" customHeight="1">
+      <c r="L44" s="16"/>
+      <c r="M44" s="16"/>
+    </row>
+    <row r="45" spans="12:14" ht="189.75" customHeight="1">
+      <c r="L45" s="16"/>
+      <c r="M45" s="16"/>
+      <c r="N45" s="16"/>
+    </row>
+    <row r="46" spans="12:14" ht="144" customHeight="1">
+      <c r="L46" s="16"/>
+      <c r="M46" s="16"/>
+    </row>
+    <row r="47" spans="12:14" ht="189.75" customHeight="1">
+      <c r="L47" s="16"/>
+      <c r="M47" s="16"/>
+    </row>
+    <row r="48" spans="12:14" ht="213" customHeight="1">
+      <c r="L48" s="16"/>
+      <c r="M48" s="16"/>
+    </row>
+    <row r="49" spans="12:14" ht="189.75" customHeight="1">
+      <c r="L49" s="16"/>
+      <c r="M49" s="16"/>
+      <c r="N49" s="16"/>
+    </row>
+    <row r="50" spans="12:14" ht="189.75" customHeight="1">
+      <c r="L50" s="16"/>
+      <c r="M50" s="16"/>
+    </row>
+    <row r="51" spans="12:14" ht="189.75" customHeight="1">
+      <c r="L51" s="16"/>
+      <c r="M51" s="16"/>
+      <c r="N51" s="16"/>
+    </row>
+    <row r="52" spans="12:14" ht="189.75" customHeight="1">
+      <c r="L52" s="16"/>
+      <c r="M52" s="16"/>
+    </row>
+    <row r="53" spans="12:14" ht="189.75" customHeight="1">
+      <c r="L53" s="16"/>
+      <c r="M53" s="16"/>
+    </row>
+    <row r="54" spans="12:14" ht="189.75" customHeight="1">
+      <c r="L54" s="16"/>
+      <c r="M54" s="16"/>
+    </row>
+    <row r="55" spans="12:14" ht="189.75" customHeight="1">
+      <c r="L55" s="16"/>
+      <c r="M55" s="16"/>
+    </row>
+    <row r="56" spans="12:14" ht="189.75" customHeight="1">
+      <c r="L56" s="16"/>
+      <c r="M56" s="16"/>
+      <c r="N56" s="16"/>
+    </row>
+    <row r="57" spans="12:14" ht="189.75" customHeight="1">
+      <c r="L57" s="16"/>
+      <c r="M57" s="16"/>
+    </row>
+    <row r="58" spans="12:14" ht="189.75" customHeight="1">
+      <c r="L58" s="16"/>
+      <c r="M58" s="16"/>
+    </row>
+    <row r="59" spans="12:14" ht="189.75" customHeight="1">
+      <c r="L59" s="16"/>
+      <c r="M59" s="16"/>
+    </row>
+    <row r="60" spans="12:14" ht="189.75" customHeight="1">
+      <c r="L60" s="16"/>
+      <c r="M60" s="16"/>
+    </row>
+    <row r="61" spans="12:14" ht="189.75" customHeight="1">
+      <c r="L61" s="16"/>
+      <c r="M61" s="16"/>
+      <c r="N61" s="16"/>
+    </row>
+    <row r="62" spans="12:14" ht="189.75" customHeight="1">
+      <c r="L62" s="16"/>
+      <c r="M62" s="16"/>
+    </row>
+    <row r="63" spans="12:14" ht="189.75" customHeight="1">
+      <c r="L63" s="16"/>
+      <c r="M63" s="16"/>
+    </row>
+    <row r="64" spans="12:14" ht="144" customHeight="1">
+      <c r="L64" s="16"/>
+      <c r="M64" s="16"/>
+      <c r="N64" s="16"/>
+    </row>
+    <row r="65" spans="12:14" ht="189.75" customHeight="1">
+      <c r="L65" s="16"/>
+      <c r="M65" s="16"/>
+    </row>
+    <row r="66" spans="12:14" ht="189.75" customHeight="1">
+      <c r="L66" s="16"/>
+      <c r="M66" s="16"/>
+    </row>
+    <row r="67" spans="12:14" ht="189.75" customHeight="1">
+      <c r="L67" s="16"/>
+      <c r="M67" s="16"/>
+    </row>
+    <row r="68" spans="12:14" ht="189.75" customHeight="1">
+      <c r="L68" s="16"/>
+      <c r="M68" s="16"/>
+    </row>
+    <row r="69" spans="12:14" ht="189.75" customHeight="1">
+      <c r="L69" s="16"/>
+      <c r="M69" s="16"/>
+    </row>
+    <row r="70" spans="12:14" ht="166.5" customHeight="1">
+      <c r="L70" s="16"/>
+      <c r="M70" s="16"/>
+      <c r="N70" s="16"/>
+    </row>
+    <row r="71" spans="12:14" ht="189.75" customHeight="1">
+      <c r="L71" s="16"/>
+      <c r="M71" s="16"/>
+      <c r="N71" s="16"/>
+    </row>
+    <row r="72" spans="12:14" ht="189.75" customHeight="1">
+      <c r="L72" s="16"/>
+      <c r="M72" s="16"/>
+    </row>
+    <row r="73" spans="12:14" ht="189.75" customHeight="1">
+      <c r="L73" s="16"/>
+      <c r="M73" s="16"/>
+    </row>
+    <row r="74" spans="12:14" ht="189.75" customHeight="1">
+      <c r="L74" s="16"/>
+      <c r="M74" s="16"/>
+    </row>
+    <row r="75" spans="12:14" ht="189.75" customHeight="1">
+      <c r="L75" s="16"/>
+      <c r="M75" s="16"/>
+    </row>
+    <row r="76" spans="12:14" ht="189.75" customHeight="1">
+      <c r="L76" s="16"/>
+      <c r="M76" s="16"/>
+    </row>
+    <row r="77" spans="12:14" ht="166.5" customHeight="1">
+      <c r="L77" s="16"/>
+      <c r="M77" s="16"/>
+      <c r="N77" s="16"/>
+    </row>
+    <row r="78" spans="12:14" ht="166.5" customHeight="1">
+      <c r="L78" s="16"/>
+      <c r="M78" s="16"/>
+    </row>
+    <row r="79" spans="12:14" ht="189.75" customHeight="1">
+      <c r="L79" s="16"/>
+      <c r="M79" s="16"/>
+    </row>
+    <row r="80" spans="12:14" ht="166.5" customHeight="1">
+      <c r="L80" s="16"/>
+      <c r="M80" s="16"/>
+      <c r="N80" s="16"/>
+    </row>
+    <row r="81" spans="12:14" ht="189.75" customHeight="1">
+      <c r="L81" s="16"/>
+      <c r="M81" s="16"/>
+    </row>
+    <row r="82" spans="12:14" ht="189.75" customHeight="1">
+      <c r="L82" s="16"/>
+      <c r="M82" s="16"/>
+    </row>
+    <row r="83" spans="12:14" ht="189.75" customHeight="1">
+      <c r="L83" s="16"/>
+      <c r="M83" s="16"/>
+    </row>
+    <row r="84" spans="12:14" ht="213" customHeight="1">
+      <c r="L84" s="16"/>
+      <c r="M84" s="16"/>
+      <c r="N84" s="16"/>
+    </row>
+    <row r="85" spans="12:14" ht="36" customHeight="1"/>
+    <row r="86" spans="12:14" ht="36" customHeight="1"/>
+    <row r="87" spans="12:14" ht="36" customHeight="1"/>
+    <row r="88" spans="12:14" ht="36" customHeight="1">
+      <c r="M88" s="16"/>
+      <c r="N88" s="16"/>
+    </row>
+    <row r="89" spans="12:14" ht="36" customHeight="1"/>
+    <row r="90" spans="12:14" ht="36" customHeight="1"/>
+    <row r="91" spans="12:14" ht="36" customHeight="1">
+      <c r="M91" s="16"/>
+      <c r="N91" s="16"/>
+    </row>
+    <row r="92" spans="12:14" ht="36" customHeight="1"/>
+    <row r="93" spans="12:14" ht="36" customHeight="1"/>
+    <row r="94" spans="12:14" ht="36" customHeight="1"/>
+    <row r="95" spans="12:14" ht="36" customHeight="1"/>
+    <row r="96" spans="12:14" ht="36" customHeight="1"/>
+    <row r="97" spans="13:14" ht="36" customHeight="1">
+      <c r="M97" s="16"/>
+      <c r="N97" s="16"/>
+    </row>
+    <row r="98" spans="13:14" ht="36" customHeight="1"/>
+    <row r="99" spans="13:14" ht="36" customHeight="1"/>
+    <row r="100" spans="13:14" ht="36" customHeight="1"/>
+    <row r="101" spans="13:14" ht="36" customHeight="1"/>
+    <row r="102" spans="13:14" ht="36" customHeight="1">
+      <c r="M102" s="16"/>
+      <c r="N102" s="16"/>
+    </row>
+    <row r="103" spans="13:14" ht="36" customHeight="1"/>
+    <row r="104" spans="13:14" ht="36" customHeight="1"/>
+    <row r="105" spans="13:14" ht="36" customHeight="1">
+      <c r="M105" s="16"/>
+      <c r="N105" s="16"/>
+    </row>
+    <row r="106" spans="13:14" ht="36" customHeight="1"/>
+    <row r="107" spans="13:14" ht="36" customHeight="1"/>
+    <row r="108" spans="13:14" ht="36" customHeight="1">
+      <c r="M108" s="16"/>
+      <c r="N108" s="16"/>
+    </row>
+    <row r="109" spans="13:14" ht="36" customHeight="1"/>
+    <row r="110" spans="13:14" ht="36" customHeight="1"/>
+    <row r="111" spans="13:14" ht="36" customHeight="1"/>
+    <row r="112" spans="13:14" ht="36" customHeight="1">
+      <c r="M112" s="16"/>
+      <c r="N112" s="16"/>
+    </row>
+    <row r="113" spans="13:14" ht="36" customHeight="1"/>
+    <row r="114" spans="13:14" ht="36" customHeight="1">
+      <c r="M114" s="16"/>
+      <c r="N114" s="16"/>
+    </row>
+    <row r="115" spans="13:14" ht="36" customHeight="1"/>
+    <row r="116" spans="13:14" ht="36" customHeight="1"/>
+    <row r="117" spans="13:14" ht="36" customHeight="1"/>
+    <row r="118" spans="13:14" ht="36" customHeight="1">
+      <c r="M118" s="16"/>
+      <c r="N118" s="16"/>
+    </row>
+    <row r="119" spans="13:14" ht="36" customHeight="1"/>
+    <row r="120" spans="13:14" ht="36" customHeight="1">
+      <c r="M120" s="16"/>
+      <c r="N120" s="16"/>
+    </row>
+    <row r="121" spans="13:14" ht="36" customHeight="1"/>
+    <row r="122" spans="13:14" ht="36" customHeight="1"/>
+    <row r="123" spans="13:14" ht="36" customHeight="1"/>
+    <row r="124" spans="13:14" ht="36" customHeight="1"/>
+    <row r="125" spans="13:14" ht="36" customHeight="1">
+      <c r="M125" s="16"/>
+      <c r="N125" s="16"/>
+    </row>
+    <row r="126" spans="13:14" ht="36" customHeight="1"/>
+    <row r="127" spans="13:14" ht="36" customHeight="1"/>
+    <row r="128" spans="13:14" ht="36" customHeight="1"/>
+    <row r="129" spans="13:14" ht="36" customHeight="1"/>
+    <row r="130" spans="13:14" ht="36" customHeight="1"/>
+    <row r="131" spans="13:14" ht="36" customHeight="1">
+      <c r="M131" s="16"/>
+      <c r="N131" s="16"/>
+    </row>
+    <row r="132" spans="13:14" ht="36" customHeight="1">
+      <c r="M132" s="16"/>
+      <c r="N132" s="16"/>
+    </row>
+    <row r="133" spans="13:14" ht="36" customHeight="1"/>
+    <row r="134" spans="13:14" ht="36" customHeight="1"/>
+    <row r="135" spans="13:14" ht="36" customHeight="1"/>
+    <row r="136" spans="13:14" ht="36" customHeight="1"/>
+    <row r="137" spans="13:14" ht="36" customHeight="1">
+      <c r="M137" s="16"/>
+      <c r="N137" s="16"/>
+    </row>
+    <row r="138" spans="13:14" ht="36" customHeight="1"/>
+    <row r="139" spans="13:14" ht="36" customHeight="1">
+      <c r="M139" s="16"/>
+      <c r="N139" s="16"/>
+    </row>
+    <row r="140" spans="13:14" ht="36" customHeight="1"/>
+    <row r="141" spans="13:14" ht="36" customHeight="1"/>
+    <row r="142" spans="13:14" ht="36" customHeight="1"/>
+    <row r="143" spans="13:14" ht="36" customHeight="1">
+      <c r="M143" s="16"/>
+      <c r="N143" s="16"/>
+    </row>
+    <row r="144" spans="13:14" ht="36" customHeight="1">
+      <c r="M144" s="16"/>
+      <c r="N144" s="16"/>
+    </row>
+    <row r="145" spans="13:14" ht="36" customHeight="1"/>
+    <row r="146" spans="13:14" ht="36" customHeight="1"/>
+    <row r="147" spans="13:14" ht="36" customHeight="1"/>
+    <row r="148" spans="13:14" ht="36" customHeight="1"/>
+    <row r="149" spans="13:14" ht="36" customHeight="1">
+      <c r="M149" s="16"/>
+      <c r="N149" s="16"/>
+    </row>
+    <row r="150" spans="13:14" ht="36" customHeight="1">
+      <c r="M150" s="16"/>
+      <c r="N150" s="16"/>
+    </row>
+    <row r="151" spans="13:14" ht="36" customHeight="1"/>
+    <row r="152" spans="13:14" ht="36" customHeight="1"/>
+    <row r="153" spans="13:14" ht="36" customHeight="1"/>
+    <row r="154" spans="13:14" ht="36" customHeight="1"/>
+    <row r="155" spans="13:14" ht="36" customHeight="1"/>
+    <row r="156" spans="13:14" ht="36" customHeight="1">
+      <c r="M156" s="16"/>
+      <c r="N156" s="16"/>
+    </row>
+    <row r="157" spans="13:14" ht="36" customHeight="1">
+      <c r="M157" s="16"/>
+      <c r="N157" s="16"/>
+    </row>
+    <row r="158" spans="13:14" ht="36" customHeight="1"/>
+    <row r="159" spans="13:14" ht="36" customHeight="1"/>
+    <row r="160" spans="13:14" ht="36" customHeight="1"/>
+    <row r="161" spans="13:14" ht="36" customHeight="1"/>
+    <row r="162" spans="13:14" ht="36" customHeight="1">
+      <c r="M162" s="16"/>
+      <c r="N162" s="16"/>
+    </row>
+    <row r="163" spans="13:14" ht="36" customHeight="1"/>
+    <row r="164" spans="13:14" ht="36" customHeight="1">
+      <c r="M164" s="16"/>
+      <c r="N164" s="16"/>
+    </row>
+    <row r="165" spans="13:14" ht="36" customHeight="1"/>
+    <row r="166" spans="13:14" ht="36" customHeight="1"/>
+    <row r="167" spans="13:14" ht="36" customHeight="1">
+      <c r="M167" s="16"/>
+      <c r="N167" s="16"/>
+    </row>
+    <row r="168" spans="13:14" ht="36" customHeight="1"/>
+    <row r="169" spans="13:14" ht="36" customHeight="1"/>
+    <row r="170" spans="13:14" ht="36" customHeight="1"/>
+    <row r="171" spans="13:14" ht="36" customHeight="1"/>
+    <row r="172" spans="13:14" ht="36" customHeight="1">
+      <c r="M172" s="16"/>
+      <c r="N172" s="16"/>
+    </row>
+    <row r="173" spans="13:14" ht="36" customHeight="1">
+      <c r="M173" s="16"/>
+      <c r="N173" s="16"/>
+    </row>
+    <row r="174" spans="13:14" ht="36" customHeight="1"/>
+    <row r="175" spans="13:14" ht="36" customHeight="1"/>
+    <row r="176" spans="13:14" ht="36" customHeight="1"/>
+    <row r="177" spans="13:14" ht="36" customHeight="1"/>
+    <row r="178" spans="13:14" ht="36" customHeight="1"/>
+    <row r="179" spans="13:14" ht="36" customHeight="1">
+      <c r="M179" s="16"/>
+      <c r="N179" s="16"/>
+    </row>
+    <row r="180" spans="13:14" ht="36" customHeight="1"/>
+    <row r="181" spans="13:14" ht="36" customHeight="1">
+      <c r="M181" s="16"/>
+      <c r="N181" s="16"/>
+    </row>
+    <row r="182" spans="13:14" ht="36" customHeight="1"/>
+    <row r="183" spans="13:14" ht="36" customHeight="1"/>
+    <row r="184" spans="13:14" ht="36" customHeight="1"/>
+    <row r="185" spans="13:14" ht="36" customHeight="1">
+      <c r="M185" s="16"/>
+      <c r="N185" s="16"/>
+    </row>
+    <row r="186" spans="13:14" ht="36" customHeight="1"/>
+    <row r="187" spans="13:14" ht="36" customHeight="1"/>
+    <row r="188" spans="13:14" ht="36" customHeight="1">
+      <c r="M188" s="16"/>
+      <c r="N188" s="16"/>
+    </row>
+    <row r="189" spans="13:14" ht="36" customHeight="1"/>
+    <row r="190" spans="13:14" ht="36" customHeight="1">
+      <c r="M190" s="16"/>
+      <c r="N190" s="16"/>
+    </row>
+    <row r="191" spans="13:14" ht="36" customHeight="1"/>
+    <row r="192" spans="13:14" ht="36" customHeight="1"/>
+    <row r="193" spans="13:14" ht="36" customHeight="1"/>
+    <row r="194" spans="13:14" ht="36" customHeight="1">
+      <c r="M194" s="16"/>
+      <c r="N194" s="16"/>
+    </row>
+    <row r="195" spans="13:14" ht="36" customHeight="1">
+      <c r="M195" s="16"/>
+      <c r="N195" s="16"/>
+    </row>
+    <row r="196" spans="13:14" ht="36" customHeight="1"/>
+    <row r="197" spans="13:14" ht="36" customHeight="1"/>
+    <row r="198" spans="13:14" ht="36" customHeight="1"/>
+    <row r="199" spans="13:14" ht="36" customHeight="1"/>
+    <row r="200" spans="13:14" ht="36" customHeight="1"/>
+    <row r="201" spans="13:14" ht="36" customHeight="1">
+      <c r="M201" s="16"/>
+      <c r="N201" s="16"/>
+    </row>
+    <row r="202" spans="13:14" ht="36" customHeight="1"/>
+    <row r="203" spans="13:14" ht="36" customHeight="1"/>
+    <row r="204" spans="13:14" ht="36" customHeight="1"/>
+    <row r="205" spans="13:14" ht="36" customHeight="1"/>
+    <row r="206" spans="13:14" ht="36" customHeight="1">
+      <c r="M206" s="16"/>
+      <c r="N206" s="16"/>
+    </row>
+    <row r="207" spans="13:14" ht="36" customHeight="1"/>
+    <row r="208" spans="13:14" ht="36" customHeight="1">
+      <c r="M208" s="16"/>
+      <c r="N208" s="16"/>
+    </row>
+    <row r="209" spans="13:14" ht="36" customHeight="1"/>
+    <row r="210" spans="13:14" ht="36" customHeight="1"/>
+    <row r="211" spans="13:14" ht="36" customHeight="1"/>
+    <row r="212" spans="13:14" ht="36" customHeight="1">
+      <c r="M212" s="16"/>
+      <c r="N212" s="16"/>
+    </row>
+    <row r="213" spans="13:14" ht="36" customHeight="1"/>
+    <row r="214" spans="13:14" ht="36" customHeight="1"/>
+    <row r="215" spans="13:14" ht="36" customHeight="1">
+      <c r="M215" s="16"/>
+      <c r="N215" s="16"/>
+    </row>
+    <row r="216" spans="13:14" ht="36" customHeight="1"/>
+    <row r="217" spans="13:14" ht="36" customHeight="1">
+      <c r="M217" s="16"/>
+      <c r="N217" s="16"/>
+    </row>
+    <row r="218" spans="13:14" ht="36" customHeight="1"/>
+    <row r="219" spans="13:14" ht="36" customHeight="1"/>
+    <row r="220" spans="13:14" ht="36" customHeight="1">
+      <c r="M220" s="16"/>
+      <c r="N220" s="16"/>
+    </row>
+    <row r="221" spans="13:14" ht="36" customHeight="1"/>
+    <row r="222" spans="13:14" ht="36" customHeight="1"/>
+    <row r="223" spans="13:14" ht="36" customHeight="1">
+      <c r="M223" s="16"/>
+      <c r="N223" s="16"/>
+    </row>
+    <row r="224" spans="13:14" ht="36" customHeight="1"/>
+    <row r="225" spans="13:14" ht="15.75" customHeight="1">
+      <c r="M225" s="16"/>
+      <c r="N225" s="16"/>
+    </row>
+    <row r="226" spans="13:14" ht="15.75" customHeight="1"/>
+    <row r="227" spans="13:14" ht="15.75" customHeight="1"/>
+    <row r="228" spans="13:14" ht="15.75" customHeight="1">
+      <c r="M228" s="16"/>
+      <c r="N228" s="16"/>
+    </row>
+    <row r="229" spans="13:14" ht="15.75" customHeight="1"/>
+    <row r="230" spans="13:14" ht="15.75" customHeight="1"/>
+    <row r="231" spans="13:14" ht="15.75" customHeight="1">
+      <c r="M231" s="16"/>
+      <c r="N231" s="16"/>
+    </row>
+    <row r="232" spans="13:14" ht="15.75" customHeight="1"/>
+    <row r="233" spans="13:14" ht="15.75" customHeight="1"/>
+    <row r="234" spans="13:14" ht="15.75" customHeight="1">
+      <c r="M234" s="16"/>
+      <c r="N234" s="16"/>
+    </row>
+    <row r="235" spans="13:14" ht="15.75" customHeight="1"/>
+    <row r="236" spans="13:14" ht="15.75" customHeight="1"/>
+    <row r="237" spans="13:14" ht="15.75" customHeight="1">
+      <c r="M237" s="16"/>
+      <c r="N237" s="16"/>
+    </row>
+    <row r="238" spans="13:14" ht="15.75" customHeight="1"/>
+    <row r="239" spans="13:14" ht="15.75" customHeight="1"/>
+    <row r="240" spans="13:14" ht="15.75" customHeight="1">
+      <c r="M240" s="16"/>
+      <c r="N240" s="16"/>
+    </row>
+    <row r="241" spans="13:14" ht="15.75" customHeight="1"/>
+    <row r="242" spans="13:14" ht="15.75" customHeight="1"/>
+    <row r="243" spans="13:14" ht="15.75" customHeight="1">
+      <c r="M243" s="16"/>
+      <c r="N243" s="16"/>
+    </row>
+    <row r="244" spans="13:14" ht="15.75" customHeight="1"/>
+    <row r="245" spans="13:14" ht="15.75" customHeight="1"/>
+    <row r="246" spans="13:14" ht="15.75" customHeight="1">
+      <c r="M246" s="16"/>
+      <c r="N246" s="16"/>
+    </row>
+    <row r="247" spans="13:14" ht="15.75" customHeight="1"/>
+    <row r="248" spans="13:14" ht="15.75" customHeight="1">
+      <c r="M248" s="16"/>
+      <c r="N248" s="16"/>
+    </row>
+    <row r="249" spans="13:14" ht="15.75" customHeight="1"/>
+    <row r="250" spans="13:14" ht="15.75" customHeight="1"/>
+    <row r="251" spans="13:14" ht="15.75" customHeight="1"/>
+    <row r="252" spans="13:14" ht="15.75" customHeight="1">
+      <c r="M252" s="16"/>
+      <c r="N252" s="16"/>
+    </row>
+    <row r="253" spans="13:14" ht="15.75" customHeight="1"/>
+    <row r="254" spans="13:14" ht="15.75" customHeight="1"/>
+    <row r="255" spans="13:14" ht="15.75" customHeight="1">
+      <c r="M255" s="16"/>
+      <c r="N255" s="16"/>
+    </row>
+    <row r="256" spans="13:14" ht="15.75" customHeight="1"/>
+    <row r="257" spans="13:14" ht="15.75" customHeight="1"/>
+    <row r="258" spans="13:14" ht="15.75" customHeight="1"/>
+    <row r="259" spans="13:14" ht="15.75" customHeight="1">
+      <c r="M259" s="16"/>
+      <c r="N259" s="16"/>
+    </row>
+    <row r="260" spans="13:14" ht="15.75" customHeight="1"/>
+    <row r="261" spans="13:14" ht="15.75" customHeight="1">
+      <c r="M261" s="16"/>
+      <c r="N261" s="16"/>
+    </row>
+    <row r="262" spans="13:14" ht="15.75" customHeight="1"/>
+    <row r="263" spans="13:14" ht="15.75" customHeight="1"/>
+    <row r="264" spans="13:14" ht="15.75" customHeight="1"/>
+    <row r="265" spans="13:14" ht="15.75" customHeight="1">
+      <c r="M265" s="16"/>
+      <c r="N265" s="16"/>
+    </row>
+    <row r="266" spans="13:14" ht="15.75" customHeight="1"/>
+    <row r="267" spans="13:14" ht="15.75" customHeight="1"/>
+    <row r="268" spans="13:14" ht="15.75" customHeight="1">
+      <c r="M268" s="16"/>
+      <c r="N268" s="16"/>
+    </row>
+    <row r="269" spans="13:14" ht="15.75" customHeight="1"/>
+    <row r="270" spans="13:14" ht="15.75" customHeight="1"/>
+    <row r="271" spans="13:14" ht="15.75" customHeight="1">
+      <c r="M271" s="16"/>
+      <c r="N271" s="16"/>
+    </row>
+    <row r="272" spans="13:14" ht="15.75" customHeight="1"/>
+    <row r="273" spans="13:14" ht="15.75" customHeight="1"/>
+    <row r="274" spans="13:14" ht="15.75" customHeight="1"/>
+    <row r="275" spans="13:14" ht="15.75" customHeight="1">
+      <c r="M275" s="16"/>
+      <c r="N275" s="16"/>
+    </row>
+    <row r="276" spans="13:14" ht="15.75" customHeight="1"/>
+    <row r="277" spans="13:14" ht="15.75" customHeight="1">
+      <c r="M277" s="16"/>
+      <c r="N277" s="16"/>
+    </row>
+    <row r="278" spans="13:14" ht="15.75" customHeight="1"/>
+    <row r="279" spans="13:14" ht="15.75" customHeight="1"/>
+    <row r="280" spans="13:14" ht="15.75" customHeight="1">
+      <c r="M280" s="16"/>
+      <c r="N280" s="16"/>
+    </row>
+    <row r="281" spans="13:14" ht="15.75" customHeight="1"/>
+    <row r="282" spans="13:14" ht="15.75" customHeight="1"/>
+    <row r="283" spans="13:14" ht="15.75" customHeight="1">
+      <c r="M283" s="16"/>
+      <c r="N283" s="16"/>
+    </row>
+    <row r="284" spans="13:14" ht="15.75" customHeight="1"/>
+    <row r="285" spans="13:14" ht="15.75" customHeight="1"/>
+    <row r="286" spans="13:14" ht="15.75" customHeight="1"/>
+    <row r="287" spans="13:14" ht="15.75" customHeight="1">
+      <c r="M287" s="16"/>
+      <c r="N287" s="16"/>
+    </row>
+    <row r="288" spans="13:14" ht="15.75" customHeight="1"/>
+    <row r="289" spans="13:14" ht="15.75" customHeight="1">
+      <c r="M289" s="16"/>
+      <c r="N289" s="16"/>
+    </row>
+    <row r="290" spans="13:14" ht="15.75" customHeight="1"/>
+    <row r="291" spans="13:14" ht="15.75" customHeight="1"/>
+    <row r="292" spans="13:14" ht="15.75" customHeight="1"/>
+    <row r="293" spans="13:14" ht="15.75" customHeight="1"/>
+    <row r="294" spans="13:14" ht="15.75" customHeight="1"/>
+    <row r="295" spans="13:14" ht="15.75" customHeight="1">
+      <c r="M295" s="16"/>
+      <c r="N295" s="16"/>
+    </row>
+    <row r="296" spans="13:14" ht="15.75" customHeight="1"/>
+    <row r="297" spans="13:14" ht="15.75" customHeight="1"/>
+    <row r="298" spans="13:14" ht="15.75" customHeight="1"/>
+    <row r="299" spans="13:14" ht="15.75" customHeight="1"/>
+    <row r="300" spans="13:14" ht="15.75" customHeight="1"/>
+    <row r="301" spans="13:14" ht="15.75" customHeight="1">
+      <c r="M301" s="16"/>
+      <c r="N301" s="16"/>
+    </row>
+    <row r="302" spans="13:14" ht="15.75" customHeight="1">
+      <c r="M302" s="16"/>
+      <c r="N302" s="16"/>
+    </row>
+    <row r="303" spans="13:14" ht="15.75" customHeight="1"/>
+    <row r="304" spans="13:14" ht="15.75" customHeight="1"/>
+    <row r="305" spans="13:14" ht="15.75" customHeight="1"/>
+    <row r="306" spans="13:14" ht="15.75" customHeight="1"/>
+    <row r="307" spans="13:14" ht="15.75" customHeight="1">
+      <c r="M307" s="16"/>
+      <c r="N307" s="16"/>
+    </row>
+    <row r="308" spans="13:14" ht="15.75" customHeight="1"/>
+    <row r="309" spans="13:14" ht="15.75" customHeight="1">
+      <c r="M309" s="16"/>
+      <c r="N309" s="16"/>
+    </row>
+    <row r="310" spans="13:14" ht="15.75" customHeight="1"/>
+    <row r="311" spans="13:14" ht="15.75" customHeight="1"/>
+    <row r="312" spans="13:14" ht="15.75" customHeight="1"/>
+    <row r="313" spans="13:14" ht="15.75" customHeight="1">
+      <c r="M313" s="16"/>
+      <c r="N313" s="16"/>
+    </row>
+    <row r="314" spans="13:14" ht="15.75" customHeight="1"/>
+    <row r="315" spans="13:14" ht="15.75" customHeight="1"/>
+    <row r="316" spans="13:14" ht="15.75" customHeight="1">
+      <c r="M316" s="16"/>
+      <c r="N316" s="16"/>
+    </row>
+    <row r="317" spans="13:14" ht="15.75" customHeight="1"/>
+    <row r="318" spans="13:14" ht="15.75" customHeight="1"/>
+    <row r="319" spans="13:14" ht="15.75" customHeight="1">
+      <c r="M319" s="16"/>
+      <c r="N319" s="16"/>
+    </row>
+    <row r="320" spans="13:14" ht="15.75" customHeight="1"/>
+    <row r="321" spans="13:14" ht="15.75" customHeight="1"/>
+    <row r="322" spans="13:14" ht="15.75" customHeight="1"/>
+    <row r="323" spans="13:14" ht="15.75" customHeight="1">
+      <c r="M323" s="16"/>
+      <c r="N323" s="16"/>
+    </row>
+    <row r="324" spans="13:14" ht="15.75" customHeight="1"/>
+    <row r="325" spans="13:14" ht="15.75" customHeight="1">
+      <c r="M325" s="16"/>
+      <c r="N325" s="16"/>
+    </row>
+    <row r="326" spans="13:14" ht="15.75" customHeight="1"/>
+    <row r="327" spans="13:14" ht="15.75" customHeight="1"/>
+    <row r="328" spans="13:14" ht="15.75" customHeight="1"/>
+    <row r="329" spans="13:14" ht="15.75" customHeight="1"/>
+    <row r="330" spans="13:14" ht="15.75" customHeight="1">
+      <c r="M330" s="16"/>
+      <c r="N330" s="16"/>
+    </row>
+    <row r="331" spans="13:14" ht="15.75" customHeight="1">
+      <c r="M331" s="16"/>
+      <c r="N331" s="16"/>
+    </row>
+    <row r="332" spans="13:14" ht="15.75" customHeight="1"/>
+    <row r="333" spans="13:14" ht="15.75" customHeight="1"/>
+    <row r="334" spans="13:14" ht="15.75" customHeight="1"/>
+    <row r="335" spans="13:14" ht="15.75" customHeight="1"/>
+    <row r="336" spans="13:14" ht="15.75" customHeight="1"/>
+    <row r="337" spans="13:14" ht="15.75" customHeight="1">
+      <c r="M337" s="16"/>
+      <c r="N337" s="16"/>
+    </row>
+    <row r="338" spans="13:14" ht="15.75" customHeight="1"/>
+    <row r="339" spans="13:14" ht="15.75" customHeight="1"/>
+    <row r="340" spans="13:14" ht="15.75" customHeight="1"/>
+    <row r="341" spans="13:14" ht="15.75" customHeight="1"/>
+    <row r="342" spans="13:14" ht="15.75" customHeight="1"/>
+    <row r="343" spans="13:14" ht="15.75" customHeight="1">
+      <c r="M343" s="16"/>
+      <c r="N343" s="16"/>
+    </row>
+    <row r="344" spans="13:14" ht="15.75" customHeight="1">
+      <c r="M344" s="16"/>
+      <c r="N344" s="16"/>
+    </row>
+    <row r="345" spans="13:14" ht="15.75" customHeight="1"/>
+    <row r="346" spans="13:14" ht="15.75" customHeight="1"/>
+    <row r="347" spans="13:14" ht="15.75" customHeight="1"/>
+    <row r="348" spans="13:14" ht="15.75" customHeight="1"/>
+    <row r="349" spans="13:14" ht="15.75" customHeight="1">
+      <c r="M349" s="16"/>
+      <c r="N349" s="16"/>
+    </row>
+    <row r="350" spans="13:14" ht="15.75" customHeight="1"/>
+    <row r="351" spans="13:14" ht="15.75" customHeight="1">
+      <c r="M351" s="16"/>
+      <c r="N351" s="16"/>
+    </row>
+    <row r="352" spans="13:14" ht="15.75" customHeight="1"/>
+    <row r="353" spans="13:14" ht="15.75" customHeight="1"/>
+    <row r="354" spans="13:14" ht="15.75" customHeight="1">
+      <c r="M354" s="16"/>
+      <c r="N354" s="16"/>
+    </row>
+    <row r="355" spans="13:14" ht="15.75" customHeight="1"/>
+    <row r="356" spans="13:14" ht="15.75" customHeight="1"/>
+    <row r="357" spans="13:14" ht="15.75" customHeight="1"/>
+    <row r="358" spans="13:14" ht="15.75" customHeight="1">
+      <c r="M358" s="16"/>
+      <c r="N358" s="16"/>
+    </row>
+    <row r="359" spans="13:14" ht="15.75" customHeight="1"/>
+    <row r="360" spans="13:14" ht="15.75" customHeight="1">
+      <c r="M360" s="16"/>
+      <c r="N360" s="16"/>
+    </row>
+    <row r="361" spans="13:14" ht="15.75" customHeight="1"/>
+    <row r="362" spans="13:14" ht="15.75" customHeight="1"/>
+    <row r="363" spans="13:14" ht="15.75" customHeight="1"/>
+    <row r="364" spans="13:14" ht="15.75" customHeight="1"/>
+    <row r="365" spans="13:14" ht="15.75" customHeight="1">
+      <c r="M365" s="16"/>
+      <c r="N365" s="16"/>
+    </row>
+    <row r="366" spans="13:14" ht="15.75" customHeight="1">
+      <c r="M366" s="16"/>
+      <c r="N366" s="16"/>
+    </row>
+    <row r="367" spans="13:14" ht="15.75" customHeight="1"/>
+    <row r="368" spans="13:14" ht="15.75" customHeight="1"/>
+    <row r="369" spans="13:14" ht="15.75" customHeight="1"/>
+    <row r="370" spans="13:14" ht="15.75" customHeight="1"/>
+    <row r="371" spans="13:14" ht="15.75" customHeight="1"/>
+    <row r="372" spans="13:14" ht="15.75" customHeight="1">
+      <c r="M372" s="16"/>
+      <c r="N372" s="16"/>
+    </row>
+    <row r="373" spans="13:14" ht="15.75" customHeight="1"/>
+    <row r="374" spans="13:14" ht="15.75" customHeight="1"/>
+    <row r="375" spans="13:14" ht="15.75" customHeight="1"/>
+    <row r="376" spans="13:14" ht="15.75" customHeight="1"/>
+    <row r="377" spans="13:14" ht="15.75" customHeight="1"/>
+    <row r="378" spans="13:14" ht="15.75" customHeight="1">
+      <c r="M378" s="16"/>
+      <c r="N378" s="16"/>
+    </row>
+    <row r="379" spans="13:14" ht="15.75" customHeight="1">
+      <c r="M379" s="16"/>
+      <c r="N379" s="16"/>
+    </row>
+    <row r="380" spans="13:14" ht="15.75" customHeight="1"/>
+    <row r="381" spans="13:14" ht="15.75" customHeight="1"/>
+    <row r="382" spans="13:14" ht="15.75" customHeight="1"/>
+    <row r="383" spans="13:14" ht="15.75" customHeight="1"/>
+    <row r="384" spans="13:14" ht="15.75" customHeight="1">
+      <c r="M384" s="16"/>
+      <c r="N384" s="16"/>
+    </row>
+    <row r="385" spans="13:14" ht="15.75" customHeight="1"/>
+    <row r="386" spans="13:14" ht="15.75" customHeight="1">
+      <c r="M386" s="16"/>
+      <c r="N386" s="16"/>
+    </row>
+    <row r="387" spans="13:14" ht="15.75" customHeight="1"/>
+    <row r="388" spans="13:14" ht="15.75" customHeight="1"/>
+    <row r="389" spans="13:14" ht="15.75" customHeight="1"/>
+    <row r="390" spans="13:14" ht="15.75" customHeight="1">
+      <c r="M390" s="16"/>
+      <c r="N390" s="16"/>
+    </row>
+    <row r="391" spans="13:14" ht="15.75" customHeight="1"/>
+    <row r="392" spans="13:14" ht="15.75" customHeight="1"/>
+    <row r="393" spans="13:14" ht="15.75" customHeight="1">
+      <c r="M393" s="16"/>
+      <c r="N393" s="16"/>
+    </row>
+    <row r="394" spans="13:14" ht="15.75" customHeight="1"/>
+    <row r="395" spans="13:14" ht="15.75" customHeight="1"/>
+    <row r="396" spans="13:14" ht="15.75" customHeight="1">
+      <c r="M396" s="16"/>
+      <c r="N396" s="16"/>
+    </row>
+    <row r="397" spans="13:14" ht="15.75" customHeight="1"/>
+    <row r="398" spans="13:14" ht="15.75" customHeight="1"/>
+    <row r="399" spans="13:14" ht="15.75" customHeight="1"/>
+    <row r="400" spans="13:14" ht="15.75" customHeight="1">
+      <c r="M400" s="16"/>
+      <c r="N400" s="16"/>
+    </row>
+    <row r="401" spans="13:14" ht="15.75" customHeight="1"/>
+    <row r="402" spans="13:14" ht="15.75" customHeight="1">
+      <c r="M402" s="16"/>
+      <c r="N402" s="16"/>
+    </row>
+    <row r="403" spans="13:14" ht="15.75" customHeight="1"/>
+    <row r="404" spans="13:14" ht="15.75" customHeight="1"/>
+    <row r="405" spans="13:14" ht="15.75" customHeight="1">
+      <c r="M405" s="16"/>
+      <c r="N405" s="16"/>
+    </row>
+    <row r="406" spans="13:14" ht="15.75" customHeight="1"/>
+    <row r="407" spans="13:14" ht="15.75" customHeight="1"/>
+    <row r="408" spans="13:14" ht="15.75" customHeight="1">
+      <c r="M408" s="16"/>
+      <c r="N408" s="16"/>
+    </row>
+    <row r="409" spans="13:14" ht="15.75" customHeight="1"/>
+    <row r="410" spans="13:14" ht="15.75" customHeight="1"/>
+    <row r="411" spans="13:14" ht="15.75" customHeight="1"/>
+    <row r="412" spans="13:14" ht="15.75" customHeight="1">
+      <c r="M412" s="16"/>
+      <c r="N412" s="16"/>
+    </row>
+    <row r="413" spans="13:14" ht="15.75" customHeight="1"/>
+    <row r="414" spans="13:14" ht="15.75" customHeight="1">
+      <c r="M414" s="16"/>
+      <c r="N414" s="16"/>
+    </row>
+    <row r="415" spans="13:14" ht="15.75" customHeight="1"/>
+    <row r="416" spans="13:14" ht="15.75" customHeight="1"/>
+    <row r="417" spans="13:14" ht="15.75" customHeight="1"/>
+    <row r="418" spans="13:14" ht="15.75" customHeight="1"/>
+    <row r="419" spans="13:14" ht="15.75" customHeight="1">
+      <c r="M419" s="16"/>
+      <c r="N419" s="16"/>
+    </row>
+    <row r="420" spans="13:14" ht="15.75" customHeight="1">
+      <c r="M420" s="16"/>
+      <c r="N420" s="16"/>
+    </row>
+    <row r="421" spans="13:14" ht="15.75" customHeight="1"/>
+    <row r="422" spans="13:14" ht="15.75" customHeight="1"/>
+    <row r="423" spans="13:14" ht="15.75" customHeight="1"/>
+    <row r="424" spans="13:14" ht="15.75" customHeight="1"/>
+    <row r="425" spans="13:14" ht="15.75" customHeight="1"/>
+    <row r="426" spans="13:14" ht="15.75" customHeight="1">
+      <c r="M426" s="16"/>
+      <c r="N426" s="16"/>
+    </row>
+    <row r="427" spans="13:14" ht="15.75" customHeight="1"/>
+    <row r="428" spans="13:14" ht="15.75" customHeight="1"/>
+    <row r="429" spans="13:14" ht="15.75" customHeight="1"/>
+    <row r="430" spans="13:14" ht="15.75" customHeight="1"/>
+    <row r="431" spans="13:14" ht="15.75" customHeight="1">
+      <c r="M431" s="16"/>
+      <c r="N431" s="16"/>
+    </row>
+    <row r="432" spans="13:14" ht="15.75" customHeight="1"/>
+    <row r="433" spans="13:14" ht="15.75" customHeight="1">
+      <c r="M433" s="16"/>
+      <c r="N433" s="16"/>
+    </row>
+    <row r="434" spans="13:14" ht="15.75" customHeight="1"/>
+    <row r="435" spans="13:14" ht="15.75" customHeight="1"/>
+    <row r="436" spans="13:14" ht="15.75" customHeight="1">
+      <c r="M436" s="16"/>
+      <c r="N436" s="16"/>
+    </row>
+    <row r="437" spans="13:14" ht="15.75" customHeight="1"/>
+    <row r="438" spans="13:14" ht="15.75" customHeight="1"/>
+    <row r="439" spans="13:14" ht="15.75" customHeight="1"/>
+    <row r="440" spans="13:14" ht="15.75" customHeight="1">
+      <c r="M440" s="16"/>
+      <c r="N440" s="16"/>
+    </row>
+    <row r="441" spans="13:14" ht="15.75" customHeight="1"/>
+    <row r="442" spans="13:14" ht="15.75" customHeight="1">
+      <c r="M442" s="16"/>
+      <c r="N442" s="16"/>
+    </row>
+    <row r="443" spans="13:14" ht="15.75" customHeight="1"/>
+    <row r="444" spans="13:14" ht="15.75" customHeight="1"/>
+    <row r="445" spans="13:14" ht="15.75" customHeight="1"/>
+    <row r="446" spans="13:14" ht="15.75" customHeight="1">
+      <c r="M446" s="16"/>
+      <c r="N446" s="16"/>
+    </row>
+    <row r="447" spans="13:14" ht="15.75" customHeight="1">
+      <c r="M447" s="16"/>
+      <c r="N447" s="16"/>
+    </row>
+    <row r="448" spans="13:14" ht="15.75" customHeight="1"/>
+    <row r="449" spans="13:14" ht="15.75" customHeight="1"/>
+    <row r="450" spans="13:14" ht="15.75" customHeight="1"/>
+    <row r="451" spans="13:14" ht="15.75" customHeight="1"/>
+    <row r="452" spans="13:14" ht="15.75" customHeight="1"/>
+    <row r="453" spans="13:14" ht="15.75" customHeight="1">
+      <c r="M453" s="16"/>
+      <c r="N453" s="16"/>
+    </row>
+    <row r="454" spans="13:14" ht="15.75" customHeight="1"/>
+    <row r="455" spans="13:14" ht="15.75" customHeight="1"/>
+    <row r="456" spans="13:14" ht="15.75" customHeight="1"/>
+    <row r="457" spans="13:14" ht="15.75" customHeight="1"/>
+    <row r="458" spans="13:14" ht="15.75" customHeight="1"/>
+    <row r="459" spans="13:14" ht="15.75" customHeight="1">
+      <c r="M459" s="16"/>
+      <c r="N459" s="16"/>
+    </row>
+    <row r="460" spans="13:14" ht="15.75" customHeight="1">
+      <c r="M460" s="16"/>
+      <c r="N460" s="16"/>
+    </row>
+    <row r="461" spans="13:14" ht="15.75" customHeight="1"/>
+    <row r="462" spans="13:14" ht="15.75" customHeight="1"/>
+    <row r="463" spans="13:14" ht="15.75" customHeight="1"/>
+    <row r="464" spans="13:14" ht="15.75" customHeight="1"/>
+    <row r="465" spans="13:14" ht="15.75" customHeight="1">
+      <c r="M465" s="16"/>
+      <c r="N465" s="16"/>
+    </row>
+    <row r="466" spans="13:14" ht="15.75" customHeight="1"/>
+    <row r="467" spans="13:14" ht="15.75" customHeight="1">
+      <c r="M467" s="16"/>
+      <c r="N467" s="16"/>
+    </row>
+    <row r="468" spans="13:14" ht="15.75" customHeight="1"/>
+    <row r="469" spans="13:14" ht="15.75" customHeight="1"/>
+    <row r="470" spans="13:14" ht="15.75" customHeight="1"/>
+    <row r="471" spans="13:14" ht="15.75" customHeight="1"/>
+    <row r="472" spans="13:14" ht="15.75" customHeight="1"/>
+    <row r="473" spans="13:14" ht="15.75" customHeight="1"/>
+    <row r="474" spans="13:14" ht="15.75" customHeight="1">
+      <c r="M474" s="16"/>
+      <c r="N474" s="16"/>
+    </row>
+    <row r="475" spans="13:14" ht="15.75" customHeight="1"/>
+    <row r="476" spans="13:14" ht="15.75" customHeight="1"/>
+    <row r="477" spans="13:14" ht="15.75" customHeight="1"/>
+    <row r="478" spans="13:14" ht="15.75" customHeight="1"/>
+    <row r="479" spans="13:14" ht="15.75" customHeight="1"/>
+    <row r="480" spans="13:14" ht="15.75" customHeight="1"/>
+    <row r="481" spans="13:14" ht="15.75" customHeight="1">
+      <c r="M481" s="16"/>
+      <c r="N481" s="16"/>
+    </row>
+    <row r="482" spans="13:14" ht="15.75" customHeight="1"/>
+    <row r="483" spans="13:14" ht="15.75" customHeight="1"/>
+    <row r="484" spans="13:14" ht="15.75" customHeight="1"/>
+    <row r="485" spans="13:14" ht="15.75" customHeight="1"/>
+    <row r="486" spans="13:14" ht="15.75" customHeight="1"/>
+    <row r="487" spans="13:14" ht="15.75" customHeight="1"/>
+    <row r="488" spans="13:14" ht="15.75" customHeight="1">
+      <c r="M488" s="16"/>
+      <c r="N488" s="16"/>
+    </row>
+    <row r="489" spans="13:14" ht="15.75" customHeight="1"/>
+    <row r="490" spans="13:14" ht="15.75" customHeight="1"/>
+    <row r="491" spans="13:14" ht="15.75" customHeight="1"/>
+    <row r="492" spans="13:14" ht="15.75" customHeight="1"/>
+    <row r="493" spans="13:14" ht="15.75" customHeight="1"/>
+    <row r="494" spans="13:14" ht="15.75" customHeight="1">
+      <c r="M494" s="16"/>
+      <c r="N494" s="16"/>
+    </row>
+    <row r="495" spans="13:14" ht="15.75" customHeight="1"/>
+    <row r="496" spans="13:14" ht="15.75" customHeight="1"/>
+    <row r="497" spans="13:14" ht="15.75" customHeight="1"/>
+    <row r="498" spans="13:14" ht="15.75" customHeight="1"/>
+    <row r="499" spans="13:14" ht="15.75" customHeight="1"/>
+    <row r="500" spans="13:14" ht="15.75" customHeight="1">
+      <c r="M500" s="16"/>
+      <c r="N500" s="16"/>
+    </row>
+    <row r="501" spans="13:14" ht="15.75" customHeight="1"/>
+    <row r="502" spans="13:14" ht="15.75" customHeight="1"/>
+    <row r="503" spans="13:14" ht="15.75" customHeight="1"/>
+    <row r="504" spans="13:14" ht="15.75" customHeight="1"/>
+    <row r="505" spans="13:14" ht="15.75" customHeight="1"/>
+    <row r="506" spans="13:14" ht="15.75" customHeight="1"/>
+    <row r="507" spans="13:14" ht="15.75" customHeight="1">
+      <c r="M507" s="16"/>
+      <c r="N507" s="16"/>
+    </row>
+    <row r="508" spans="13:14" ht="15.75" customHeight="1"/>
+    <row r="509" spans="13:14" ht="15.75" customHeight="1"/>
+    <row r="510" spans="13:14" ht="15.75" customHeight="1"/>
+    <row r="511" spans="13:14" ht="15.75" customHeight="1"/>
+    <row r="512" spans="13:14" ht="15.75" customHeight="1"/>
+    <row r="513" spans="13:14" ht="15.75" customHeight="1">
+      <c r="M513" s="16"/>
+      <c r="N513" s="16"/>
+    </row>
+    <row r="514" spans="13:14" ht="15.75" customHeight="1"/>
+    <row r="515" spans="13:14" ht="15.75" customHeight="1"/>
+    <row r="516" spans="13:14" ht="15.75" customHeight="1"/>
+    <row r="517" spans="13:14" ht="15.75" customHeight="1"/>
+    <row r="518" spans="13:14" ht="15.75" customHeight="1"/>
+    <row r="519" spans="13:14" ht="15.75" customHeight="1"/>
+    <row r="520" spans="13:14" ht="15.75" customHeight="1">
+      <c r="M520" s="16"/>
+      <c r="N520" s="16"/>
+    </row>
+    <row r="521" spans="13:14" ht="15.75" customHeight="1"/>
+    <row r="522" spans="13:14" ht="15.75" customHeight="1"/>
+    <row r="523" spans="13:14" ht="15.75" customHeight="1"/>
+    <row r="524" spans="13:14" ht="15.75" customHeight="1"/>
+    <row r="525" spans="13:14" ht="15.75" customHeight="1"/>
+    <row r="526" spans="13:14" ht="15.75" customHeight="1"/>
+    <row r="527" spans="13:14" ht="15.75" customHeight="1">
+      <c r="M527" s="16"/>
+      <c r="N527" s="16"/>
+    </row>
+    <row r="528" spans="13:14" ht="15.75" customHeight="1"/>
+    <row r="529" spans="13:14" ht="15.75" customHeight="1"/>
+    <row r="530" spans="13:14" ht="15.75" customHeight="1"/>
+    <row r="531" spans="13:14" ht="15.75" customHeight="1"/>
+    <row r="532" spans="13:14" ht="15.75" customHeight="1"/>
+    <row r="533" spans="13:14" ht="15.75" customHeight="1"/>
+    <row r="534" spans="13:14" ht="15.75" customHeight="1">
+      <c r="M534" s="16"/>
+      <c r="N534" s="16"/>
+    </row>
+    <row r="535" spans="13:14" ht="15.75" customHeight="1"/>
+    <row r="536" spans="13:14" ht="15.75" customHeight="1"/>
+    <row r="537" spans="13:14" ht="15.75" customHeight="1"/>
+    <row r="538" spans="13:14" ht="15.75" customHeight="1"/>
+    <row r="539" spans="13:14" ht="15.75" customHeight="1"/>
+    <row r="540" spans="13:14" ht="15.75" customHeight="1"/>
+    <row r="541" spans="13:14" ht="15.75" customHeight="1"/>
+    <row r="542" spans="13:14" ht="15.75" customHeight="1"/>
+    <row r="543" spans="13:14" ht="15.75" customHeight="1"/>
+    <row r="544" spans="13:14" ht="15.75" customHeight="1"/>
     <row r="545" ht="15.75" customHeight="1"/>
     <row r="546" ht="15.75" customHeight="1"/>
     <row r="547" ht="15.75" customHeight="1"/>
@@ -8172,26 +8532,27 @@
     <mergeCell ref="A1:O2"/>
     <mergeCell ref="A3:O3"/>
   </mergeCells>
-  <dataValidations>
-    <dataValidation type="list" allowBlank="1" sqref="M6:M24">
+  <dataValidations count="4">
+    <dataValidation type="list" allowBlank="1" sqref="M6:M24" xr:uid="{00000000-0002-0000-0200-000000000000}">
       <formula1>"Not Run,Pass,Fail,Blocked,Planned"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="L6:L24">
+    <dataValidation type="list" allowBlank="1" sqref="L6:L24" xr:uid="{00000000-0002-0000-0200-000001000000}">
       <formula1>"Not Automated,In Progress,Automated,Skipped,Planned"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="N6 N11 N17:N18 N22 N24 M25:M27 M28:N28 M29 M30:N30 M31:M32 M33:N33 M34:M35 M36:N36 M37:M38 M39:N39 M40:M41 M42:N42 M43:M44 M45:N45 M46:M48 M49:N49 M50 M51:N51 M52:M55 M56:N56 M57:M60 M61:N61 M62:M63 M64:N64 M65:M69 M70:N71 M72:M76 M77:N77 M78:M79 M80:N80 M81:M83 M84:N84 N88 N91 N97 N102 N105 N108 N112 N114 N118 N120 N125 N131:N132 N137 N139 N143:N144 N149:N150 N156:N157 N162 N164 N167 N172:N173 N179 N181 N185 N188 N190 N194:N195 N201 N206 N208 N212 N215 N217 N220 N223 N225 N228 N231 N234 N237 N240 N243 N246 N248 N252 N255 N259 N261 N265 N268 N271 N275 N277 N280 N283 N287 N289 N295 N301:N302 N307 N309 N313 N316 N319 N323 N325 N330:N331 N337 N343:N344 N349 N351 N354 N358 N360 N365:N366 N372 N378:N379 N384 N386 N390 N393 N396 N400 N402 N405 N408 N412 N414 N419:N420 N426 N431 N433 N436 N440 N442 N446:N447 N453 N459:N460 N465 N467 N474 N481 N488 N494 N500 N507 N513 N520 N527 N534">
+    <dataValidation type="list" allowBlank="1" sqref="N6 N11 N17:N18 N22 N24 M25:M27 M28:N28 M29 M30:N30 M31:M32 M33:N33 M34:M35 M36:N36 M37:M38 M39:N39 M40:M41 M42:N42 M43:M44 M45:N45 M46:M48 M49:N49 M50 M51:N51 M52:M55 M56:N56 M57:M60 M61:N61 M62:M63 M64:N64 M65:M69 M70:N71 M72:M76 M77:N77 M78:M79 M80:N80 M81:M83 M84:N84 N88 N91 N97 N102 N105 N108 N112 N114 N118 N120 N125 N131:N132 N137 N139 N143:N144 N149:N150 N156:N157 N162 N164 N167 N172:N173 N179 N181 N185 N188 N190 N194:N195 N201 N206 N208 N212 N215 N217 N220 N223 N225 N228 N231 N234 N237 N240 N243 N246 N248 N252 N255 N259 N261 N265 N268 N271 N275 N277 N280 N283 N287 N289 N295 N301:N302 N307 N309 N313 N316 N319 N323 N325 N330:N331 N337 N343:N344 N349 N351 N354 N358 N360 N365:N366 N372 N378:N379 N384 N386 N390 N393 N396 N400 N402 N405 N408 N412 N414 N419:N420 N426 N431 N433 N436 N440 N442 N446:N447 N453 N459:N460 N465 N467 N474 N481 N488 N494 N500 N507 N513 N520 N527 N534" xr:uid="{00000000-0002-0000-0200-000002000000}">
       <formula1>"Not Run,Pass,Fail,Blocked"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="L25:L84 M88 M91 M97 M102 M105 M108 M112 M114 M118 M120 M125 M131:M132 M137 M139 M143:M144 M149:M150 M156:M157 M162 M164 M167 M172:M173 M179 M181 M185 M188 M190 M194:M195 M201 M206 M208 M212 M215 M217 M220 M223 M225 M228 M231 M234 M237 M240 M243 M246 M248 M252 M255 M259 M261 M265 M268 M271 M275 M277 M280 M283 M287 M289 M295 M301:M302 M307 M309 M313 M316 M319 M323 M325 M330:M331 M337 M343:M344 M349 M351 M354 M358 M360 M365:M366 M372 M378:M379 M384 M386 M390 M393 M396 M400 M402 M405 M408 M412 M414 M419:M420 M426 M431 M433 M436 M440 M442 M446:M447 M453 M459:M460 M465 M467 M474 M481 M488 M494 M500 M507 M513 M520 M527 M534">
+    <dataValidation type="list" allowBlank="1" sqref="L25:L84 M88 M91 M97 M102 M105 M108 M112 M114 M118 M120 M125 M131:M132 M137 M139 M143:M144 M149:M150 M156:M157 M162 M164 M167 M172:M173 M179 M181 M185 M188 M190 M194:M195 M201 M206 M208 M212 M215 M217 M220 M223 M225 M228 M231 M234 M237 M240 M243 M246 M248 M252 M255 M259 M261 M265 M268 M271 M275 M277 M280 M283 M287 M289 M295 M301:M302 M307 M309 M313 M316 M319 M323 M325 M330:M331 M337 M343:M344 M349 M351 M354 M358 M360 M365:M366 M372 M378:M379 M384 M386 M390 M393 M396 M400 M402 M405 M408 M412 M414 M419:M420 M426 M431 M433 M436 M440 M442 M446:M447 M453 M459:M460 M465 M467 M474 M481 M488 M494 M500 M507 M513 M520 M527 M534" xr:uid="{00000000-0002-0000-0200-000003000000}">
       <formula1>"Not Automated,In Progress,Automated,Skipped"</formula1>
     </dataValidation>
   </dataValidations>
-  <printOptions/>
-  <pageMargins bottom="0.75" footer="0.0" header="0.0" left="0.7" right="0.7" top="0.75"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup orientation="landscape"/>
-  <drawing r:id="rId1"/>
+  <ignoredErrors>
+    <ignoredError sqref="N6" listDataValidation="1"/>
+  </ignoredErrors>
   <tableParts count="1">
-    <tablePart r:id="rId3"/>
+    <tablePart r:id="rId1"/>
   </tableParts>
 </worksheet>
 </file>
--- a/test-cases/QA_Playground_TypeScript_Playwright_Test_Suite.xlsx
+++ b/test-cases/QA_Playground_TypeScript_Playwright_Test_Suite.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Silerio\Music\PLAYWRIGHT AUTOMATION\test-cases\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96FC1E58-8D21-454D-8555-AE066D3A5776}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{86D14260-A1C0-48E4-A47A-36B28DAFFE62}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Dashboard" sheetId="1" r:id="rId1"/>
@@ -1274,59 +1274,37 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="9" fontId="11" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="8">
-    <dxf>
-      <border>
-        <left style="thin">
-          <color theme="4"/>
-        </left>
-        <right style="thin">
-          <color theme="4"/>
-        </right>
-        <top style="thin">
-          <color theme="4"/>
-        </top>
-        <bottom style="thin">
-          <color theme="4"/>
-        </bottom>
-        <vertical style="thin">
-          <color rgb="FFD4D4D4"/>
-        </vertical>
-        <horizontal style="thin">
-          <color rgb="FFD4D4D4"/>
-        </horizontal>
-      </border>
-    </dxf>
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -1397,19 +1375,41 @@
         </patternFill>
       </fill>
     </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color theme="4"/>
+        </left>
+        <right style="thin">
+          <color theme="4"/>
+        </right>
+        <top style="thin">
+          <color theme="4"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4"/>
+        </bottom>
+        <vertical style="thin">
+          <color rgb="FFD4D4D4"/>
+        </vertical>
+        <horizontal style="thin">
+          <color rgb="FFD4D4D4"/>
+        </horizontal>
+      </border>
+    </dxf>
   </dxfs>
   <tableStyles count="2">
     <tableStyle name="Test Scenarios-style" pivot="0" count="4" xr9:uid="{00000000-0011-0000-FFFF-FFFF00000000}">
-      <tableStyleElement type="wholeTable" size="0" dxfId="4"/>
-      <tableStyleElement type="headerRow" dxfId="7"/>
-      <tableStyleElement type="firstRowStripe" dxfId="6"/>
-      <tableStyleElement type="secondRowStripe" dxfId="5"/>
+      <tableStyleElement type="wholeTable" size="0" dxfId="7"/>
+      <tableStyleElement type="headerRow" dxfId="6"/>
+      <tableStyleElement type="firstRowStripe" dxfId="5"/>
+      <tableStyleElement type="secondRowStripe" dxfId="4"/>
     </tableStyle>
     <tableStyle name="Test Cases-style" pivot="0" count="4" xr9:uid="{00000000-0011-0000-FFFF-FFFF01000000}">
-      <tableStyleElement type="wholeTable" size="0" dxfId="0"/>
-      <tableStyleElement type="headerRow" dxfId="3"/>
-      <tableStyleElement type="firstRowStripe" dxfId="2"/>
-      <tableStyleElement type="secondRowStripe" dxfId="1"/>
+      <tableStyleElement type="wholeTable" size="0" dxfId="3"/>
+      <tableStyleElement type="headerRow" dxfId="2"/>
+      <tableStyleElement type="firstRowStripe" dxfId="1"/>
+      <tableStyleElement type="secondRowStripe" dxfId="0"/>
     </tableStyle>
   </tableStyles>
   <extLst>
@@ -1549,13 +1549,13 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="4"/>
                 <c:pt idx="0">
-                  <c:v>16</c:v>
+                  <c:v>14</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>2</c:v>
+                  <c:v>4</c:v>
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>0</c:v>
@@ -1761,7 +1761,7 @@
                   <c:v>2</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0</c:v>
+                  <c:v>2</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>0</c:v>
@@ -2269,55 +2269,55 @@
   <sheetData>
     <row r="1" spans="1:14" ht="27.75" customHeight="1">
       <c r="A1" s="9"/>
-      <c r="B1" s="17" t="s">
+      <c r="B1" s="24" t="s">
         <v>160</v>
       </c>
-      <c r="C1" s="18"/>
-      <c r="D1" s="18"/>
-      <c r="E1" s="18"/>
-      <c r="F1" s="18"/>
-      <c r="G1" s="18"/>
-      <c r="H1" s="18"/>
-      <c r="I1" s="18"/>
-      <c r="J1" s="18"/>
-      <c r="K1" s="18"/>
-      <c r="L1" s="18"/>
-      <c r="M1" s="18"/>
-      <c r="N1" s="18"/>
+      <c r="C1" s="19"/>
+      <c r="D1" s="19"/>
+      <c r="E1" s="19"/>
+      <c r="F1" s="19"/>
+      <c r="G1" s="19"/>
+      <c r="H1" s="19"/>
+      <c r="I1" s="19"/>
+      <c r="J1" s="19"/>
+      <c r="K1" s="19"/>
+      <c r="L1" s="19"/>
+      <c r="M1" s="19"/>
+      <c r="N1" s="19"/>
     </row>
     <row r="2" spans="1:14" ht="27.75" customHeight="1">
       <c r="A2" s="9"/>
-      <c r="B2" s="18"/>
-      <c r="C2" s="18"/>
-      <c r="D2" s="18"/>
-      <c r="E2" s="18"/>
-      <c r="F2" s="18"/>
-      <c r="G2" s="18"/>
-      <c r="H2" s="18"/>
-      <c r="I2" s="18"/>
-      <c r="J2" s="18"/>
-      <c r="K2" s="18"/>
-      <c r="L2" s="18"/>
-      <c r="M2" s="18"/>
-      <c r="N2" s="18"/>
+      <c r="B2" s="19"/>
+      <c r="C2" s="19"/>
+      <c r="D2" s="19"/>
+      <c r="E2" s="19"/>
+      <c r="F2" s="19"/>
+      <c r="G2" s="19"/>
+      <c r="H2" s="19"/>
+      <c r="I2" s="19"/>
+      <c r="J2" s="19"/>
+      <c r="K2" s="19"/>
+      <c r="L2" s="19"/>
+      <c r="M2" s="19"/>
+      <c r="N2" s="19"/>
     </row>
     <row r="3" spans="1:14" ht="27.75" customHeight="1">
       <c r="A3" s="9"/>
-      <c r="B3" s="19" t="s">
+      <c r="B3" s="25" t="s">
         <v>161</v>
       </c>
-      <c r="C3" s="18"/>
-      <c r="D3" s="18"/>
-      <c r="E3" s="18"/>
-      <c r="F3" s="18"/>
-      <c r="G3" s="18"/>
-      <c r="H3" s="18"/>
-      <c r="I3" s="18"/>
-      <c r="J3" s="18"/>
-      <c r="K3" s="18"/>
-      <c r="L3" s="18"/>
-      <c r="M3" s="18"/>
-      <c r="N3" s="18"/>
+      <c r="C3" s="19"/>
+      <c r="D3" s="19"/>
+      <c r="E3" s="19"/>
+      <c r="F3" s="19"/>
+      <c r="G3" s="19"/>
+      <c r="H3" s="19"/>
+      <c r="I3" s="19"/>
+      <c r="J3" s="19"/>
+      <c r="K3" s="19"/>
+      <c r="L3" s="19"/>
+      <c r="M3" s="19"/>
+      <c r="N3" s="19"/>
     </row>
     <row r="4" spans="1:14">
       <c r="A4" s="9"/>
@@ -2337,81 +2337,81 @@
     </row>
     <row r="5" spans="1:14">
       <c r="A5" s="9"/>
-      <c r="B5" s="20" t="s">
+      <c r="B5" s="23" t="s">
         <v>163</v>
       </c>
-      <c r="C5" s="18"/>
-      <c r="D5" s="20" t="s">
+      <c r="C5" s="19"/>
+      <c r="D5" s="23" t="s">
         <v>164</v>
       </c>
-      <c r="E5" s="18"/>
-      <c r="F5" s="20" t="s">
+      <c r="E5" s="19"/>
+      <c r="F5" s="23" t="s">
         <v>165</v>
       </c>
-      <c r="G5" s="18"/>
-      <c r="H5" s="18"/>
-      <c r="I5" s="20" t="s">
+      <c r="G5" s="19"/>
+      <c r="H5" s="19"/>
+      <c r="I5" s="23" t="s">
         <v>166</v>
       </c>
-      <c r="J5" s="18"/>
-      <c r="K5" s="20" t="s">
+      <c r="J5" s="19"/>
+      <c r="K5" s="23" t="s">
         <v>167</v>
       </c>
-      <c r="L5" s="18"/>
-      <c r="M5" s="20" t="s">
+      <c r="L5" s="19"/>
+      <c r="M5" s="23" t="s">
         <v>168</v>
       </c>
-      <c r="N5" s="18"/>
+      <c r="N5" s="19"/>
     </row>
     <row r="6" spans="1:14">
       <c r="A6" s="9"/>
-      <c r="B6" s="21">
+      <c r="B6" s="18">
         <f>COUNTA('Test Scenarios'!$A$6:$A$24)</f>
         <v>19</v>
       </c>
-      <c r="C6" s="18"/>
-      <c r="D6" s="21">
+      <c r="C6" s="19"/>
+      <c r="D6" s="18">
         <f>COUNTA('Test Cases'!$B$6:$B$24)</f>
         <v>19</v>
       </c>
-      <c r="E6" s="18"/>
-      <c r="F6" s="23">
+      <c r="E6" s="19"/>
+      <c r="F6" s="20">
         <f>IFERROR(COUNTIF('Test Cases'!$L$6:$L$23,"Automated")/D6,0)</f>
-        <v>0.10526315789473684</v>
-      </c>
-      <c r="G6" s="18"/>
-      <c r="H6" s="18"/>
-      <c r="I6" s="21">
+        <v>0.21052631578947367</v>
+      </c>
+      <c r="G6" s="19"/>
+      <c r="H6" s="19"/>
+      <c r="I6" s="18">
         <f>COUNTIFS('Test Cases'!$M$6:$M$23,"Pass")</f>
-        <v>2</v>
-      </c>
-      <c r="J6" s="18"/>
-      <c r="K6" s="21">
+        <v>4</v>
+      </c>
+      <c r="J6" s="19"/>
+      <c r="K6" s="18">
         <f>COUNTIFS('Test Cases'!$M$6:$M$23,"Fail")</f>
         <v>0</v>
       </c>
-      <c r="L6" s="18"/>
-      <c r="M6" s="23">
+      <c r="L6" s="19"/>
+      <c r="M6" s="20">
         <f>IFERROR((COUNTIF('Test Cases'!$M$6:$M$23,"Pass")+COUNTIF('Test Cases'!$M$6:$M$23,"Fail")+COUNTIF('Test Cases'!$M$6:$M$23,"Blocked"))/D6,0)</f>
-        <v>0.10526315789473684</v>
-      </c>
-      <c r="N6" s="18"/>
+        <v>0.21052631578947367</v>
+      </c>
+      <c r="N6" s="19"/>
     </row>
     <row r="7" spans="1:14">
       <c r="A7" s="9"/>
-      <c r="B7" s="18"/>
-      <c r="C7" s="18"/>
-      <c r="D7" s="18"/>
-      <c r="E7" s="18"/>
-      <c r="F7" s="18"/>
-      <c r="G7" s="18"/>
-      <c r="H7" s="18"/>
-      <c r="I7" s="18"/>
-      <c r="J7" s="18"/>
-      <c r="K7" s="18"/>
-      <c r="L7" s="18"/>
-      <c r="M7" s="18"/>
-      <c r="N7" s="18"/>
+      <c r="B7" s="19"/>
+      <c r="C7" s="19"/>
+      <c r="D7" s="19"/>
+      <c r="E7" s="19"/>
+      <c r="F7" s="19"/>
+      <c r="G7" s="19"/>
+      <c r="H7" s="19"/>
+      <c r="I7" s="19"/>
+      <c r="J7" s="19"/>
+      <c r="K7" s="19"/>
+      <c r="L7" s="19"/>
+      <c r="M7" s="19"/>
+      <c r="N7" s="19"/>
     </row>
     <row r="8" spans="1:14">
       <c r="A8" s="9"/>
@@ -2431,21 +2431,21 @@
     </row>
     <row r="9" spans="1:14" ht="36.75" customHeight="1">
       <c r="A9" s="9"/>
-      <c r="B9" s="24" t="s">
+      <c r="B9" s="21" t="s">
         <v>179</v>
       </c>
-      <c r="C9" s="18"/>
-      <c r="D9" s="18"/>
-      <c r="E9" s="18"/>
-      <c r="F9" s="18"/>
-      <c r="G9" s="18"/>
-      <c r="H9" s="18"/>
-      <c r="I9" s="18"/>
-      <c r="J9" s="18"/>
-      <c r="K9" s="18"/>
-      <c r="L9" s="18"/>
-      <c r="M9" s="18"/>
-      <c r="N9" s="18"/>
+      <c r="C9" s="19"/>
+      <c r="D9" s="19"/>
+      <c r="E9" s="19"/>
+      <c r="F9" s="19"/>
+      <c r="G9" s="19"/>
+      <c r="H9" s="19"/>
+      <c r="I9" s="19"/>
+      <c r="J9" s="19"/>
+      <c r="K9" s="19"/>
+      <c r="L9" s="19"/>
+      <c r="M9" s="19"/>
+      <c r="N9" s="19"/>
     </row>
     <row r="10" spans="1:14">
       <c r="A10" s="9"/>
@@ -2484,10 +2484,10 @@
       <c r="B12" s="22" t="s">
         <v>181</v>
       </c>
-      <c r="C12" s="18"/>
-      <c r="D12" s="18"/>
-      <c r="E12" s="18"/>
-      <c r="F12" s="18"/>
+      <c r="C12" s="19"/>
+      <c r="D12" s="19"/>
+      <c r="E12" s="19"/>
+      <c r="F12" s="19"/>
       <c r="G12" s="9"/>
       <c r="H12" s="9"/>
       <c r="I12" s="9"/>
@@ -2564,15 +2564,15 @@
       </c>
       <c r="D15" s="11">
         <f>COUNTIFS('Test Cases'!$K$6:$K$23,B15,'Test Cases'!$L$6:$L$23,"Automated")</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E15" s="11">
         <f>COUNTIFS('Test Cases'!$K$6:$K$23,B15,'Test Cases'!$M$6:$M$23,"Pass")</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F15" s="12">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="G15" s="9"/>
       <c r="H15" s="9"/>
@@ -2680,10 +2680,10 @@
       <c r="B20" s="22" t="s">
         <v>196</v>
       </c>
-      <c r="C20" s="18"/>
-      <c r="D20" s="18"/>
-      <c r="E20" s="18"/>
-      <c r="F20" s="18"/>
+      <c r="C20" s="19"/>
+      <c r="D20" s="19"/>
+      <c r="E20" s="19"/>
+      <c r="F20" s="19"/>
       <c r="G20" s="9"/>
       <c r="H20" s="9"/>
       <c r="I20" s="9"/>
@@ -2724,7 +2724,7 @@
       </c>
       <c r="C22" s="11">
         <f>COUNTIFS('Test Cases'!$L$6:$L$24,B22)</f>
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="D22" s="9"/>
       <c r="E22" s="11" t="s">
@@ -2732,7 +2732,7 @@
       </c>
       <c r="F22" s="11">
         <f>COUNTIFS('Test Cases'!$M$6:$M$23,E22)</f>
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="G22" s="9"/>
       <c r="H22" s="9"/>
@@ -2758,7 +2758,7 @@
       </c>
       <c r="F23" s="11">
         <f>COUNTIFS('Test Cases'!$M$6:$M$23,E23)</f>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G23" s="9"/>
       <c r="H23" s="9"/>
@@ -2776,7 +2776,7 @@
       </c>
       <c r="C24" s="11">
         <f>COUNTIFS('Test Cases'!$L$6:$L$23,B24)</f>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D24" s="9"/>
       <c r="E24" s="11" t="s">
@@ -2858,10 +2858,10 @@
       <c r="B28" s="22" t="s">
         <v>210</v>
       </c>
-      <c r="C28" s="18"/>
-      <c r="D28" s="18"/>
-      <c r="E28" s="18"/>
-      <c r="F28" s="18"/>
+      <c r="C28" s="19"/>
+      <c r="D28" s="19"/>
+      <c r="E28" s="19"/>
+      <c r="F28" s="19"/>
       <c r="G28" s="9"/>
       <c r="H28" s="9"/>
       <c r="I28" s="9"/>
@@ -2971,15 +2971,15 @@
       </c>
       <c r="D32" s="14">
         <f>COUNTIFS('Test Cases'!$D$6:$D$23,B32,'Test Cases'!$L$6:$L$23,"Automated")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E32" s="14">
         <f>COUNTIFS('Test Cases'!$D$6:$D$23,B32,'Test Cases'!$M$6:$M$23,"Pass")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F32" s="15">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G32" s="9"/>
       <c r="H32" s="9"/>
@@ -3002,15 +3002,15 @@
       </c>
       <c r="D33" s="14">
         <f>COUNTIFS('Test Cases'!$D$6:$D$23,B33,'Test Cases'!$L$6:$L$23,"Automated")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E33" s="14">
         <f>COUNTIFS('Test Cases'!$D$6:$D$23,B33,'Test Cases'!$M$6:$M$23,"Pass")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F33" s="15">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G33" s="9"/>
       <c r="H33" s="9"/>
@@ -4425,17 +4425,6 @@
     <row r="1000" ht="15.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="18">
-    <mergeCell ref="I6:J7"/>
-    <mergeCell ref="K6:L7"/>
-    <mergeCell ref="M6:N7"/>
-    <mergeCell ref="B9:N9"/>
-    <mergeCell ref="D6:E7"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B20:F20"/>
-    <mergeCell ref="B28:F28"/>
-    <mergeCell ref="B5:C5"/>
-    <mergeCell ref="B6:C7"/>
-    <mergeCell ref="F6:H7"/>
     <mergeCell ref="B1:N2"/>
     <mergeCell ref="B3:N3"/>
     <mergeCell ref="D5:E5"/>
@@ -4443,6 +4432,17 @@
     <mergeCell ref="I5:J5"/>
     <mergeCell ref="K5:L5"/>
     <mergeCell ref="M5:N5"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="B20:F20"/>
+    <mergeCell ref="B28:F28"/>
+    <mergeCell ref="B5:C5"/>
+    <mergeCell ref="B6:C7"/>
+    <mergeCell ref="F6:H7"/>
+    <mergeCell ref="I6:J7"/>
+    <mergeCell ref="K6:L7"/>
+    <mergeCell ref="M6:N7"/>
+    <mergeCell ref="B9:N9"/>
+    <mergeCell ref="D6:E7"/>
   </mergeCells>
   <conditionalFormatting sqref="F30:F47">
     <cfRule type="colorScale" priority="1">
@@ -4480,35 +4480,35 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="25.5" customHeight="1">
-      <c r="A1" s="25" t="s">
+      <c r="A1" s="26" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="18"/>
-      <c r="C1" s="18"/>
-      <c r="D1" s="18"/>
-      <c r="E1" s="18"/>
-      <c r="F1" s="18"/>
-      <c r="G1" s="18"/>
+      <c r="B1" s="19"/>
+      <c r="C1" s="19"/>
+      <c r="D1" s="19"/>
+      <c r="E1" s="19"/>
+      <c r="F1" s="19"/>
+      <c r="G1" s="19"/>
     </row>
     <row r="2" spans="1:7" ht="25.5" customHeight="1">
-      <c r="A2" s="18"/>
-      <c r="B2" s="18"/>
-      <c r="C2" s="18"/>
-      <c r="D2" s="18"/>
-      <c r="E2" s="18"/>
-      <c r="F2" s="18"/>
-      <c r="G2" s="18"/>
+      <c r="A2" s="19"/>
+      <c r="B2" s="19"/>
+      <c r="C2" s="19"/>
+      <c r="D2" s="19"/>
+      <c r="E2" s="19"/>
+      <c r="F2" s="19"/>
+      <c r="G2" s="19"/>
     </row>
     <row r="3" spans="1:7" ht="27.75" customHeight="1">
-      <c r="A3" s="19" t="s">
+      <c r="A3" s="25" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="18"/>
-      <c r="C3" s="18"/>
-      <c r="D3" s="18"/>
-      <c r="E3" s="18"/>
-      <c r="F3" s="18"/>
-      <c r="G3" s="18"/>
+      <c r="B3" s="19"/>
+      <c r="C3" s="19"/>
+      <c r="D3" s="19"/>
+      <c r="E3" s="19"/>
+      <c r="F3" s="19"/>
+      <c r="G3" s="19"/>
     </row>
     <row r="5" spans="1:7">
       <c r="A5" s="1" t="s">
@@ -4599,7 +4599,7 @@
         <v>40</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="42" customHeight="1">
@@ -5988,59 +5988,59 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="25.5" customHeight="1">
-      <c r="A1" s="25" t="s">
+      <c r="A1" s="26" t="s">
         <v>2</v>
       </c>
-      <c r="B1" s="25"/>
-      <c r="C1" s="25"/>
-      <c r="D1" s="25"/>
-      <c r="E1" s="25"/>
-      <c r="F1" s="25"/>
-      <c r="G1" s="25"/>
-      <c r="H1" s="25"/>
-      <c r="I1" s="25"/>
-      <c r="J1" s="25"/>
-      <c r="K1" s="25"/>
-      <c r="L1" s="25"/>
-      <c r="M1" s="25"/>
-      <c r="N1" s="25"/>
-      <c r="O1" s="25"/>
+      <c r="B1" s="26"/>
+      <c r="C1" s="26"/>
+      <c r="D1" s="26"/>
+      <c r="E1" s="26"/>
+      <c r="F1" s="26"/>
+      <c r="G1" s="26"/>
+      <c r="H1" s="26"/>
+      <c r="I1" s="26"/>
+      <c r="J1" s="26"/>
+      <c r="K1" s="26"/>
+      <c r="L1" s="26"/>
+      <c r="M1" s="26"/>
+      <c r="N1" s="26"/>
+      <c r="O1" s="26"/>
     </row>
     <row r="2" spans="1:15" ht="25.5" customHeight="1">
-      <c r="A2" s="25"/>
-      <c r="B2" s="25"/>
-      <c r="C2" s="25"/>
-      <c r="D2" s="25"/>
-      <c r="E2" s="25"/>
-      <c r="F2" s="25"/>
-      <c r="G2" s="25"/>
-      <c r="H2" s="25"/>
-      <c r="I2" s="25"/>
-      <c r="J2" s="25"/>
-      <c r="K2" s="25"/>
-      <c r="L2" s="25"/>
-      <c r="M2" s="25"/>
-      <c r="N2" s="25"/>
-      <c r="O2" s="25"/>
+      <c r="A2" s="26"/>
+      <c r="B2" s="26"/>
+      <c r="C2" s="26"/>
+      <c r="D2" s="26"/>
+      <c r="E2" s="26"/>
+      <c r="F2" s="26"/>
+      <c r="G2" s="26"/>
+      <c r="H2" s="26"/>
+      <c r="I2" s="26"/>
+      <c r="J2" s="26"/>
+      <c r="K2" s="26"/>
+      <c r="L2" s="26"/>
+      <c r="M2" s="26"/>
+      <c r="N2" s="26"/>
+      <c r="O2" s="26"/>
     </row>
     <row r="3" spans="1:15" ht="27.75" customHeight="1">
-      <c r="A3" s="19" t="s">
+      <c r="A3" s="25" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="19"/>
-      <c r="C3" s="19"/>
-      <c r="D3" s="19"/>
-      <c r="E3" s="19"/>
-      <c r="F3" s="19"/>
-      <c r="G3" s="19"/>
-      <c r="H3" s="19"/>
-      <c r="I3" s="19"/>
-      <c r="J3" s="19"/>
-      <c r="K3" s="19"/>
-      <c r="L3" s="19"/>
-      <c r="M3" s="19"/>
-      <c r="N3" s="19"/>
-      <c r="O3" s="19"/>
+      <c r="B3" s="25"/>
+      <c r="C3" s="25"/>
+      <c r="D3" s="25"/>
+      <c r="E3" s="25"/>
+      <c r="F3" s="25"/>
+      <c r="G3" s="25"/>
+      <c r="H3" s="25"/>
+      <c r="I3" s="25"/>
+      <c r="J3" s="25"/>
+      <c r="K3" s="25"/>
+      <c r="L3" s="25"/>
+      <c r="M3" s="25"/>
+      <c r="N3" s="25"/>
+      <c r="O3" s="25"/>
     </row>
     <row r="5" spans="1:15" ht="36.75" customHeight="1">
       <c r="A5" s="2" t="s">
@@ -6123,10 +6123,10 @@
       <c r="K6" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="L6" s="26" t="s">
+      <c r="L6" s="17" t="s">
         <v>53</v>
       </c>
-      <c r="M6" s="26" t="s">
+      <c r="M6" s="17" t="s">
         <v>56</v>
       </c>
       <c r="N6" s="5" t="s">
@@ -6217,11 +6217,11 @@
       <c r="K8" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="L8" s="5" t="s">
-        <v>79</v>
-      </c>
-      <c r="M8" s="5" t="s">
-        <v>82</v>
+      <c r="L8" s="17" t="s">
+        <v>53</v>
+      </c>
+      <c r="M8" s="17" t="s">
+        <v>56</v>
       </c>
       <c r="N8" s="5" t="s">
         <v>39</v>
@@ -6265,10 +6265,10 @@
         <v>40</v>
       </c>
       <c r="L9" s="8" t="s">
-        <v>79</v>
+        <v>53</v>
       </c>
       <c r="M9" s="8" t="s">
-        <v>82</v>
+        <v>56</v>
       </c>
       <c r="N9" s="8" t="s">
         <v>48</v>

--- a/test-cases/QA_Playground_TypeScript_Playwright_Test_Suite.xlsx
+++ b/test-cases/QA_Playground_TypeScript_Playwright_Test_Suite.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Silerio\Music\PLAYWRIGHT AUTOMATION\test-cases\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{86D14260-A1C0-48E4-A47A-36B28DAFFE62}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED14E705-05F1-4567-B546-901C85A96DF6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Dashboard" sheetId="1" r:id="rId1"/>
@@ -1277,25 +1277,25 @@
     <xf numFmtId="0" fontId="15" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="11" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="9" fontId="11" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1549,13 +1549,13 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="4"/>
                 <c:pt idx="0">
-                  <c:v>14</c:v>
+                  <c:v>10</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>4</c:v>
+                  <c:v>8</c:v>
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>0</c:v>
@@ -1758,10 +1758,10 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="4"/>
                 <c:pt idx="0">
-                  <c:v>2</c:v>
+                  <c:v>3</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>2</c:v>
+                  <c:v>5</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>0</c:v>
@@ -2269,7 +2269,7 @@
   <sheetData>
     <row r="1" spans="1:14" ht="27.75" customHeight="1">
       <c r="A1" s="9"/>
-      <c r="B1" s="24" t="s">
+      <c r="B1" s="18" t="s">
         <v>160</v>
       </c>
       <c r="C1" s="19"/>
@@ -2303,7 +2303,7 @@
     </row>
     <row r="3" spans="1:14" ht="27.75" customHeight="1">
       <c r="A3" s="9"/>
-      <c r="B3" s="25" t="s">
+      <c r="B3" s="20" t="s">
         <v>161</v>
       </c>
       <c r="C3" s="19"/>
@@ -2337,63 +2337,63 @@
     </row>
     <row r="5" spans="1:14">
       <c r="A5" s="9"/>
-      <c r="B5" s="23" t="s">
+      <c r="B5" s="21" t="s">
         <v>163</v>
       </c>
       <c r="C5" s="19"/>
-      <c r="D5" s="23" t="s">
+      <c r="D5" s="21" t="s">
         <v>164</v>
       </c>
       <c r="E5" s="19"/>
-      <c r="F5" s="23" t="s">
+      <c r="F5" s="21" t="s">
         <v>165</v>
       </c>
       <c r="G5" s="19"/>
       <c r="H5" s="19"/>
-      <c r="I5" s="23" t="s">
+      <c r="I5" s="21" t="s">
         <v>166</v>
       </c>
       <c r="J5" s="19"/>
-      <c r="K5" s="23" t="s">
+      <c r="K5" s="21" t="s">
         <v>167</v>
       </c>
       <c r="L5" s="19"/>
-      <c r="M5" s="23" t="s">
+      <c r="M5" s="21" t="s">
         <v>168</v>
       </c>
       <c r="N5" s="19"/>
     </row>
     <row r="6" spans="1:14">
       <c r="A6" s="9"/>
-      <c r="B6" s="18">
+      <c r="B6" s="23">
         <f>COUNTA('Test Scenarios'!$A$6:$A$24)</f>
         <v>19</v>
       </c>
       <c r="C6" s="19"/>
-      <c r="D6" s="18">
+      <c r="D6" s="23">
         <f>COUNTA('Test Cases'!$B$6:$B$24)</f>
         <v>19</v>
       </c>
       <c r="E6" s="19"/>
-      <c r="F6" s="20">
+      <c r="F6" s="24">
         <f>IFERROR(COUNTIF('Test Cases'!$L$6:$L$23,"Automated")/D6,0)</f>
-        <v>0.21052631578947367</v>
+        <v>0.42105263157894735</v>
       </c>
       <c r="G6" s="19"/>
       <c r="H6" s="19"/>
-      <c r="I6" s="18">
+      <c r="I6" s="23">
         <f>COUNTIFS('Test Cases'!$M$6:$M$23,"Pass")</f>
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="J6" s="19"/>
-      <c r="K6" s="18">
+      <c r="K6" s="23">
         <f>COUNTIFS('Test Cases'!$M$6:$M$23,"Fail")</f>
         <v>0</v>
       </c>
       <c r="L6" s="19"/>
-      <c r="M6" s="20">
+      <c r="M6" s="24">
         <f>IFERROR((COUNTIF('Test Cases'!$M$6:$M$23,"Pass")+COUNTIF('Test Cases'!$M$6:$M$23,"Fail")+COUNTIF('Test Cases'!$M$6:$M$23,"Blocked"))/D6,0)</f>
-        <v>0.21052631578947367</v>
+        <v>0.42105263157894735</v>
       </c>
       <c r="N6" s="19"/>
     </row>
@@ -2431,7 +2431,7 @@
     </row>
     <row r="9" spans="1:14" ht="36.75" customHeight="1">
       <c r="A9" s="9"/>
-      <c r="B9" s="21" t="s">
+      <c r="B9" s="25" t="s">
         <v>179</v>
       </c>
       <c r="C9" s="19"/>
@@ -2534,15 +2534,15 @@
       </c>
       <c r="D14" s="11">
         <f>COUNTIFS('Test Cases'!$K$6:$K$23,B14,'Test Cases'!$L$6:$L$23,"Automated")</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E14" s="11">
         <f>COUNTIFS('Test Cases'!$K$6:$K$23,B14,'Test Cases'!$M$6:$M$23,"Pass")</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F14" s="12">
         <f t="shared" ref="F14:F17" si="0">IFERROR(D14/C14,0)</f>
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="G14" s="9"/>
       <c r="H14" s="9"/>
@@ -2564,15 +2564,15 @@
       </c>
       <c r="D15" s="11">
         <f>COUNTIFS('Test Cases'!$K$6:$K$23,B15,'Test Cases'!$L$6:$L$23,"Automated")</f>
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E15" s="11">
         <f>COUNTIFS('Test Cases'!$K$6:$K$23,B15,'Test Cases'!$M$6:$M$23,"Pass")</f>
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F15" s="12">
         <f t="shared" si="0"/>
-        <v>0.4</v>
+        <v>1</v>
       </c>
       <c r="G15" s="9"/>
       <c r="H15" s="9"/>
@@ -2724,7 +2724,7 @@
       </c>
       <c r="C22" s="11">
         <f>COUNTIFS('Test Cases'!$L$6:$L$24,B22)</f>
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="D22" s="9"/>
       <c r="E22" s="11" t="s">
@@ -2732,7 +2732,7 @@
       </c>
       <c r="F22" s="11">
         <f>COUNTIFS('Test Cases'!$M$6:$M$23,E22)</f>
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="G22" s="9"/>
       <c r="H22" s="9"/>
@@ -2758,7 +2758,7 @@
       </c>
       <c r="F23" s="11">
         <f>COUNTIFS('Test Cases'!$M$6:$M$23,E23)</f>
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="G23" s="9"/>
       <c r="H23" s="9"/>
@@ -2776,7 +2776,7 @@
       </c>
       <c r="C24" s="11">
         <f>COUNTIFS('Test Cases'!$L$6:$L$23,B24)</f>
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D24" s="9"/>
       <c r="E24" s="11" t="s">
@@ -3033,15 +3033,15 @@
       </c>
       <c r="D34" s="14">
         <f>COUNTIFS('Test Cases'!$D$6:$D$23,B34,'Test Cases'!$L$6:$L$23,"Automated")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E34" s="14">
         <f>COUNTIFS('Test Cases'!$D$6:$D$23,B34,'Test Cases'!$M$6:$M$23,"Pass")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F34" s="15">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G34" s="9"/>
       <c r="H34" s="9"/>
@@ -3064,15 +3064,15 @@
       </c>
       <c r="D35" s="14">
         <f>COUNTIFS('Test Cases'!$D$6:$D$23,B35,'Test Cases'!$L$6:$L$23,"Automated")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E35" s="14">
         <f>COUNTIFS('Test Cases'!$D$6:$D$23,B35,'Test Cases'!$M$6:$M$23,"Pass")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F35" s="15">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G35" s="9"/>
       <c r="H35" s="9"/>
@@ -3095,15 +3095,15 @@
       </c>
       <c r="D36" s="14">
         <f>COUNTIFS('Test Cases'!$D$6:$D$23,B36,'Test Cases'!$L$6:$L$23,"Automated")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E36" s="14">
         <f>COUNTIFS('Test Cases'!$D$6:$D$23,B36,'Test Cases'!$M$6:$M$23,"Pass")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F36" s="15">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G36" s="9"/>
       <c r="H36" s="9"/>
@@ -3126,15 +3126,15 @@
       </c>
       <c r="D37" s="14">
         <f>COUNTIFS('Test Cases'!$D$6:$D$23,B37,'Test Cases'!$L$6:$L$23,"Automated")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E37" s="14">
         <f>COUNTIFS('Test Cases'!$D$6:$D$23,B37,'Test Cases'!$M$6:$M$23,"Pass")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F37" s="15">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G37" s="9"/>
       <c r="H37" s="9"/>
@@ -4425,6 +4425,17 @@
     <row r="1000" ht="15.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="18">
+    <mergeCell ref="I6:J7"/>
+    <mergeCell ref="K6:L7"/>
+    <mergeCell ref="M6:N7"/>
+    <mergeCell ref="B9:N9"/>
+    <mergeCell ref="D6:E7"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="B20:F20"/>
+    <mergeCell ref="B28:F28"/>
+    <mergeCell ref="B5:C5"/>
+    <mergeCell ref="B6:C7"/>
+    <mergeCell ref="F6:H7"/>
     <mergeCell ref="B1:N2"/>
     <mergeCell ref="B3:N3"/>
     <mergeCell ref="D5:E5"/>
@@ -4432,17 +4443,6 @@
     <mergeCell ref="I5:J5"/>
     <mergeCell ref="K5:L5"/>
     <mergeCell ref="M5:N5"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B20:F20"/>
-    <mergeCell ref="B28:F28"/>
-    <mergeCell ref="B5:C5"/>
-    <mergeCell ref="B6:C7"/>
-    <mergeCell ref="F6:H7"/>
-    <mergeCell ref="I6:J7"/>
-    <mergeCell ref="K6:L7"/>
-    <mergeCell ref="M6:N7"/>
-    <mergeCell ref="B9:N9"/>
-    <mergeCell ref="D6:E7"/>
   </mergeCells>
   <conditionalFormatting sqref="F30:F47">
     <cfRule type="colorScale" priority="1">
@@ -4500,7 +4500,7 @@
       <c r="G2" s="19"/>
     </row>
     <row r="3" spans="1:7" ht="27.75" customHeight="1">
-      <c r="A3" s="25" t="s">
+      <c r="A3" s="20" t="s">
         <v>1</v>
       </c>
       <c r="B3" s="19"/>
@@ -4622,7 +4622,7 @@
         <v>40</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
     </row>
     <row r="10" spans="1:7" ht="42" customHeight="1">
@@ -4645,7 +4645,7 @@
         <v>40</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
     </row>
     <row r="11" spans="1:7" ht="42" customHeight="1">
@@ -4668,7 +4668,7 @@
         <v>40</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
     </row>
     <row r="12" spans="1:7" ht="42" customHeight="1">
@@ -4691,7 +4691,7 @@
         <v>23</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
     </row>
     <row r="13" spans="1:7" ht="42" customHeight="1">
@@ -4714,7 +4714,7 @@
         <v>40</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
     </row>
     <row r="14" spans="1:7" ht="42" customHeight="1">
@@ -6024,23 +6024,23 @@
       <c r="O2" s="26"/>
     </row>
     <row r="3" spans="1:15" ht="27.75" customHeight="1">
-      <c r="A3" s="25" t="s">
+      <c r="A3" s="20" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="25"/>
-      <c r="C3" s="25"/>
-      <c r="D3" s="25"/>
-      <c r="E3" s="25"/>
-      <c r="F3" s="25"/>
-      <c r="G3" s="25"/>
-      <c r="H3" s="25"/>
-      <c r="I3" s="25"/>
-      <c r="J3" s="25"/>
-      <c r="K3" s="25"/>
-      <c r="L3" s="25"/>
-      <c r="M3" s="25"/>
-      <c r="N3" s="25"/>
-      <c r="O3" s="25"/>
+      <c r="B3" s="20"/>
+      <c r="C3" s="20"/>
+      <c r="D3" s="20"/>
+      <c r="E3" s="20"/>
+      <c r="F3" s="20"/>
+      <c r="G3" s="20"/>
+      <c r="H3" s="20"/>
+      <c r="I3" s="20"/>
+      <c r="J3" s="20"/>
+      <c r="K3" s="20"/>
+      <c r="L3" s="20"/>
+      <c r="M3" s="20"/>
+      <c r="N3" s="20"/>
+      <c r="O3" s="20"/>
     </row>
     <row r="5" spans="1:15" ht="36.75" customHeight="1">
       <c r="A5" s="2" t="s">
@@ -6311,11 +6311,11 @@
       <c r="K10" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="L10" s="5" t="s">
-        <v>79</v>
-      </c>
-      <c r="M10" s="5" t="s">
-        <v>82</v>
+      <c r="L10" s="17" t="s">
+        <v>53</v>
+      </c>
+      <c r="M10" s="17" t="s">
+        <v>56</v>
       </c>
       <c r="N10" s="5" t="s">
         <v>55</v>
@@ -6359,10 +6359,10 @@
         <v>40</v>
       </c>
       <c r="L11" s="8" t="s">
-        <v>79</v>
+        <v>53</v>
       </c>
       <c r="M11" s="8" t="s">
-        <v>82</v>
+        <v>56</v>
       </c>
       <c r="N11" s="8" t="s">
         <v>60</v>
@@ -6405,11 +6405,11 @@
       <c r="K12" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="L12" s="5" t="s">
-        <v>79</v>
-      </c>
-      <c r="M12" s="5" t="s">
-        <v>82</v>
+      <c r="L12" s="17" t="s">
+        <v>53</v>
+      </c>
+      <c r="M12" s="17" t="s">
+        <v>56</v>
       </c>
       <c r="N12" s="5" t="s">
         <v>65</v>
@@ -6453,10 +6453,10 @@
         <v>40</v>
       </c>
       <c r="L13" s="8" t="s">
-        <v>79</v>
+        <v>53</v>
       </c>
       <c r="M13" s="8" t="s">
-        <v>82</v>
+        <v>56</v>
       </c>
       <c r="N13" s="8" t="s">
         <v>71</v>

--- a/test-cases/QA_Playground_TypeScript_Playwright_Test_Suite.xlsx
+++ b/test-cases/QA_Playground_TypeScript_Playwright_Test_Suite.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Silerio\Music\PLAYWRIGHT AUTOMATION\test-cases\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED14E705-05F1-4567-B546-901C85A96DF6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E2B30AEF-8E8E-41FB-A818-683A5AD1457B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Dashboard" sheetId="1" r:id="rId1"/>
@@ -1277,25 +1277,25 @@
     <xf numFmtId="0" fontId="15" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="11" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="9" fontId="11" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1549,13 +1549,13 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="4"/>
                 <c:pt idx="0">
-                  <c:v>10</c:v>
+                  <c:v>8</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>8</c:v>
+                  <c:v>10</c:v>
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>0</c:v>
@@ -1758,13 +1758,13 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="4"/>
                 <c:pt idx="0">
-                  <c:v>3</c:v>
+                  <c:v>4</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>5</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0</c:v>
+                  <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>0</c:v>
@@ -2269,7 +2269,7 @@
   <sheetData>
     <row r="1" spans="1:14" ht="27.75" customHeight="1">
       <c r="A1" s="9"/>
-      <c r="B1" s="18" t="s">
+      <c r="B1" s="24" t="s">
         <v>160</v>
       </c>
       <c r="C1" s="19"/>
@@ -2303,7 +2303,7 @@
     </row>
     <row r="3" spans="1:14" ht="27.75" customHeight="1">
       <c r="A3" s="9"/>
-      <c r="B3" s="20" t="s">
+      <c r="B3" s="25" t="s">
         <v>161</v>
       </c>
       <c r="C3" s="19"/>
@@ -2337,63 +2337,63 @@
     </row>
     <row r="5" spans="1:14">
       <c r="A5" s="9"/>
-      <c r="B5" s="21" t="s">
+      <c r="B5" s="23" t="s">
         <v>163</v>
       </c>
       <c r="C5" s="19"/>
-      <c r="D5" s="21" t="s">
+      <c r="D5" s="23" t="s">
         <v>164</v>
       </c>
       <c r="E5" s="19"/>
-      <c r="F5" s="21" t="s">
+      <c r="F5" s="23" t="s">
         <v>165</v>
       </c>
       <c r="G5" s="19"/>
       <c r="H5" s="19"/>
-      <c r="I5" s="21" t="s">
+      <c r="I5" s="23" t="s">
         <v>166</v>
       </c>
       <c r="J5" s="19"/>
-      <c r="K5" s="21" t="s">
+      <c r="K5" s="23" t="s">
         <v>167</v>
       </c>
       <c r="L5" s="19"/>
-      <c r="M5" s="21" t="s">
+      <c r="M5" s="23" t="s">
         <v>168</v>
       </c>
       <c r="N5" s="19"/>
     </row>
     <row r="6" spans="1:14">
       <c r="A6" s="9"/>
-      <c r="B6" s="23">
+      <c r="B6" s="18">
         <f>COUNTA('Test Scenarios'!$A$6:$A$24)</f>
         <v>19</v>
       </c>
       <c r="C6" s="19"/>
-      <c r="D6" s="23">
+      <c r="D6" s="18">
         <f>COUNTA('Test Cases'!$B$6:$B$24)</f>
         <v>19</v>
       </c>
       <c r="E6" s="19"/>
-      <c r="F6" s="24">
+      <c r="F6" s="20">
         <f>IFERROR(COUNTIF('Test Cases'!$L$6:$L$23,"Automated")/D6,0)</f>
-        <v>0.42105263157894735</v>
+        <v>0.52631578947368418</v>
       </c>
       <c r="G6" s="19"/>
       <c r="H6" s="19"/>
-      <c r="I6" s="23">
+      <c r="I6" s="18">
         <f>COUNTIFS('Test Cases'!$M$6:$M$23,"Pass")</f>
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="J6" s="19"/>
-      <c r="K6" s="23">
+      <c r="K6" s="18">
         <f>COUNTIFS('Test Cases'!$M$6:$M$23,"Fail")</f>
         <v>0</v>
       </c>
       <c r="L6" s="19"/>
-      <c r="M6" s="24">
+      <c r="M6" s="20">
         <f>IFERROR((COUNTIF('Test Cases'!$M$6:$M$23,"Pass")+COUNTIF('Test Cases'!$M$6:$M$23,"Fail")+COUNTIF('Test Cases'!$M$6:$M$23,"Blocked"))/D6,0)</f>
-        <v>0.42105263157894735</v>
+        <v>0.52631578947368418</v>
       </c>
       <c r="N6" s="19"/>
     </row>
@@ -2431,7 +2431,7 @@
     </row>
     <row r="9" spans="1:14" ht="36.75" customHeight="1">
       <c r="A9" s="9"/>
-      <c r="B9" s="25" t="s">
+      <c r="B9" s="21" t="s">
         <v>179</v>
       </c>
       <c r="C9" s="19"/>
@@ -2534,15 +2534,15 @@
       </c>
       <c r="D14" s="11">
         <f>COUNTIFS('Test Cases'!$K$6:$K$23,B14,'Test Cases'!$L$6:$L$23,"Automated")</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E14" s="11">
         <f>COUNTIFS('Test Cases'!$K$6:$K$23,B14,'Test Cases'!$M$6:$M$23,"Pass")</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F14" s="12">
         <f t="shared" ref="F14:F17" si="0">IFERROR(D14/C14,0)</f>
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="G14" s="9"/>
       <c r="H14" s="9"/>
@@ -2594,15 +2594,15 @@
       </c>
       <c r="D16" s="11">
         <f>COUNTIFS('Test Cases'!$K$6:$K$23,B16,'Test Cases'!$L$6:$L$23,"Automated")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E16" s="11">
         <f>COUNTIFS('Test Cases'!$K$6:$K$23,B16,'Test Cases'!$M$6:$M$23,"Pass")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F16" s="12">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="G16" s="9"/>
       <c r="H16" s="9"/>
@@ -2724,7 +2724,7 @@
       </c>
       <c r="C22" s="11">
         <f>COUNTIFS('Test Cases'!$L$6:$L$24,B22)</f>
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D22" s="9"/>
       <c r="E22" s="11" t="s">
@@ -2732,7 +2732,7 @@
       </c>
       <c r="F22" s="11">
         <f>COUNTIFS('Test Cases'!$M$6:$M$23,E22)</f>
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="G22" s="9"/>
       <c r="H22" s="9"/>
@@ -2758,7 +2758,7 @@
       </c>
       <c r="F23" s="11">
         <f>COUNTIFS('Test Cases'!$M$6:$M$23,E23)</f>
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G23" s="9"/>
       <c r="H23" s="9"/>
@@ -2776,7 +2776,7 @@
       </c>
       <c r="C24" s="11">
         <f>COUNTIFS('Test Cases'!$L$6:$L$23,B24)</f>
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D24" s="9"/>
       <c r="E24" s="11" t="s">
@@ -3157,15 +3157,15 @@
       </c>
       <c r="D38" s="14">
         <f>COUNTIFS('Test Cases'!$D$6:$D$23,B38,'Test Cases'!$L$6:$L$23,"Automated")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E38" s="14">
         <f>COUNTIFS('Test Cases'!$D$6:$D$23,B38,'Test Cases'!$M$6:$M$23,"Pass")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F38" s="15">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G38" s="9"/>
       <c r="H38" s="9"/>
@@ -3188,15 +3188,15 @@
       </c>
       <c r="D39" s="14">
         <f>COUNTIFS('Test Cases'!$D$6:$D$23,B39,'Test Cases'!$L$6:$L$23,"Automated")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E39" s="14">
         <f>COUNTIFS('Test Cases'!$D$6:$D$23,B39,'Test Cases'!$M$6:$M$23,"Pass")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F39" s="15">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G39" s="9"/>
       <c r="H39" s="9"/>
@@ -4425,17 +4425,6 @@
     <row r="1000" ht="15.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="18">
-    <mergeCell ref="I6:J7"/>
-    <mergeCell ref="K6:L7"/>
-    <mergeCell ref="M6:N7"/>
-    <mergeCell ref="B9:N9"/>
-    <mergeCell ref="D6:E7"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B20:F20"/>
-    <mergeCell ref="B28:F28"/>
-    <mergeCell ref="B5:C5"/>
-    <mergeCell ref="B6:C7"/>
-    <mergeCell ref="F6:H7"/>
     <mergeCell ref="B1:N2"/>
     <mergeCell ref="B3:N3"/>
     <mergeCell ref="D5:E5"/>
@@ -4443,6 +4432,17 @@
     <mergeCell ref="I5:J5"/>
     <mergeCell ref="K5:L5"/>
     <mergeCell ref="M5:N5"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="B20:F20"/>
+    <mergeCell ref="B28:F28"/>
+    <mergeCell ref="B5:C5"/>
+    <mergeCell ref="B6:C7"/>
+    <mergeCell ref="F6:H7"/>
+    <mergeCell ref="I6:J7"/>
+    <mergeCell ref="K6:L7"/>
+    <mergeCell ref="M6:N7"/>
+    <mergeCell ref="B9:N9"/>
+    <mergeCell ref="D6:E7"/>
   </mergeCells>
   <conditionalFormatting sqref="F30:F47">
     <cfRule type="colorScale" priority="1">
@@ -4500,7 +4500,7 @@
       <c r="G2" s="19"/>
     </row>
     <row r="3" spans="1:7" ht="27.75" customHeight="1">
-      <c r="A3" s="20" t="s">
+      <c r="A3" s="25" t="s">
         <v>1</v>
       </c>
       <c r="B3" s="19"/>
@@ -4737,7 +4737,7 @@
         <v>23</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
     </row>
     <row r="15" spans="1:7" ht="42" customHeight="1">
@@ -4760,7 +4760,7 @@
         <v>84</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
     </row>
     <row r="16" spans="1:7" ht="42" customHeight="1">
@@ -6024,23 +6024,23 @@
       <c r="O2" s="26"/>
     </row>
     <row r="3" spans="1:15" ht="27.75" customHeight="1">
-      <c r="A3" s="20" t="s">
+      <c r="A3" s="25" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="20"/>
-      <c r="C3" s="20"/>
-      <c r="D3" s="20"/>
-      <c r="E3" s="20"/>
-      <c r="F3" s="20"/>
-      <c r="G3" s="20"/>
-      <c r="H3" s="20"/>
-      <c r="I3" s="20"/>
-      <c r="J3" s="20"/>
-      <c r="K3" s="20"/>
-      <c r="L3" s="20"/>
-      <c r="M3" s="20"/>
-      <c r="N3" s="20"/>
-      <c r="O3" s="20"/>
+      <c r="B3" s="25"/>
+      <c r="C3" s="25"/>
+      <c r="D3" s="25"/>
+      <c r="E3" s="25"/>
+      <c r="F3" s="25"/>
+      <c r="G3" s="25"/>
+      <c r="H3" s="25"/>
+      <c r="I3" s="25"/>
+      <c r="J3" s="25"/>
+      <c r="K3" s="25"/>
+      <c r="L3" s="25"/>
+      <c r="M3" s="25"/>
+      <c r="N3" s="25"/>
+      <c r="O3" s="25"/>
     </row>
     <row r="5" spans="1:15" ht="36.75" customHeight="1">
       <c r="A5" s="2" t="s">
@@ -6499,11 +6499,11 @@
       <c r="K14" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="L14" s="5" t="s">
-        <v>79</v>
-      </c>
-      <c r="M14" s="5" t="s">
-        <v>82</v>
+      <c r="L14" s="17" t="s">
+        <v>53</v>
+      </c>
+      <c r="M14" s="17" t="s">
+        <v>56</v>
       </c>
       <c r="N14" s="5" t="s">
         <v>77</v>
@@ -6547,10 +6547,10 @@
         <v>84</v>
       </c>
       <c r="L15" s="8" t="s">
-        <v>79</v>
+        <v>53</v>
       </c>
       <c r="M15" s="8" t="s">
-        <v>82</v>
+        <v>56</v>
       </c>
       <c r="N15" s="8" t="s">
         <v>83</v>
